--- a/data/inventory_analysis/Project_Bob_Sell_Down_Priority_11092026.xlsx
+++ b/data/inventory_analysis/Project_Bob_Sell_Down_Priority_11092026.xlsx
@@ -477,7 +477,7 @@
     <row r="6" ht="75" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>527,963 total stock units across all franchises with any available stock. 377,643 matched a franchise with a known FW27 exit-season tier (Sheet 2). 23,130 matched a franchise still at "REVIEW" -- exit timing undecided, NOT force-ranked (Sheet 3). 127,190 has no FW27-tab row at all -- not on this season's plan, one way or another (Sheet 4).</t>
+          <t>527,963 total stock units across all franchises with any available stock. 377,643 matched a franchise with a known FW27 exit-season tier (Sheet 2). 23,130 matched a franchise still at "REVIEW" -- exit timing undecided, NOT force-ranked (Sheet 3). 127,190 has no FW27-tab row at all (Sheet 4) -- of which 41,566 units (54 franchises) were still Active in SS27 and are NOT safe to assume retired (REG-INV-012).</t>
         </is>
       </c>
     </row>
@@ -9716,12 +9716,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C405"/>
+  <dimension ref="A1:F405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9734,7 +9737,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Not matched to any of the 392 FW27 plan rows -- could be a franchise already fully retired before FW27, or a naming mismatch (REG-INV-011). Not assumed safe or unsafe -- just not visible to this join. Sorted by units in stock, descending.</t>
+          <t>NOT safe to blanket-label "retired before FW27" (REG-INV-012): cross-checked against SS27 (the season immediately before FW27) below. 54 franchises (41,566 units) were still Active there and need a real merch check -- likely explanations include a genuine drop, but also a name change too large for Base+Gender matching to catch (e.g. "Rosson Softshell Hood" -&gt; "Rosson Mid II Hood", confirmed both exist, neither name matches the other). Rows with "SS27 Active? = False" or blank (not in SS27 either) are the safer default for "likely already retired." Sorted by units in stock, descending.</t>
         </is>
       </c>
     </row>
@@ -9754,6 +9757,21 @@
           <t>Units in Stock</t>
         </is>
       </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>In SS27 Tab?</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>SS27 Active?</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>SS27 Status</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -9769,6 +9787,13 @@
       <c r="C6" s="6" t="n">
         <v>4936</v>
       </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -9784,6 +9809,13 @@
       <c r="C7" s="6" t="n">
         <v>3753</v>
       </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -9799,6 +9831,13 @@
       <c r="C8" s="6" t="n">
         <v>2754</v>
       </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -9814,6 +9853,19 @@
       <c r="C9" s="6" t="n">
         <v>2639</v>
       </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -9829,6 +9881,19 @@
       <c r="C10" s="6" t="n">
         <v>2525</v>
       </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -9844,6 +9909,13 @@
       <c r="C11" s="6" t="n">
         <v>2439</v>
       </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -9859,6 +9931,19 @@
       <c r="C12" s="6" t="n">
         <v>2262</v>
       </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -9874,6 +9959,19 @@
       <c r="C13" s="6" t="n">
         <v>1948</v>
       </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -9889,6 +9987,13 @@
       <c r="C14" s="6" t="n">
         <v>1930</v>
       </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -9904,6 +10009,19 @@
       <c r="C15" s="6" t="n">
         <v>1904</v>
       </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -9919,6 +10037,13 @@
       <c r="C16" s="6" t="n">
         <v>1795</v>
       </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -9934,6 +10059,19 @@
       <c r="C17" s="6" t="n">
         <v>1733</v>
       </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -9949,6 +10087,19 @@
       <c r="C18" s="6" t="n">
         <v>1628</v>
       </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -9964,6 +10115,19 @@
       <c r="C19" s="6" t="n">
         <v>1571</v>
       </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -9979,6 +10143,19 @@
       <c r="C20" s="6" t="n">
         <v>1559</v>
       </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -9994,6 +10171,19 @@
       <c r="C21" s="6" t="n">
         <v>1452</v>
       </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -10009,6 +10199,13 @@
       <c r="C22" s="6" t="n">
         <v>1449</v>
       </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -10024,6 +10221,13 @@
       <c r="C23" s="6" t="n">
         <v>1433</v>
       </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -10039,6 +10243,13 @@
       <c r="C24" s="6" t="n">
         <v>1425</v>
       </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -10054,6 +10265,13 @@
       <c r="C25" s="6" t="n">
         <v>1412</v>
       </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -10069,6 +10287,13 @@
       <c r="C26" s="6" t="n">
         <v>1266</v>
       </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -10084,6 +10309,13 @@
       <c r="C27" s="6" t="n">
         <v>1235</v>
       </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -10099,6 +10331,19 @@
       <c r="C28" s="6" t="n">
         <v>1225</v>
       </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -10114,6 +10359,13 @@
       <c r="C29" s="6" t="n">
         <v>1214</v>
       </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -10129,6 +10381,13 @@
       <c r="C30" s="6" t="n">
         <v>1189</v>
       </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -10144,6 +10403,19 @@
       <c r="C31" s="6" t="n">
         <v>1138</v>
       </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -10159,6 +10431,19 @@
       <c r="C32" s="6" t="n">
         <v>1113</v>
       </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -10174,6 +10459,13 @@
       <c r="C33" s="6" t="n">
         <v>1058</v>
       </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -10189,6 +10481,19 @@
       <c r="C34" s="6" t="n">
         <v>1036</v>
       </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -10204,6 +10509,13 @@
       <c r="C35" s="6" t="n">
         <v>1035</v>
       </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -10219,6 +10531,19 @@
       <c r="C36" s="6" t="n">
         <v>1021</v>
       </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -10234,6 +10559,19 @@
       <c r="C37" s="6" t="n">
         <v>991</v>
       </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -10249,6 +10587,19 @@
       <c r="C38" s="6" t="n">
         <v>957</v>
       </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -10264,6 +10615,13 @@
       <c r="C39" s="6" t="n">
         <v>951</v>
       </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -10279,6 +10637,13 @@
       <c r="C40" s="6" t="n">
         <v>940</v>
       </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -10294,6 +10659,19 @@
       <c r="C41" s="6" t="n">
         <v>927</v>
       </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -10309,6 +10687,13 @@
       <c r="C42" s="6" t="n">
         <v>904</v>
       </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -10324,6 +10709,13 @@
       <c r="C43" s="6" t="n">
         <v>876</v>
       </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -10339,6 +10731,19 @@
       <c r="C44" s="6" t="n">
         <v>871</v>
       </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -10354,6 +10759,13 @@
       <c r="C45" s="6" t="n">
         <v>868</v>
       </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -10369,6 +10781,13 @@
       <c r="C46" s="6" t="n">
         <v>865</v>
       </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -10384,6 +10803,13 @@
       <c r="C47" s="6" t="n">
         <v>861</v>
       </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -10399,6 +10825,19 @@
       <c r="C48" s="6" t="n">
         <v>844</v>
       </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -10414,6 +10853,13 @@
       <c r="C49" s="6" t="n">
         <v>828</v>
       </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -10429,6 +10875,19 @@
       <c r="C50" s="6" t="n">
         <v>799</v>
       </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -10444,6 +10903,13 @@
       <c r="C51" s="6" t="n">
         <v>783</v>
       </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -10459,6 +10925,13 @@
       <c r="C52" s="6" t="n">
         <v>779</v>
       </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -10474,6 +10947,19 @@
       <c r="C53" s="6" t="n">
         <v>769</v>
       </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -10489,6 +10975,13 @@
       <c r="C54" s="6" t="n">
         <v>768</v>
       </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -10504,6 +10997,13 @@
       <c r="C55" s="6" t="n">
         <v>762</v>
       </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -10519,6 +11019,13 @@
       <c r="C56" s="6" t="n">
         <v>759</v>
       </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -10534,6 +11041,13 @@
       <c r="C57" s="6" t="n">
         <v>754</v>
       </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -10549,6 +11063,19 @@
       <c r="C58" s="6" t="n">
         <v>752</v>
       </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -10564,6 +11091,13 @@
       <c r="C59" s="6" t="n">
         <v>735</v>
       </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -10579,6 +11113,13 @@
       <c r="C60" s="6" t="n">
         <v>734</v>
       </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -10594,6 +11135,13 @@
       <c r="C61" s="6" t="n">
         <v>727</v>
       </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -10609,6 +11157,13 @@
       <c r="C62" s="6" t="n">
         <v>718</v>
       </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -10624,6 +11179,13 @@
       <c r="C63" s="6" t="n">
         <v>717</v>
       </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -10639,6 +11201,13 @@
       <c r="C64" s="6" t="n">
         <v>698</v>
       </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -10654,6 +11223,19 @@
       <c r="C65" s="6" t="n">
         <v>690</v>
       </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -10669,6 +11251,13 @@
       <c r="C66" s="6" t="n">
         <v>655</v>
       </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -10684,6 +11273,19 @@
       <c r="C67" s="6" t="n">
         <v>645</v>
       </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -10699,6 +11301,13 @@
       <c r="C68" s="6" t="n">
         <v>643</v>
       </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -10714,6 +11323,13 @@
       <c r="C69" s="6" t="n">
         <v>637</v>
       </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="5" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -10729,6 +11345,13 @@
       <c r="C70" s="6" t="n">
         <v>633</v>
       </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -10744,6 +11367,13 @@
       <c r="C71" s="6" t="n">
         <v>630</v>
       </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -10759,6 +11389,13 @@
       <c r="C72" s="6" t="n">
         <v>626</v>
       </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="5" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -10774,6 +11411,13 @@
       <c r="C73" s="6" t="n">
         <v>615</v>
       </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="5" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -10789,6 +11433,13 @@
       <c r="C74" s="6" t="n">
         <v>603</v>
       </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="5" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -10804,6 +11455,13 @@
       <c r="C75" s="6" t="n">
         <v>603</v>
       </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="5" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -10819,6 +11477,13 @@
       <c r="C76" s="6" t="n">
         <v>595</v>
       </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="5" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -10834,6 +11499,13 @@
       <c r="C77" s="6" t="n">
         <v>583</v>
       </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -10849,6 +11521,13 @@
       <c r="C78" s="6" t="n">
         <v>582</v>
       </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -10864,6 +11543,13 @@
       <c r="C79" s="6" t="n">
         <v>572</v>
       </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="n"/>
+      <c r="F79" s="5" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -10879,6 +11565,19 @@
       <c r="C80" s="6" t="n">
         <v>566</v>
       </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -10894,6 +11593,13 @@
       <c r="C81" s="6" t="n">
         <v>562</v>
       </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="n"/>
+      <c r="F81" s="5" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -10909,6 +11615,19 @@
       <c r="C82" s="6" t="n">
         <v>560</v>
       </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -10924,6 +11643,13 @@
       <c r="C83" s="6" t="n">
         <v>551</v>
       </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="n"/>
+      <c r="F83" s="5" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -10939,6 +11665,13 @@
       <c r="C84" s="6" t="n">
         <v>541</v>
       </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="n"/>
+      <c r="F84" s="5" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -10954,6 +11687,19 @@
       <c r="C85" s="6" t="n">
         <v>525</v>
       </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -10969,6 +11715,19 @@
       <c r="C86" s="6" t="n">
         <v>524</v>
       </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -10984,6 +11743,13 @@
       <c r="C87" s="6" t="n">
         <v>508</v>
       </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="n"/>
+      <c r="F87" s="5" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -10999,6 +11765,13 @@
       <c r="C88" s="6" t="n">
         <v>499</v>
       </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="n"/>
+      <c r="F88" s="5" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -11014,6 +11787,13 @@
       <c r="C89" s="6" t="n">
         <v>497</v>
       </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="n"/>
+      <c r="F89" s="5" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -11029,6 +11809,19 @@
       <c r="C90" s="6" t="n">
         <v>491</v>
       </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -11044,6 +11837,13 @@
       <c r="C91" s="6" t="n">
         <v>488</v>
       </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="n"/>
+      <c r="F91" s="5" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -11059,6 +11859,13 @@
       <c r="C92" s="6" t="n">
         <v>484</v>
       </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="n"/>
+      <c r="F92" s="5" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
@@ -11074,6 +11881,13 @@
       <c r="C93" s="6" t="n">
         <v>471</v>
       </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="n"/>
+      <c r="F93" s="5" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -11089,6 +11903,13 @@
       <c r="C94" s="6" t="n">
         <v>448</v>
       </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="n"/>
+      <c r="F94" s="5" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
@@ -11104,6 +11925,13 @@
       <c r="C95" s="6" t="n">
         <v>446</v>
       </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="n"/>
+      <c r="F95" s="5" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
@@ -11119,6 +11947,13 @@
       <c r="C96" s="6" t="n">
         <v>446</v>
       </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="n"/>
+      <c r="F96" s="5" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
@@ -11134,6 +11969,13 @@
       <c r="C97" s="6" t="n">
         <v>444</v>
       </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="n"/>
+      <c r="F97" s="5" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -11149,6 +11991,13 @@
       <c r="C98" s="6" t="n">
         <v>438</v>
       </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="n"/>
+      <c r="F98" s="5" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -11164,6 +12013,13 @@
       <c r="C99" s="6" t="n">
         <v>419</v>
       </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="n"/>
+      <c r="F99" s="5" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
@@ -11179,6 +12035,19 @@
       <c r="C100" s="6" t="n">
         <v>418</v>
       </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
@@ -11194,6 +12063,13 @@
       <c r="C101" s="6" t="n">
         <v>415</v>
       </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="n"/>
+      <c r="F101" s="5" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
@@ -11209,6 +12085,13 @@
       <c r="C102" s="6" t="n">
         <v>404</v>
       </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="n"/>
+      <c r="F102" s="5" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
@@ -11224,6 +12107,13 @@
       <c r="C103" s="6" t="n">
         <v>382</v>
       </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="n"/>
+      <c r="F103" s="5" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -11239,6 +12129,19 @@
       <c r="C104" s="6" t="n">
         <v>381</v>
       </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -11254,6 +12157,13 @@
       <c r="C105" s="6" t="n">
         <v>376</v>
       </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="n"/>
+      <c r="F105" s="5" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -11269,6 +12179,19 @@
       <c r="C106" s="6" t="n">
         <v>372</v>
       </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
@@ -11284,6 +12207,19 @@
       <c r="C107" s="6" t="n">
         <v>371</v>
       </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
@@ -11299,6 +12235,13 @@
       <c r="C108" s="6" t="n">
         <v>371</v>
       </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="n"/>
+      <c r="F108" s="5" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
@@ -11314,6 +12257,19 @@
       <c r="C109" s="6" t="n">
         <v>367</v>
       </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -11329,6 +12285,13 @@
       <c r="C110" s="6" t="n">
         <v>362</v>
       </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="n"/>
+      <c r="F110" s="5" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
@@ -11344,6 +12307,19 @@
       <c r="C111" s="6" t="n">
         <v>360</v>
       </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
@@ -11359,6 +12335,13 @@
       <c r="C112" s="6" t="n">
         <v>359</v>
       </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="n"/>
+      <c r="F112" s="5" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
@@ -11374,6 +12357,13 @@
       <c r="C113" s="6" t="n">
         <v>358</v>
       </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="n"/>
+      <c r="F113" s="5" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
@@ -11389,6 +12379,13 @@
       <c r="C114" s="6" t="n">
         <v>356</v>
       </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="n"/>
+      <c r="F114" s="5" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
@@ -11404,6 +12401,19 @@
       <c r="C115" s="6" t="n">
         <v>354</v>
       </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
@@ -11419,6 +12429,13 @@
       <c r="C116" s="6" t="n">
         <v>347</v>
       </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="n"/>
+      <c r="F116" s="5" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
@@ -11434,6 +12451,13 @@
       <c r="C117" s="6" t="n">
         <v>346</v>
       </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="n"/>
+      <c r="F117" s="5" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -11449,6 +12473,13 @@
       <c r="C118" s="6" t="n">
         <v>342</v>
       </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="n"/>
+      <c r="F118" s="5" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
@@ -11464,6 +12495,19 @@
       <c r="C119" s="6" t="n">
         <v>340</v>
       </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
@@ -11479,6 +12523,19 @@
       <c r="C120" s="6" t="n">
         <v>335</v>
       </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
@@ -11494,6 +12551,19 @@
       <c r="C121" s="6" t="n">
         <v>330</v>
       </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
@@ -11509,6 +12579,13 @@
       <c r="C122" s="6" t="n">
         <v>327</v>
       </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="n"/>
+      <c r="F122" s="5" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
@@ -11524,6 +12601,13 @@
       <c r="C123" s="6" t="n">
         <v>323</v>
       </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="n"/>
+      <c r="F123" s="5" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
@@ -11539,6 +12623,13 @@
       <c r="C124" s="6" t="n">
         <v>318</v>
       </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="n"/>
+      <c r="F124" s="5" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
@@ -11554,6 +12645,13 @@
       <c r="C125" s="6" t="n">
         <v>297</v>
       </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="n"/>
+      <c r="F125" s="5" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
@@ -11569,6 +12667,19 @@
       <c r="C126" s="6" t="n">
         <v>296</v>
       </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
@@ -11584,6 +12695,19 @@
       <c r="C127" s="6" t="n">
         <v>295</v>
       </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
@@ -11599,6 +12723,13 @@
       <c r="C128" s="6" t="n">
         <v>290</v>
       </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="n"/>
+      <c r="F128" s="5" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
@@ -11614,6 +12745,13 @@
       <c r="C129" s="6" t="n">
         <v>290</v>
       </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="n"/>
+      <c r="F129" s="5" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
@@ -11629,6 +12767,13 @@
       <c r="C130" s="6" t="n">
         <v>282</v>
       </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="n"/>
+      <c r="F130" s="5" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
@@ -11644,6 +12789,13 @@
       <c r="C131" s="6" t="n">
         <v>275</v>
       </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="n"/>
+      <c r="F131" s="5" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
@@ -11659,6 +12811,19 @@
       <c r="C132" s="6" t="n">
         <v>265</v>
       </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
@@ -11674,6 +12839,13 @@
       <c r="C133" s="6" t="n">
         <v>264</v>
       </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="n"/>
+      <c r="F133" s="5" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
@@ -11689,6 +12861,13 @@
       <c r="C134" s="6" t="n">
         <v>261</v>
       </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="n"/>
+      <c r="F134" s="5" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
@@ -11704,6 +12883,13 @@
       <c r="C135" s="6" t="n">
         <v>258</v>
       </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="n"/>
+      <c r="F135" s="5" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
@@ -11719,6 +12905,19 @@
       <c r="C136" s="6" t="n">
         <v>255</v>
       </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
@@ -11734,6 +12933,13 @@
       <c r="C137" s="6" t="n">
         <v>251</v>
       </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n"/>
+      <c r="F137" s="5" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
@@ -11749,6 +12955,13 @@
       <c r="C138" s="6" t="n">
         <v>250</v>
       </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="n"/>
+      <c r="F138" s="5" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
@@ -11764,6 +12977,19 @@
       <c r="C139" s="6" t="n">
         <v>249</v>
       </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
@@ -11779,6 +13005,13 @@
       <c r="C140" s="6" t="n">
         <v>248</v>
       </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="n"/>
+      <c r="F140" s="5" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
@@ -11794,6 +13027,19 @@
       <c r="C141" s="6" t="n">
         <v>246</v>
       </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -11809,6 +13055,13 @@
       <c r="C142" s="6" t="n">
         <v>241</v>
       </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="n"/>
+      <c r="F142" s="5" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
@@ -11824,6 +13077,13 @@
       <c r="C143" s="6" t="n">
         <v>240</v>
       </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="n"/>
+      <c r="F143" s="5" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
@@ -11839,6 +13099,13 @@
       <c r="C144" s="6" t="n">
         <v>235</v>
       </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="n"/>
+      <c r="F144" s="5" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
@@ -11854,6 +13121,13 @@
       <c r="C145" s="6" t="n">
         <v>235</v>
       </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="n"/>
+      <c r="F145" s="5" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
@@ -11869,6 +13143,13 @@
       <c r="C146" s="6" t="n">
         <v>234</v>
       </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="n"/>
+      <c r="F146" s="5" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
@@ -11884,6 +13165,13 @@
       <c r="C147" s="6" t="n">
         <v>232</v>
       </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="n"/>
+      <c r="F147" s="5" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
@@ -11899,6 +13187,13 @@
       <c r="C148" s="6" t="n">
         <v>224</v>
       </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="n"/>
+      <c r="F148" s="5" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
@@ -11914,6 +13209,13 @@
       <c r="C149" s="6" t="n">
         <v>218</v>
       </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="n"/>
+      <c r="F149" s="5" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
@@ -11929,6 +13231,13 @@
       <c r="C150" s="6" t="n">
         <v>214</v>
       </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="n"/>
+      <c r="F150" s="5" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
@@ -11944,6 +13253,13 @@
       <c r="C151" s="6" t="n">
         <v>209</v>
       </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="n"/>
+      <c r="F151" s="5" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
@@ -11959,6 +13275,13 @@
       <c r="C152" s="6" t="n">
         <v>207</v>
       </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="n"/>
+      <c r="F152" s="5" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
@@ -11974,6 +13297,13 @@
       <c r="C153" s="6" t="n">
         <v>203</v>
       </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="n"/>
+      <c r="F153" s="5" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
@@ -11989,6 +13319,13 @@
       <c r="C154" s="6" t="n">
         <v>200</v>
       </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="n"/>
+      <c r="F154" s="5" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
@@ -12004,6 +13341,13 @@
       <c r="C155" s="6" t="n">
         <v>198</v>
       </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="n"/>
+      <c r="F155" s="5" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
@@ -12019,6 +13363,13 @@
       <c r="C156" s="6" t="n">
         <v>197</v>
       </c>
+      <c r="D156" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="n"/>
+      <c r="F156" s="5" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
@@ -12034,6 +13385,19 @@
       <c r="C157" s="6" t="n">
         <v>194</v>
       </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
@@ -12049,6 +13413,13 @@
       <c r="C158" s="6" t="n">
         <v>185</v>
       </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="n"/>
+      <c r="F158" s="5" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
@@ -12064,6 +13435,19 @@
       <c r="C159" s="6" t="n">
         <v>184</v>
       </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
@@ -12079,6 +13463,13 @@
       <c r="C160" s="6" t="n">
         <v>181</v>
       </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="n"/>
+      <c r="F160" s="5" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
@@ -12094,6 +13485,19 @@
       <c r="C161" s="6" t="n">
         <v>179</v>
       </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
@@ -12109,6 +13513,13 @@
       <c r="C162" s="6" t="n">
         <v>173</v>
       </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="n"/>
+      <c r="F162" s="5" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
@@ -12124,6 +13535,13 @@
       <c r="C163" s="6" t="n">
         <v>170</v>
       </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="n"/>
+      <c r="F163" s="5" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
@@ -12139,6 +13557,13 @@
       <c r="C164" s="6" t="n">
         <v>164</v>
       </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="n"/>
+      <c r="F164" s="5" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
@@ -12154,6 +13579,13 @@
       <c r="C165" s="6" t="n">
         <v>161</v>
       </c>
+      <c r="D165" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="n"/>
+      <c r="F165" s="5" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
@@ -12169,6 +13601,13 @@
       <c r="C166" s="6" t="n">
         <v>159</v>
       </c>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="n"/>
+      <c r="F166" s="5" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
@@ -12184,6 +13623,19 @@
       <c r="C167" s="6" t="n">
         <v>158</v>
       </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F167" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
@@ -12199,6 +13651,13 @@
       <c r="C168" s="6" t="n">
         <v>156</v>
       </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="n"/>
+      <c r="F168" s="5" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
@@ -12214,6 +13673,19 @@
       <c r="C169" s="6" t="n">
         <v>155</v>
       </c>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
@@ -12229,6 +13701,13 @@
       <c r="C170" s="6" t="n">
         <v>154</v>
       </c>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="n"/>
+      <c r="F170" s="5" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
@@ -12244,6 +13723,13 @@
       <c r="C171" s="6" t="n">
         <v>153</v>
       </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="n"/>
+      <c r="F171" s="5" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
@@ -12259,6 +13745,13 @@
       <c r="C172" s="6" t="n">
         <v>153</v>
       </c>
+      <c r="D172" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="n"/>
+      <c r="F172" s="5" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
@@ -12274,6 +13767,13 @@
       <c r="C173" s="6" t="n">
         <v>149</v>
       </c>
+      <c r="D173" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="n"/>
+      <c r="F173" s="5" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
@@ -12289,6 +13789,13 @@
       <c r="C174" s="6" t="n">
         <v>149</v>
       </c>
+      <c r="D174" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E174" s="5" t="n"/>
+      <c r="F174" s="5" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
@@ -12304,6 +13811,13 @@
       <c r="C175" s="6" t="n">
         <v>149</v>
       </c>
+      <c r="D175" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="n"/>
+      <c r="F175" s="5" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
@@ -12319,6 +13833,13 @@
       <c r="C176" s="6" t="n">
         <v>148</v>
       </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E176" s="5" t="n"/>
+      <c r="F176" s="5" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
@@ -12334,6 +13855,13 @@
       <c r="C177" s="6" t="n">
         <v>147</v>
       </c>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="n"/>
+      <c r="F177" s="5" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
@@ -12349,6 +13877,13 @@
       <c r="C178" s="6" t="n">
         <v>147</v>
       </c>
+      <c r="D178" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E178" s="5" t="n"/>
+      <c r="F178" s="5" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
@@ -12364,6 +13899,13 @@
       <c r="C179" s="6" t="n">
         <v>145</v>
       </c>
+      <c r="D179" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="n"/>
+      <c r="F179" s="5" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
@@ -12379,6 +13921,13 @@
       <c r="C180" s="6" t="n">
         <v>145</v>
       </c>
+      <c r="D180" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E180" s="5" t="n"/>
+      <c r="F180" s="5" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
@@ -12394,6 +13943,13 @@
       <c r="C181" s="6" t="n">
         <v>141</v>
       </c>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="n"/>
+      <c r="F181" s="5" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
@@ -12409,6 +13965,13 @@
       <c r="C182" s="6" t="n">
         <v>139</v>
       </c>
+      <c r="D182" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="n"/>
+      <c r="F182" s="5" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
@@ -12424,6 +13987,13 @@
       <c r="C183" s="6" t="n">
         <v>138</v>
       </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E183" s="5" t="n"/>
+      <c r="F183" s="5" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
@@ -12439,6 +14009,13 @@
       <c r="C184" s="6" t="n">
         <v>138</v>
       </c>
+      <c r="D184" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E184" s="5" t="n"/>
+      <c r="F184" s="5" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
@@ -12454,6 +14031,19 @@
       <c r="C185" s="6" t="n">
         <v>136</v>
       </c>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
@@ -12469,6 +14059,13 @@
       <c r="C186" s="6" t="n">
         <v>134</v>
       </c>
+      <c r="D186" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E186" s="5" t="n"/>
+      <c r="F186" s="5" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
@@ -12484,6 +14081,13 @@
       <c r="C187" s="6" t="n">
         <v>133</v>
       </c>
+      <c r="D187" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E187" s="5" t="n"/>
+      <c r="F187" s="5" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
@@ -12499,6 +14103,13 @@
       <c r="C188" s="6" t="n">
         <v>130</v>
       </c>
+      <c r="D188" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E188" s="5" t="n"/>
+      <c r="F188" s="5" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
@@ -12514,6 +14125,13 @@
       <c r="C189" s="6" t="n">
         <v>129</v>
       </c>
+      <c r="D189" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="n"/>
+      <c r="F189" s="5" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
@@ -12529,6 +14147,13 @@
       <c r="C190" s="6" t="n">
         <v>127</v>
       </c>
+      <c r="D190" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E190" s="5" t="n"/>
+      <c r="F190" s="5" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
@@ -12544,6 +14169,13 @@
       <c r="C191" s="6" t="n">
         <v>127</v>
       </c>
+      <c r="D191" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="n"/>
+      <c r="F191" s="5" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
@@ -12559,6 +14191,13 @@
       <c r="C192" s="6" t="n">
         <v>127</v>
       </c>
+      <c r="D192" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E192" s="5" t="n"/>
+      <c r="F192" s="5" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
@@ -12574,6 +14213,13 @@
       <c r="C193" s="6" t="n">
         <v>124</v>
       </c>
+      <c r="D193" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="n"/>
+      <c r="F193" s="5" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
@@ -12589,6 +14235,13 @@
       <c r="C194" s="6" t="n">
         <v>124</v>
       </c>
+      <c r="D194" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E194" s="5" t="n"/>
+      <c r="F194" s="5" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
@@ -12604,6 +14257,13 @@
       <c r="C195" s="6" t="n">
         <v>117</v>
       </c>
+      <c r="D195" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E195" s="5" t="n"/>
+      <c r="F195" s="5" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
@@ -12619,6 +14279,13 @@
       <c r="C196" s="6" t="n">
         <v>116</v>
       </c>
+      <c r="D196" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E196" s="5" t="n"/>
+      <c r="F196" s="5" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
@@ -12634,6 +14301,13 @@
       <c r="C197" s="6" t="n">
         <v>113</v>
       </c>
+      <c r="D197" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E197" s="5" t="n"/>
+      <c r="F197" s="5" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
@@ -12649,6 +14323,13 @@
       <c r="C198" s="6" t="n">
         <v>113</v>
       </c>
+      <c r="D198" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E198" s="5" t="n"/>
+      <c r="F198" s="5" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
@@ -12664,6 +14345,13 @@
       <c r="C199" s="6" t="n">
         <v>107</v>
       </c>
+      <c r="D199" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E199" s="5" t="n"/>
+      <c r="F199" s="5" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
@@ -12679,6 +14367,19 @@
       <c r="C200" s="6" t="n">
         <v>104</v>
       </c>
+      <c r="D200" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E200" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F200" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
@@ -12694,6 +14395,13 @@
       <c r="C201" s="6" t="n">
         <v>102</v>
       </c>
+      <c r="D201" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E201" s="5" t="n"/>
+      <c r="F201" s="5" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
@@ -12709,6 +14417,13 @@
       <c r="C202" s="6" t="n">
         <v>102</v>
       </c>
+      <c r="D202" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E202" s="5" t="n"/>
+      <c r="F202" s="5" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
@@ -12724,6 +14439,19 @@
       <c r="C203" s="6" t="n">
         <v>102</v>
       </c>
+      <c r="D203" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E203" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F203" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="5" t="inlineStr">
@@ -12739,6 +14467,13 @@
       <c r="C204" s="6" t="n">
         <v>101</v>
       </c>
+      <c r="D204" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E204" s="5" t="n"/>
+      <c r="F204" s="5" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="5" t="inlineStr">
@@ -12754,6 +14489,13 @@
       <c r="C205" s="6" t="n">
         <v>101</v>
       </c>
+      <c r="D205" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="n"/>
+      <c r="F205" s="5" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
@@ -12769,6 +14511,13 @@
       <c r="C206" s="6" t="n">
         <v>96</v>
       </c>
+      <c r="D206" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="n"/>
+      <c r="F206" s="5" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
@@ -12784,6 +14533,13 @@
       <c r="C207" s="6" t="n">
         <v>96</v>
       </c>
+      <c r="D207" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="n"/>
+      <c r="F207" s="5" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="5" t="inlineStr">
@@ -12799,6 +14555,13 @@
       <c r="C208" s="6" t="n">
         <v>93</v>
       </c>
+      <c r="D208" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E208" s="5" t="n"/>
+      <c r="F208" s="5" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
@@ -12814,6 +14577,13 @@
       <c r="C209" s="6" t="n">
         <v>92</v>
       </c>
+      <c r="D209" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E209" s="5" t="n"/>
+      <c r="F209" s="5" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
@@ -12829,6 +14599,13 @@
       <c r="C210" s="6" t="n">
         <v>91</v>
       </c>
+      <c r="D210" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="n"/>
+      <c r="F210" s="5" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
@@ -12844,6 +14621,13 @@
       <c r="C211" s="6" t="n">
         <v>90</v>
       </c>
+      <c r="D211" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E211" s="5" t="n"/>
+      <c r="F211" s="5" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="5" t="inlineStr">
@@ -12859,6 +14643,13 @@
       <c r="C212" s="6" t="n">
         <v>89</v>
       </c>
+      <c r="D212" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E212" s="5" t="n"/>
+      <c r="F212" s="5" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
@@ -12874,6 +14665,13 @@
       <c r="C213" s="6" t="n">
         <v>87</v>
       </c>
+      <c r="D213" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E213" s="5" t="n"/>
+      <c r="F213" s="5" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
@@ -12889,6 +14687,13 @@
       <c r="C214" s="6" t="n">
         <v>87</v>
       </c>
+      <c r="D214" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E214" s="5" t="n"/>
+      <c r="F214" s="5" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
@@ -12904,6 +14709,13 @@
       <c r="C215" s="6" t="n">
         <v>86</v>
       </c>
+      <c r="D215" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E215" s="5" t="n"/>
+      <c r="F215" s="5" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
@@ -12919,6 +14731,13 @@
       <c r="C216" s="6" t="n">
         <v>85</v>
       </c>
+      <c r="D216" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E216" s="5" t="n"/>
+      <c r="F216" s="5" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
@@ -12934,6 +14753,13 @@
       <c r="C217" s="6" t="n">
         <v>84</v>
       </c>
+      <c r="D217" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E217" s="5" t="n"/>
+      <c r="F217" s="5" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
@@ -12949,6 +14775,19 @@
       <c r="C218" s="6" t="n">
         <v>84</v>
       </c>
+      <c r="D218" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E218" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F218" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
@@ -12964,6 +14803,13 @@
       <c r="C219" s="6" t="n">
         <v>84</v>
       </c>
+      <c r="D219" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E219" s="5" t="n"/>
+      <c r="F219" s="5" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
@@ -12979,6 +14825,13 @@
       <c r="C220" s="6" t="n">
         <v>83</v>
       </c>
+      <c r="D220" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E220" s="5" t="n"/>
+      <c r="F220" s="5" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
@@ -12994,6 +14847,13 @@
       <c r="C221" s="6" t="n">
         <v>82</v>
       </c>
+      <c r="D221" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E221" s="5" t="n"/>
+      <c r="F221" s="5" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
@@ -13009,6 +14869,13 @@
       <c r="C222" s="6" t="n">
         <v>82</v>
       </c>
+      <c r="D222" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E222" s="5" t="n"/>
+      <c r="F222" s="5" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
@@ -13024,6 +14891,13 @@
       <c r="C223" s="6" t="n">
         <v>81</v>
       </c>
+      <c r="D223" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E223" s="5" t="n"/>
+      <c r="F223" s="5" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
@@ -13039,6 +14913,13 @@
       <c r="C224" s="6" t="n">
         <v>80</v>
       </c>
+      <c r="D224" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E224" s="5" t="n"/>
+      <c r="F224" s="5" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="5" t="inlineStr">
@@ -13054,6 +14935,13 @@
       <c r="C225" s="6" t="n">
         <v>79</v>
       </c>
+      <c r="D225" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E225" s="5" t="n"/>
+      <c r="F225" s="5" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="5" t="inlineStr">
@@ -13069,6 +14957,13 @@
       <c r="C226" s="6" t="n">
         <v>79</v>
       </c>
+      <c r="D226" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E226" s="5" t="n"/>
+      <c r="F226" s="5" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
@@ -13084,6 +14979,13 @@
       <c r="C227" s="6" t="n">
         <v>77</v>
       </c>
+      <c r="D227" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E227" s="5" t="n"/>
+      <c r="F227" s="5" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="5" t="inlineStr">
@@ -13099,6 +15001,13 @@
       <c r="C228" s="6" t="n">
         <v>76</v>
       </c>
+      <c r="D228" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E228" s="5" t="n"/>
+      <c r="F228" s="5" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
@@ -13114,6 +15023,13 @@
       <c r="C229" s="6" t="n">
         <v>76</v>
       </c>
+      <c r="D229" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E229" s="5" t="n"/>
+      <c r="F229" s="5" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
@@ -13129,6 +15045,13 @@
       <c r="C230" s="6" t="n">
         <v>71</v>
       </c>
+      <c r="D230" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E230" s="5" t="n"/>
+      <c r="F230" s="5" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
@@ -13144,6 +15067,19 @@
       <c r="C231" s="6" t="n">
         <v>69</v>
       </c>
+      <c r="D231" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E231" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F231" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
@@ -13159,6 +15095,13 @@
       <c r="C232" s="6" t="n">
         <v>68</v>
       </c>
+      <c r="D232" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E232" s="5" t="n"/>
+      <c r="F232" s="5" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
@@ -13174,6 +15117,13 @@
       <c r="C233" s="6" t="n">
         <v>66</v>
       </c>
+      <c r="D233" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E233" s="5" t="n"/>
+      <c r="F233" s="5" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="5" t="inlineStr">
@@ -13189,6 +15139,13 @@
       <c r="C234" s="6" t="n">
         <v>65</v>
       </c>
+      <c r="D234" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E234" s="5" t="n"/>
+      <c r="F234" s="5" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="5" t="inlineStr">
@@ -13204,6 +15161,13 @@
       <c r="C235" s="6" t="n">
         <v>64</v>
       </c>
+      <c r="D235" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E235" s="5" t="n"/>
+      <c r="F235" s="5" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
@@ -13219,6 +15183,13 @@
       <c r="C236" s="6" t="n">
         <v>63</v>
       </c>
+      <c r="D236" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E236" s="5" t="n"/>
+      <c r="F236" s="5" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="5" t="inlineStr">
@@ -13234,6 +15205,13 @@
       <c r="C237" s="6" t="n">
         <v>63</v>
       </c>
+      <c r="D237" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E237" s="5" t="n"/>
+      <c r="F237" s="5" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="5" t="inlineStr">
@@ -13249,6 +15227,13 @@
       <c r="C238" s="6" t="n">
         <v>62</v>
       </c>
+      <c r="D238" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E238" s="5" t="n"/>
+      <c r="F238" s="5" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="5" t="inlineStr">
@@ -13264,6 +15249,13 @@
       <c r="C239" s="6" t="n">
         <v>62</v>
       </c>
+      <c r="D239" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E239" s="5" t="n"/>
+      <c r="F239" s="5" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="5" t="inlineStr">
@@ -13279,6 +15271,13 @@
       <c r="C240" s="6" t="n">
         <v>62</v>
       </c>
+      <c r="D240" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E240" s="5" t="n"/>
+      <c r="F240" s="5" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
@@ -13294,6 +15293,13 @@
       <c r="C241" s="6" t="n">
         <v>61</v>
       </c>
+      <c r="D241" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E241" s="5" t="n"/>
+      <c r="F241" s="5" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
@@ -13309,6 +15315,13 @@
       <c r="C242" s="6" t="n">
         <v>61</v>
       </c>
+      <c r="D242" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E242" s="5" t="n"/>
+      <c r="F242" s="5" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
@@ -13324,6 +15337,13 @@
       <c r="C243" s="6" t="n">
         <v>61</v>
       </c>
+      <c r="D243" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E243" s="5" t="n"/>
+      <c r="F243" s="5" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="5" t="inlineStr">
@@ -13339,6 +15359,13 @@
       <c r="C244" s="6" t="n">
         <v>60</v>
       </c>
+      <c r="D244" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E244" s="5" t="n"/>
+      <c r="F244" s="5" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="5" t="inlineStr">
@@ -13354,6 +15381,13 @@
       <c r="C245" s="6" t="n">
         <v>58</v>
       </c>
+      <c r="D245" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E245" s="5" t="n"/>
+      <c r="F245" s="5" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="5" t="inlineStr">
@@ -13369,6 +15403,13 @@
       <c r="C246" s="6" t="n">
         <v>56</v>
       </c>
+      <c r="D246" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E246" s="5" t="n"/>
+      <c r="F246" s="5" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
@@ -13384,6 +15425,13 @@
       <c r="C247" s="6" t="n">
         <v>56</v>
       </c>
+      <c r="D247" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E247" s="5" t="n"/>
+      <c r="F247" s="5" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="5" t="inlineStr">
@@ -13399,6 +15447,13 @@
       <c r="C248" s="6" t="n">
         <v>55</v>
       </c>
+      <c r="D248" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E248" s="5" t="n"/>
+      <c r="F248" s="5" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
@@ -13414,6 +15469,13 @@
       <c r="C249" s="6" t="n">
         <v>53</v>
       </c>
+      <c r="D249" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E249" s="5" t="n"/>
+      <c r="F249" s="5" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="5" t="inlineStr">
@@ -13429,6 +15491,13 @@
       <c r="C250" s="6" t="n">
         <v>52</v>
       </c>
+      <c r="D250" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E250" s="5" t="n"/>
+      <c r="F250" s="5" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="5" t="inlineStr">
@@ -13444,6 +15513,13 @@
       <c r="C251" s="6" t="n">
         <v>52</v>
       </c>
+      <c r="D251" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E251" s="5" t="n"/>
+      <c r="F251" s="5" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="5" t="inlineStr">
@@ -13459,6 +15535,13 @@
       <c r="C252" s="6" t="n">
         <v>52</v>
       </c>
+      <c r="D252" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E252" s="5" t="n"/>
+      <c r="F252" s="5" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
@@ -13474,6 +15557,13 @@
       <c r="C253" s="6" t="n">
         <v>51</v>
       </c>
+      <c r="D253" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E253" s="5" t="n"/>
+      <c r="F253" s="5" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
@@ -13489,6 +15579,13 @@
       <c r="C254" s="6" t="n">
         <v>50</v>
       </c>
+      <c r="D254" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E254" s="5" t="n"/>
+      <c r="F254" s="5" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
@@ -13504,6 +15601,13 @@
       <c r="C255" s="6" t="n">
         <v>50</v>
       </c>
+      <c r="D255" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E255" s="5" t="n"/>
+      <c r="F255" s="5" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
@@ -13519,6 +15623,13 @@
       <c r="C256" s="6" t="n">
         <v>49</v>
       </c>
+      <c r="D256" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E256" s="5" t="n"/>
+      <c r="F256" s="5" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
@@ -13534,6 +15645,13 @@
       <c r="C257" s="6" t="n">
         <v>49</v>
       </c>
+      <c r="D257" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E257" s="5" t="n"/>
+      <c r="F257" s="5" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
@@ -13549,6 +15667,13 @@
       <c r="C258" s="6" t="n">
         <v>49</v>
       </c>
+      <c r="D258" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E258" s="5" t="n"/>
+      <c r="F258" s="5" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
@@ -13564,6 +15689,13 @@
       <c r="C259" s="6" t="n">
         <v>48</v>
       </c>
+      <c r="D259" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E259" s="5" t="n"/>
+      <c r="F259" s="5" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
@@ -13579,6 +15711,13 @@
       <c r="C260" s="6" t="n">
         <v>48</v>
       </c>
+      <c r="D260" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E260" s="5" t="n"/>
+      <c r="F260" s="5" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
@@ -13594,6 +15733,19 @@
       <c r="C261" s="6" t="n">
         <v>46</v>
       </c>
+      <c r="D261" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E261" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F261" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
@@ -13609,6 +15761,13 @@
       <c r="C262" s="6" t="n">
         <v>44</v>
       </c>
+      <c r="D262" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E262" s="5" t="n"/>
+      <c r="F262" s="5" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="5" t="inlineStr">
@@ -13624,6 +15783,13 @@
       <c r="C263" s="6" t="n">
         <v>44</v>
       </c>
+      <c r="D263" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E263" s="5" t="n"/>
+      <c r="F263" s="5" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="5" t="inlineStr">
@@ -13639,6 +15805,19 @@
       <c r="C264" s="6" t="n">
         <v>44</v>
       </c>
+      <c r="D264" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E264" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F264" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="5" t="inlineStr">
@@ -13654,6 +15833,13 @@
       <c r="C265" s="6" t="n">
         <v>43</v>
       </c>
+      <c r="D265" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E265" s="5" t="n"/>
+      <c r="F265" s="5" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="5" t="inlineStr">
@@ -13669,6 +15855,13 @@
       <c r="C266" s="6" t="n">
         <v>43</v>
       </c>
+      <c r="D266" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E266" s="5" t="n"/>
+      <c r="F266" s="5" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
@@ -13684,6 +15877,13 @@
       <c r="C267" s="6" t="n">
         <v>43</v>
       </c>
+      <c r="D267" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E267" s="5" t="n"/>
+      <c r="F267" s="5" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="5" t="inlineStr">
@@ -13699,6 +15899,13 @@
       <c r="C268" s="6" t="n">
         <v>41</v>
       </c>
+      <c r="D268" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E268" s="5" t="n"/>
+      <c r="F268" s="5" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
@@ -13714,6 +15921,13 @@
       <c r="C269" s="6" t="n">
         <v>40</v>
       </c>
+      <c r="D269" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E269" s="5" t="n"/>
+      <c r="F269" s="5" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="5" t="inlineStr">
@@ -13729,6 +15943,13 @@
       <c r="C270" s="6" t="n">
         <v>40</v>
       </c>
+      <c r="D270" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E270" s="5" t="n"/>
+      <c r="F270" s="5" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
@@ -13744,6 +15965,13 @@
       <c r="C271" s="6" t="n">
         <v>40</v>
       </c>
+      <c r="D271" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E271" s="5" t="n"/>
+      <c r="F271" s="5" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
@@ -13759,6 +15987,13 @@
       <c r="C272" s="6" t="n">
         <v>40</v>
       </c>
+      <c r="D272" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E272" s="5" t="n"/>
+      <c r="F272" s="5" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
@@ -13774,6 +16009,13 @@
       <c r="C273" s="6" t="n">
         <v>37</v>
       </c>
+      <c r="D273" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E273" s="5" t="n"/>
+      <c r="F273" s="5" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
@@ -13789,6 +16031,13 @@
       <c r="C274" s="6" t="n">
         <v>36</v>
       </c>
+      <c r="D274" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E274" s="5" t="n"/>
+      <c r="F274" s="5" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
@@ -13804,6 +16053,13 @@
       <c r="C275" s="6" t="n">
         <v>35</v>
       </c>
+      <c r="D275" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E275" s="5" t="n"/>
+      <c r="F275" s="5" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="5" t="inlineStr">
@@ -13819,6 +16075,19 @@
       <c r="C276" s="6" t="n">
         <v>35</v>
       </c>
+      <c r="D276" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E276" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F276" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
@@ -13834,6 +16103,13 @@
       <c r="C277" s="6" t="n">
         <v>34</v>
       </c>
+      <c r="D277" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E277" s="5" t="n"/>
+      <c r="F277" s="5" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="5" t="inlineStr">
@@ -13849,6 +16125,13 @@
       <c r="C278" s="6" t="n">
         <v>34</v>
       </c>
+      <c r="D278" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E278" s="5" t="n"/>
+      <c r="F278" s="5" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
@@ -13864,6 +16147,13 @@
       <c r="C279" s="6" t="n">
         <v>34</v>
       </c>
+      <c r="D279" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E279" s="5" t="n"/>
+      <c r="F279" s="5" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
@@ -13879,6 +16169,13 @@
       <c r="C280" s="6" t="n">
         <v>33</v>
       </c>
+      <c r="D280" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E280" s="5" t="n"/>
+      <c r="F280" s="5" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
@@ -13894,6 +16191,13 @@
       <c r="C281" s="6" t="n">
         <v>32</v>
       </c>
+      <c r="D281" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E281" s="5" t="n"/>
+      <c r="F281" s="5" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
@@ -13909,6 +16213,13 @@
       <c r="C282" s="6" t="n">
         <v>32</v>
       </c>
+      <c r="D282" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E282" s="5" t="n"/>
+      <c r="F282" s="5" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
@@ -13924,6 +16235,13 @@
       <c r="C283" s="6" t="n">
         <v>31</v>
       </c>
+      <c r="D283" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E283" s="5" t="n"/>
+      <c r="F283" s="5" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
@@ -13939,6 +16257,13 @@
       <c r="C284" s="6" t="n">
         <v>31</v>
       </c>
+      <c r="D284" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E284" s="5" t="n"/>
+      <c r="F284" s="5" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
@@ -13954,6 +16279,13 @@
       <c r="C285" s="6" t="n">
         <v>30</v>
       </c>
+      <c r="D285" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E285" s="5" t="n"/>
+      <c r="F285" s="5" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
@@ -13969,6 +16301,13 @@
       <c r="C286" s="6" t="n">
         <v>30</v>
       </c>
+      <c r="D286" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E286" s="5" t="n"/>
+      <c r="F286" s="5" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
@@ -13984,6 +16323,13 @@
       <c r="C287" s="6" t="n">
         <v>29</v>
       </c>
+      <c r="D287" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E287" s="5" t="n"/>
+      <c r="F287" s="5" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
@@ -13999,6 +16345,13 @@
       <c r="C288" s="6" t="n">
         <v>29</v>
       </c>
+      <c r="D288" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E288" s="5" t="n"/>
+      <c r="F288" s="5" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
@@ -14014,6 +16367,13 @@
       <c r="C289" s="6" t="n">
         <v>28</v>
       </c>
+      <c r="D289" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E289" s="5" t="n"/>
+      <c r="F289" s="5" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
@@ -14029,6 +16389,13 @@
       <c r="C290" s="6" t="n">
         <v>28</v>
       </c>
+      <c r="D290" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E290" s="5" t="n"/>
+      <c r="F290" s="5" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="5" t="inlineStr">
@@ -14044,6 +16411,13 @@
       <c r="C291" s="6" t="n">
         <v>26</v>
       </c>
+      <c r="D291" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E291" s="5" t="n"/>
+      <c r="F291" s="5" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
@@ -14059,6 +16433,13 @@
       <c r="C292" s="6" t="n">
         <v>26</v>
       </c>
+      <c r="D292" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E292" s="5" t="n"/>
+      <c r="F292" s="5" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
@@ -14074,6 +16455,13 @@
       <c r="C293" s="6" t="n">
         <v>26</v>
       </c>
+      <c r="D293" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E293" s="5" t="n"/>
+      <c r="F293" s="5" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
@@ -14089,6 +16477,13 @@
       <c r="C294" s="6" t="n">
         <v>25</v>
       </c>
+      <c r="D294" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E294" s="5" t="n"/>
+      <c r="F294" s="5" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
@@ -14104,6 +16499,13 @@
       <c r="C295" s="6" t="n">
         <v>25</v>
       </c>
+      <c r="D295" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E295" s="5" t="n"/>
+      <c r="F295" s="5" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
@@ -14119,6 +16521,13 @@
       <c r="C296" s="6" t="n">
         <v>25</v>
       </c>
+      <c r="D296" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E296" s="5" t="n"/>
+      <c r="F296" s="5" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
@@ -14134,6 +16543,13 @@
       <c r="C297" s="6" t="n">
         <v>25</v>
       </c>
+      <c r="D297" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E297" s="5" t="n"/>
+      <c r="F297" s="5" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="5" t="inlineStr">
@@ -14149,6 +16565,13 @@
       <c r="C298" s="6" t="n">
         <v>24</v>
       </c>
+      <c r="D298" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E298" s="5" t="n"/>
+      <c r="F298" s="5" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="5" t="inlineStr">
@@ -14164,6 +16587,13 @@
       <c r="C299" s="6" t="n">
         <v>24</v>
       </c>
+      <c r="D299" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E299" s="5" t="n"/>
+      <c r="F299" s="5" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="5" t="inlineStr">
@@ -14179,6 +16609,13 @@
       <c r="C300" s="6" t="n">
         <v>24</v>
       </c>
+      <c r="D300" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E300" s="5" t="n"/>
+      <c r="F300" s="5" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
@@ -14194,6 +16631,13 @@
       <c r="C301" s="6" t="n">
         <v>24</v>
       </c>
+      <c r="D301" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E301" s="5" t="n"/>
+      <c r="F301" s="5" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="5" t="inlineStr">
@@ -14209,6 +16653,13 @@
       <c r="C302" s="6" t="n">
         <v>24</v>
       </c>
+      <c r="D302" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E302" s="5" t="n"/>
+      <c r="F302" s="5" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="5" t="inlineStr">
@@ -14224,6 +16675,13 @@
       <c r="C303" s="6" t="n">
         <v>24</v>
       </c>
+      <c r="D303" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E303" s="5" t="n"/>
+      <c r="F303" s="5" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="5" t="inlineStr">
@@ -14239,6 +16697,13 @@
       <c r="C304" s="6" t="n">
         <v>24</v>
       </c>
+      <c r="D304" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E304" s="5" t="n"/>
+      <c r="F304" s="5" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="5" t="inlineStr">
@@ -14254,6 +16719,13 @@
       <c r="C305" s="6" t="n">
         <v>23</v>
       </c>
+      <c r="D305" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E305" s="5" t="n"/>
+      <c r="F305" s="5" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="5" t="inlineStr">
@@ -14269,6 +16741,13 @@
       <c r="C306" s="6" t="n">
         <v>23</v>
       </c>
+      <c r="D306" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E306" s="5" t="n"/>
+      <c r="F306" s="5" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="5" t="inlineStr">
@@ -14284,6 +16763,13 @@
       <c r="C307" s="6" t="n">
         <v>22</v>
       </c>
+      <c r="D307" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E307" s="5" t="n"/>
+      <c r="F307" s="5" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="5" t="inlineStr">
@@ -14299,6 +16785,13 @@
       <c r="C308" s="6" t="n">
         <v>22</v>
       </c>
+      <c r="D308" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E308" s="5" t="n"/>
+      <c r="F308" s="5" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="5" t="inlineStr">
@@ -14314,6 +16807,13 @@
       <c r="C309" s="6" t="n">
         <v>22</v>
       </c>
+      <c r="D309" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E309" s="5" t="n"/>
+      <c r="F309" s="5" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="5" t="inlineStr">
@@ -14329,6 +16829,13 @@
       <c r="C310" s="6" t="n">
         <v>21</v>
       </c>
+      <c r="D310" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E310" s="5" t="n"/>
+      <c r="F310" s="5" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="5" t="inlineStr">
@@ -14344,6 +16851,13 @@
       <c r="C311" s="6" t="n">
         <v>21</v>
       </c>
+      <c r="D311" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E311" s="5" t="n"/>
+      <c r="F311" s="5" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="5" t="inlineStr">
@@ -14359,6 +16873,13 @@
       <c r="C312" s="6" t="n">
         <v>21</v>
       </c>
+      <c r="D312" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E312" s="5" t="n"/>
+      <c r="F312" s="5" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="5" t="inlineStr">
@@ -14374,6 +16895,13 @@
       <c r="C313" s="6" t="n">
         <v>21</v>
       </c>
+      <c r="D313" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E313" s="5" t="n"/>
+      <c r="F313" s="5" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="5" t="inlineStr">
@@ -14389,6 +16917,13 @@
       <c r="C314" s="6" t="n">
         <v>21</v>
       </c>
+      <c r="D314" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E314" s="5" t="n"/>
+      <c r="F314" s="5" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="5" t="inlineStr">
@@ -14404,6 +16939,13 @@
       <c r="C315" s="6" t="n">
         <v>21</v>
       </c>
+      <c r="D315" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E315" s="5" t="n"/>
+      <c r="F315" s="5" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="5" t="inlineStr">
@@ -14419,6 +16961,13 @@
       <c r="C316" s="6" t="n">
         <v>21</v>
       </c>
+      <c r="D316" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E316" s="5" t="n"/>
+      <c r="F316" s="5" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="5" t="inlineStr">
@@ -14434,6 +16983,13 @@
       <c r="C317" s="6" t="n">
         <v>21</v>
       </c>
+      <c r="D317" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E317" s="5" t="n"/>
+      <c r="F317" s="5" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="5" t="inlineStr">
@@ -14449,6 +17005,13 @@
       <c r="C318" s="6" t="n">
         <v>20</v>
       </c>
+      <c r="D318" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E318" s="5" t="n"/>
+      <c r="F318" s="5" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
@@ -14464,6 +17027,13 @@
       <c r="C319" s="6" t="n">
         <v>20</v>
       </c>
+      <c r="D319" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E319" s="5" t="n"/>
+      <c r="F319" s="5" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="5" t="inlineStr">
@@ -14479,6 +17049,13 @@
       <c r="C320" s="6" t="n">
         <v>19</v>
       </c>
+      <c r="D320" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E320" s="5" t="n"/>
+      <c r="F320" s="5" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="5" t="inlineStr">
@@ -14494,6 +17071,13 @@
       <c r="C321" s="6" t="n">
         <v>19</v>
       </c>
+      <c r="D321" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E321" s="5" t="n"/>
+      <c r="F321" s="5" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="5" t="inlineStr">
@@ -14509,6 +17093,13 @@
       <c r="C322" s="6" t="n">
         <v>19</v>
       </c>
+      <c r="D322" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E322" s="5" t="n"/>
+      <c r="F322" s="5" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="5" t="inlineStr">
@@ -14524,6 +17115,13 @@
       <c r="C323" s="6" t="n">
         <v>19</v>
       </c>
+      <c r="D323" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E323" s="5" t="n"/>
+      <c r="F323" s="5" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="5" t="inlineStr">
@@ -14539,6 +17137,13 @@
       <c r="C324" s="6" t="n">
         <v>18</v>
       </c>
+      <c r="D324" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E324" s="5" t="n"/>
+      <c r="F324" s="5" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="5" t="inlineStr">
@@ -14554,6 +17159,13 @@
       <c r="C325" s="6" t="n">
         <v>17</v>
       </c>
+      <c r="D325" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E325" s="5" t="n"/>
+      <c r="F325" s="5" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="5" t="inlineStr">
@@ -14569,6 +17181,13 @@
       <c r="C326" s="6" t="n">
         <v>16</v>
       </c>
+      <c r="D326" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E326" s="5" t="n"/>
+      <c r="F326" s="5" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="5" t="inlineStr">
@@ -14584,6 +17203,19 @@
       <c r="C327" s="6" t="n">
         <v>16</v>
       </c>
+      <c r="D327" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E327" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F327" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="5" t="inlineStr">
@@ -14599,6 +17231,13 @@
       <c r="C328" s="6" t="n">
         <v>16</v>
       </c>
+      <c r="D328" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E328" s="5" t="n"/>
+      <c r="F328" s="5" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="5" t="inlineStr">
@@ -14614,6 +17253,13 @@
       <c r="C329" s="6" t="n">
         <v>16</v>
       </c>
+      <c r="D329" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E329" s="5" t="n"/>
+      <c r="F329" s="5" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="5" t="inlineStr">
@@ -14629,6 +17275,13 @@
       <c r="C330" s="6" t="n">
         <v>16</v>
       </c>
+      <c r="D330" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E330" s="5" t="n"/>
+      <c r="F330" s="5" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="5" t="inlineStr">
@@ -14644,6 +17297,13 @@
       <c r="C331" s="6" t="n">
         <v>15</v>
       </c>
+      <c r="D331" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E331" s="5" t="n"/>
+      <c r="F331" s="5" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="5" t="inlineStr">
@@ -14659,6 +17319,13 @@
       <c r="C332" s="6" t="n">
         <v>15</v>
       </c>
+      <c r="D332" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E332" s="5" t="n"/>
+      <c r="F332" s="5" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="5" t="inlineStr">
@@ -14674,6 +17341,13 @@
       <c r="C333" s="6" t="n">
         <v>15</v>
       </c>
+      <c r="D333" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E333" s="5" t="n"/>
+      <c r="F333" s="5" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="5" t="inlineStr">
@@ -14689,6 +17363,13 @@
       <c r="C334" s="6" t="n">
         <v>14</v>
       </c>
+      <c r="D334" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E334" s="5" t="n"/>
+      <c r="F334" s="5" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="5" t="inlineStr">
@@ -14704,6 +17385,13 @@
       <c r="C335" s="6" t="n">
         <v>14</v>
       </c>
+      <c r="D335" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E335" s="5" t="n"/>
+      <c r="F335" s="5" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="5" t="inlineStr">
@@ -14719,6 +17407,13 @@
       <c r="C336" s="6" t="n">
         <v>14</v>
       </c>
+      <c r="D336" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E336" s="5" t="n"/>
+      <c r="F336" s="5" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="5" t="inlineStr">
@@ -14734,6 +17429,13 @@
       <c r="C337" s="6" t="n">
         <v>14</v>
       </c>
+      <c r="D337" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E337" s="5" t="n"/>
+      <c r="F337" s="5" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="5" t="inlineStr">
@@ -14749,6 +17451,13 @@
       <c r="C338" s="6" t="n">
         <v>14</v>
       </c>
+      <c r="D338" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E338" s="5" t="n"/>
+      <c r="F338" s="5" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="5" t="inlineStr">
@@ -14764,6 +17473,13 @@
       <c r="C339" s="6" t="n">
         <v>13</v>
       </c>
+      <c r="D339" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E339" s="5" t="n"/>
+      <c r="F339" s="5" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="5" t="inlineStr">
@@ -14779,6 +17495,13 @@
       <c r="C340" s="6" t="n">
         <v>13</v>
       </c>
+      <c r="D340" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E340" s="5" t="n"/>
+      <c r="F340" s="5" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="5" t="inlineStr">
@@ -14794,6 +17517,13 @@
       <c r="C341" s="6" t="n">
         <v>11</v>
       </c>
+      <c r="D341" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E341" s="5" t="n"/>
+      <c r="F341" s="5" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="5" t="inlineStr">
@@ -14809,6 +17539,13 @@
       <c r="C342" s="6" t="n">
         <v>11</v>
       </c>
+      <c r="D342" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E342" s="5" t="n"/>
+      <c r="F342" s="5" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="5" t="inlineStr">
@@ -14824,6 +17561,13 @@
       <c r="C343" s="6" t="n">
         <v>11</v>
       </c>
+      <c r="D343" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E343" s="5" t="n"/>
+      <c r="F343" s="5" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="5" t="inlineStr">
@@ -14839,6 +17583,13 @@
       <c r="C344" s="6" t="n">
         <v>11</v>
       </c>
+      <c r="D344" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E344" s="5" t="n"/>
+      <c r="F344" s="5" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="5" t="inlineStr">
@@ -14854,6 +17605,13 @@
       <c r="C345" s="6" t="n">
         <v>11</v>
       </c>
+      <c r="D345" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E345" s="5" t="n"/>
+      <c r="F345" s="5" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="5" t="inlineStr">
@@ -14869,6 +17627,13 @@
       <c r="C346" s="6" t="n">
         <v>10</v>
       </c>
+      <c r="D346" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E346" s="5" t="n"/>
+      <c r="F346" s="5" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="5" t="inlineStr">
@@ -14884,6 +17649,13 @@
       <c r="C347" s="6" t="n">
         <v>10</v>
       </c>
+      <c r="D347" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E347" s="5" t="n"/>
+      <c r="F347" s="5" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="5" t="inlineStr">
@@ -14899,6 +17671,13 @@
       <c r="C348" s="6" t="n">
         <v>10</v>
       </c>
+      <c r="D348" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E348" s="5" t="n"/>
+      <c r="F348" s="5" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="5" t="inlineStr">
@@ -14914,6 +17693,13 @@
       <c r="C349" s="6" t="n">
         <v>10</v>
       </c>
+      <c r="D349" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E349" s="5" t="n"/>
+      <c r="F349" s="5" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="5" t="inlineStr">
@@ -14929,6 +17715,13 @@
       <c r="C350" s="6" t="n">
         <v>9</v>
       </c>
+      <c r="D350" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E350" s="5" t="n"/>
+      <c r="F350" s="5" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="5" t="inlineStr">
@@ -14944,6 +17737,13 @@
       <c r="C351" s="6" t="n">
         <v>9</v>
       </c>
+      <c r="D351" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E351" s="5" t="n"/>
+      <c r="F351" s="5" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="5" t="inlineStr">
@@ -14959,6 +17759,13 @@
       <c r="C352" s="6" t="n">
         <v>8</v>
       </c>
+      <c r="D352" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E352" s="5" t="n"/>
+      <c r="F352" s="5" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="5" t="inlineStr">
@@ -14974,6 +17781,13 @@
       <c r="C353" s="6" t="n">
         <v>8</v>
       </c>
+      <c r="D353" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E353" s="5" t="n"/>
+      <c r="F353" s="5" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="5" t="inlineStr">
@@ -14989,6 +17803,13 @@
       <c r="C354" s="6" t="n">
         <v>8</v>
       </c>
+      <c r="D354" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E354" s="5" t="n"/>
+      <c r="F354" s="5" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="5" t="inlineStr">
@@ -15004,6 +17825,13 @@
       <c r="C355" s="6" t="n">
         <v>8</v>
       </c>
+      <c r="D355" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E355" s="5" t="n"/>
+      <c r="F355" s="5" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="5" t="inlineStr">
@@ -15019,6 +17847,13 @@
       <c r="C356" s="6" t="n">
         <v>8</v>
       </c>
+      <c r="D356" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E356" s="5" t="n"/>
+      <c r="F356" s="5" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="5" t="inlineStr">
@@ -15034,6 +17869,13 @@
       <c r="C357" s="6" t="n">
         <v>8</v>
       </c>
+      <c r="D357" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E357" s="5" t="n"/>
+      <c r="F357" s="5" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="5" t="inlineStr">
@@ -15049,6 +17891,13 @@
       <c r="C358" s="6" t="n">
         <v>7</v>
       </c>
+      <c r="D358" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E358" s="5" t="n"/>
+      <c r="F358" s="5" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="5" t="inlineStr">
@@ -15064,6 +17913,13 @@
       <c r="C359" s="6" t="n">
         <v>7</v>
       </c>
+      <c r="D359" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E359" s="5" t="n"/>
+      <c r="F359" s="5" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="5" t="inlineStr">
@@ -15079,6 +17935,13 @@
       <c r="C360" s="6" t="n">
         <v>7</v>
       </c>
+      <c r="D360" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E360" s="5" t="n"/>
+      <c r="F360" s="5" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="5" t="inlineStr">
@@ -15094,6 +17957,13 @@
       <c r="C361" s="6" t="n">
         <v>7</v>
       </c>
+      <c r="D361" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E361" s="5" t="n"/>
+      <c r="F361" s="5" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="5" t="inlineStr">
@@ -15109,6 +17979,13 @@
       <c r="C362" s="6" t="n">
         <v>7</v>
       </c>
+      <c r="D362" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E362" s="5" t="n"/>
+      <c r="F362" s="5" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="5" t="inlineStr">
@@ -15124,6 +18001,13 @@
       <c r="C363" s="6" t="n">
         <v>6</v>
       </c>
+      <c r="D363" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E363" s="5" t="n"/>
+      <c r="F363" s="5" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="5" t="inlineStr">
@@ -15139,6 +18023,13 @@
       <c r="C364" s="6" t="n">
         <v>6</v>
       </c>
+      <c r="D364" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E364" s="5" t="n"/>
+      <c r="F364" s="5" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="5" t="inlineStr">
@@ -15154,6 +18045,13 @@
       <c r="C365" s="6" t="n">
         <v>6</v>
       </c>
+      <c r="D365" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E365" s="5" t="n"/>
+      <c r="F365" s="5" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="5" t="inlineStr">
@@ -15169,6 +18067,13 @@
       <c r="C366" s="6" t="n">
         <v>6</v>
       </c>
+      <c r="D366" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E366" s="5" t="n"/>
+      <c r="F366" s="5" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="5" t="inlineStr">
@@ -15184,6 +18089,13 @@
       <c r="C367" s="6" t="n">
         <v>5</v>
       </c>
+      <c r="D367" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E367" s="5" t="n"/>
+      <c r="F367" s="5" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="5" t="inlineStr">
@@ -15199,6 +18111,13 @@
       <c r="C368" s="6" t="n">
         <v>5</v>
       </c>
+      <c r="D368" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E368" s="5" t="n"/>
+      <c r="F368" s="5" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="5" t="inlineStr">
@@ -15214,6 +18133,13 @@
       <c r="C369" s="6" t="n">
         <v>4</v>
       </c>
+      <c r="D369" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E369" s="5" t="n"/>
+      <c r="F369" s="5" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="5" t="inlineStr">
@@ -15229,6 +18155,13 @@
       <c r="C370" s="6" t="n">
         <v>4</v>
       </c>
+      <c r="D370" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E370" s="5" t="n"/>
+      <c r="F370" s="5" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="5" t="inlineStr">
@@ -15244,6 +18177,13 @@
       <c r="C371" s="6" t="n">
         <v>3</v>
       </c>
+      <c r="D371" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E371" s="5" t="n"/>
+      <c r="F371" s="5" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="5" t="inlineStr">
@@ -15259,6 +18199,13 @@
       <c r="C372" s="6" t="n">
         <v>3</v>
       </c>
+      <c r="D372" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E372" s="5" t="n"/>
+      <c r="F372" s="5" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="5" t="inlineStr">
@@ -15274,6 +18221,13 @@
       <c r="C373" s="6" t="n">
         <v>2</v>
       </c>
+      <c r="D373" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E373" s="5" t="n"/>
+      <c r="F373" s="5" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="5" t="inlineStr">
@@ -15289,6 +18243,13 @@
       <c r="C374" s="6" t="n">
         <v>2</v>
       </c>
+      <c r="D374" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E374" s="5" t="n"/>
+      <c r="F374" s="5" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="5" t="inlineStr">
@@ -15304,6 +18265,13 @@
       <c r="C375" s="6" t="n">
         <v>2</v>
       </c>
+      <c r="D375" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E375" s="5" t="n"/>
+      <c r="F375" s="5" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="5" t="inlineStr">
@@ -15319,6 +18287,13 @@
       <c r="C376" s="6" t="n">
         <v>2</v>
       </c>
+      <c r="D376" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E376" s="5" t="n"/>
+      <c r="F376" s="5" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="5" t="inlineStr">
@@ -15334,6 +18309,13 @@
       <c r="C377" s="6" t="n">
         <v>2</v>
       </c>
+      <c r="D377" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E377" s="5" t="n"/>
+      <c r="F377" s="5" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="5" t="inlineStr">
@@ -15349,6 +18331,13 @@
       <c r="C378" s="6" t="n">
         <v>2</v>
       </c>
+      <c r="D378" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E378" s="5" t="n"/>
+      <c r="F378" s="5" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="5" t="inlineStr">
@@ -15364,6 +18353,13 @@
       <c r="C379" s="6" t="n">
         <v>2</v>
       </c>
+      <c r="D379" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E379" s="5" t="n"/>
+      <c r="F379" s="5" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="5" t="inlineStr">
@@ -15379,6 +18375,13 @@
       <c r="C380" s="6" t="n">
         <v>2</v>
       </c>
+      <c r="D380" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E380" s="5" t="n"/>
+      <c r="F380" s="5" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="5" t="inlineStr">
@@ -15394,6 +18397,13 @@
       <c r="C381" s="6" t="n">
         <v>2</v>
       </c>
+      <c r="D381" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E381" s="5" t="n"/>
+      <c r="F381" s="5" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="5" t="inlineStr">
@@ -15409,6 +18419,13 @@
       <c r="C382" s="6" t="n">
         <v>2</v>
       </c>
+      <c r="D382" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E382" s="5" t="n"/>
+      <c r="F382" s="5" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="5" t="inlineStr">
@@ -15424,6 +18441,13 @@
       <c r="C383" s="6" t="n">
         <v>2</v>
       </c>
+      <c r="D383" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E383" s="5" t="n"/>
+      <c r="F383" s="5" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="5" t="inlineStr">
@@ -15439,6 +18463,13 @@
       <c r="C384" s="6" t="n">
         <v>2</v>
       </c>
+      <c r="D384" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E384" s="5" t="n"/>
+      <c r="F384" s="5" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="5" t="inlineStr">
@@ -15454,6 +18485,13 @@
       <c r="C385" s="6" t="n">
         <v>2</v>
       </c>
+      <c r="D385" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E385" s="5" t="n"/>
+      <c r="F385" s="5" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="5" t="inlineStr">
@@ -15469,6 +18507,13 @@
       <c r="C386" s="6" t="n">
         <v>2</v>
       </c>
+      <c r="D386" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E386" s="5" t="n"/>
+      <c r="F386" s="5" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="5" t="inlineStr">
@@ -15484,6 +18529,13 @@
       <c r="C387" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="D387" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E387" s="5" t="n"/>
+      <c r="F387" s="5" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="5" t="inlineStr">
@@ -15499,6 +18551,13 @@
       <c r="C388" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="D388" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E388" s="5" t="n"/>
+      <c r="F388" s="5" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="5" t="inlineStr">
@@ -15514,6 +18573,13 @@
       <c r="C389" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="D389" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E389" s="5" t="n"/>
+      <c r="F389" s="5" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="5" t="inlineStr">
@@ -15529,6 +18595,13 @@
       <c r="C390" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="D390" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E390" s="5" t="n"/>
+      <c r="F390" s="5" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="5" t="inlineStr">
@@ -15544,6 +18617,13 @@
       <c r="C391" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="D391" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E391" s="5" t="n"/>
+      <c r="F391" s="5" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="5" t="inlineStr">
@@ -15559,6 +18639,13 @@
       <c r="C392" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="D392" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E392" s="5" t="n"/>
+      <c r="F392" s="5" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="5" t="inlineStr">
@@ -15574,6 +18661,13 @@
       <c r="C393" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="D393" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E393" s="5" t="n"/>
+      <c r="F393" s="5" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="5" t="inlineStr">
@@ -15589,6 +18683,13 @@
       <c r="C394" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="D394" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E394" s="5" t="n"/>
+      <c r="F394" s="5" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="5" t="inlineStr">
@@ -15604,6 +18705,13 @@
       <c r="C395" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="D395" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E395" s="5" t="n"/>
+      <c r="F395" s="5" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="5" t="inlineStr">
@@ -15619,6 +18727,13 @@
       <c r="C396" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="D396" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E396" s="5" t="n"/>
+      <c r="F396" s="5" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="5" t="inlineStr">
@@ -15634,6 +18749,13 @@
       <c r="C397" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="D397" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E397" s="5" t="n"/>
+      <c r="F397" s="5" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="5" t="inlineStr">
@@ -15649,6 +18771,13 @@
       <c r="C398" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="D398" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E398" s="5" t="n"/>
+      <c r="F398" s="5" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="5" t="inlineStr">
@@ -15664,6 +18793,13 @@
       <c r="C399" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="D399" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E399" s="5" t="n"/>
+      <c r="F399" s="5" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="5" t="inlineStr">
@@ -15679,6 +18815,13 @@
       <c r="C400" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="D400" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E400" s="5" t="n"/>
+      <c r="F400" s="5" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="5" t="inlineStr">
@@ -15694,6 +18837,13 @@
       <c r="C401" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="D401" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E401" s="5" t="n"/>
+      <c r="F401" s="5" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="5" t="inlineStr">
@@ -15709,6 +18859,13 @@
       <c r="C402" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="D402" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E402" s="5" t="n"/>
+      <c r="F402" s="5" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="5" t="inlineStr">
@@ -15724,6 +18881,13 @@
       <c r="C403" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="D403" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E403" s="5" t="n"/>
+      <c r="F403" s="5" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="5" t="inlineStr">
@@ -15739,6 +18903,13 @@
       <c r="C404" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="D404" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E404" s="5" t="n"/>
+      <c r="F404" s="5" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="5" t="inlineStr">
@@ -15754,11 +18925,18 @@
       <c r="C405" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="D405" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E405" s="5" t="n"/>
+      <c r="F405" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/inventory_analysis/Project_Bob_Sell_Down_Priority_11092026.xlsx
+++ b/data/inventory_analysis/Project_Bob_Sell_Down_Priority_11092026.xlsx
@@ -11,6 +11,7 @@
     <sheet name="2. Sell-Down Priority" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="3. Pending Review" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="4. Not on FW27 Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5. Possible FW27 Renames" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18940,4 +18941,526 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Heuristic Rename Candidates (REG-INV-013) — Needs Human Confirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>For the 54 franchises on Sheet 4 that were still Active in SS27: does an FW27 style of the same gender + Business Area share a distinctive family word (e.g. "Rosson", "Korp") with this SS27 style? HIGH = same family word AND same last word (garment type). MEDIUM = 2+ shared distinctive words, different garment type. LOW = exactly one shared distinctive word, different garment type. This is a candidate list to check, not a resolved mapping -- REG-INV-012 stays Open regardless of confidence shown here. Rows with no candidate are omitted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Base (SS27)</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Units in Stock</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Candidate FW27 Name(s)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Shared Word(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Magma Mid Hood</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Men</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>2262</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Magma Rugged Prototype Pant; Magma Rugged Pant</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>magma; magma</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Magma Mid Hood</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1948</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Magma Rugged Pant</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>magma</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Korp Lite Shorts</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Men</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>1733</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Korp Lite Pant AF; Korp Softshell Hood; Korp Mid Halfzip</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>korp; korp; korp</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Korp Lite Pant</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Men</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>1571</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Korp Proof Pant; Korp Softshell Pant</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>korp; korp</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Rosson Softshell Hood</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>1138</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Rosson Down Hood; Rosson Mid Hood</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>rosson; rosson</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Korp Lite Pant</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>1113</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Korp Proof Pant; Korp Softshell Pant</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>korp; korp</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Korp Lite Shorts</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>1036</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Korp Softshell Hood; Korp Mid Halfzip; Korp Mid Hood</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>korp; korp; korp</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Zircon Shorts</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>871</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Zircon Flex Pant; Zircon Proof Jacket; Zircon Slim Pant</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>zircon; zircon; zircon</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Rosson Softshell Hood</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Men</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>844</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Rosson Down Hood; Rosson Mid Hood</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>rosson; rosson</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Zircon Shorts</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Men</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>360</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Zircon Flex Pant; Zircon Proof Jacket; Zircon Slim Pant</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>zircon; zircon; zircon</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>ROC Lite Slim Pant</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>184</v>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>ROC Sight Softshell Pant</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>roc</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Solis Zip Off Jacket</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Men</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>155</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Solis Zip Off Pant</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>solis</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Solis Zip Off Jacket</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>136</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Solis Zip Off Pant</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>solis</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>ROC Lite Slim Pant</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Men</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>ROC Sight Softshell Pant</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>roc</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>L.I.M Sunpack Hoodie</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Men</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Sunpack Prototype Hoodie</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>sunpack</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/inventory_analysis/Project_Bob_Sell_Down_Priority_11092026.xlsx
+++ b/data/inventory_analysis/Project_Bob_Sell_Down_Priority_11092026.xlsx
@@ -12,6 +12,7 @@
     <sheet name="3. Pending Review" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="4. Not on FW27 Plan" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="5. Possible FW27 Renames" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6. Inventory Value Summary" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -73,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -85,6 +86,8 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -482,11 +485,19 @@
         </is>
       </c>
     </row>
+    <row r="9" ht="75" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Value estimate (REG-INV-014, Sheets 2-3 only -- 400,773 of 527,963 total units, 76%): 775,185,200 SEK at Target RRP, 370,741,160 SEK at WP, 145,752,246 SEK estimated landed cost (reconstructed -- see Sheet 2's own note and REG-INV-014). Sheet 4 (Not on FW27 Plan) has no price source anywhere in this data and is NOT included in these totals -- not zero, just unknown. See Sheet 6 for the breakdown by priority tier and by Activity.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -498,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G258"/>
+  <dimension ref="A1:J258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -508,6 +519,9 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -520,7 +534,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sorted by exit urgency (Sheet 1's tier order), then by units in stock, descending. "FW28+" rows are long-runway, low-urgency -- included for completeness, not action.</t>
+          <t>Sorted by exit urgency (Sheet 1's tier order), then by units in stock, descending. "FW28+" rows are long-runway, low-urgency -- included for completeness, not action. Value columns per REG-INV-014: Retail/Wholesale Value = units x the FW27 plan's own Target RRP/WP for that franchise; Est. Cost Value = units x Landed Cost RECONSTRUCTED as WP x (1-GM0%) since the plan's own Landed Cost field is broken (#ERROR!, REG-INV-011). One planned price per franchise applied uniformly across all sizes/colors in stock -- not a per-SKU actual. Target RRP is a planned price, not realized/discounted revenue -- read Retail Value as a ceiling, not expected recovery.</t>
         </is>
       </c>
     </row>
@@ -560,6 +574,21 @@
           <t>Active?</t>
         </is>
       </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Retail Value (RRP, SEK)</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Wholesale Value (WP, SEK)</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Est. Cost Value (SEK)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -593,6 +622,15 @@
       <c r="G6" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H6" s="6" t="n">
+        <v>15525000</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>7392850</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>3795148</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -626,6 +664,15 @@
       <c r="G7" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H7" s="6" t="n">
+        <v>8652000</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>4119996</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>1700868</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -659,6 +706,15 @@
       <c r="G8" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H8" s="6" t="n">
+        <v>6687000</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>3184283</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>1233239</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -692,6 +748,15 @@
       <c r="G9" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H9" s="6" t="n">
+        <v>820000</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>394236</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>131016</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -725,6 +790,15 @@
       <c r="G10" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H10" s="6" t="n">
+        <v>3449300</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>1642516</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>620002</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -758,6 +832,15 @@
       <c r="G11" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H11" s="6" t="n">
+        <v>9765000</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>4649995</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>2181931</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -791,6 +874,15 @@
       <c r="G12" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H12" s="6" t="n">
+        <v>3179000</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1513802</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>606572</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -824,6 +916,15 @@
       <c r="G13" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H13" s="6" t="n">
+        <v>1136200</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>541050</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>237387</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -857,6 +958,15 @@
       <c r="G14" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H14" s="6" t="n">
+        <v>810000</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>385714</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>157837</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -890,6 +1000,15 @@
       <c r="G15" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H15" s="6" t="n">
+        <v>765000</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>364285</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>162256</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -923,6 +1042,15 @@
       <c r="G16" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H16" s="6" t="n">
+        <v>787800</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>375144</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>177406</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -956,6 +1084,15 @@
       <c r="G17" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H17" s="6" t="n">
+        <v>1918000</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>913335</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>420080</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -989,6 +1126,15 @@
       <c r="G18" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H18" s="6" t="n">
+        <v>469800</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>223714</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>88359</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1022,6 +1168,15 @@
       <c r="G19" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H19" s="6" t="n">
+        <v>1676500</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>798335</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>335674</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1055,6 +1210,15 @@
       <c r="G20" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H20" s="6" t="n">
+        <v>288000</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>137142</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>55235</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1088,6 +1252,15 @@
       <c r="G21" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H21" s="6" t="n">
+        <v>199500</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>94999</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>24345</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -1121,6 +1294,15 @@
       <c r="G22" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H22" s="6" t="n">
+        <v>121500</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>57858</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>17790</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -1154,6 +1336,15 @@
       <c r="G23" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H23" s="6" t="n">
+        <v>102500</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>48810</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>14180</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -1187,6 +1378,15 @@
       <c r="G24" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H24" s="6" t="n">
+        <v>114800</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>54666</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>12669</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1220,6 +1420,15 @@
       <c r="G25" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H25" s="6" t="n">
+        <v>3738600</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>1780280</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>646155</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -1253,6 +1462,15 @@
       <c r="G26" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H26" s="6" t="n">
+        <v>3409200</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>1623423</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>533350</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -1286,6 +1504,15 @@
       <c r="G27" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H27" s="6" t="n">
+        <v>904800</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>430854</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>174174</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -1319,6 +1546,15 @@
       <c r="G28" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H28" s="6" t="n">
+        <v>6005000</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>2859521</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>1519745</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -1352,6 +1588,15 @@
       <c r="G29" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H29" s="6" t="n">
+        <v>7935000</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>3778573</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>1946688</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -1385,6 +1630,15 @@
       <c r="G30" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H30" s="6" t="n">
+        <v>4845000</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>2307141</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>1162955</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -1418,6 +1672,15 @@
       <c r="G31" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H31" s="6" t="n">
+        <v>4567500</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>2175001</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>1053473</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -1451,6 +1714,15 @@
       <c r="G32" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H32" s="6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>480768</v>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>204660</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -1484,6 +1756,15 @@
       <c r="G33" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H33" s="6" t="n">
+        <v>509600</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>242666</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>92361</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -1517,6 +1798,15 @@
       <c r="G34" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H34" s="6" t="n">
+        <v>434000</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>206666</v>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>80374</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -1550,6 +1840,15 @@
       <c r="G35" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H35" s="6" t="n">
+        <v>358400</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>170667</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>55774</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -1583,6 +1882,15 @@
       <c r="G36" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H36" s="6" t="n">
+        <v>51200</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>24381</v>
+      </c>
+      <c r="J36" s="6" t="n">
+        <v>8498</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -1616,6 +1924,15 @@
       <c r="G37" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H37" s="6" t="n">
+        <v>12338700</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>5932110</v>
+      </c>
+      <c r="J37" s="6" t="n">
+        <v>2468301</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -1649,6 +1966,15 @@
       <c r="G38" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H38" s="6" t="n">
+        <v>17333800</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>8333540</v>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>3259464</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -1682,6 +2008,15 @@
       <c r="G39" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H39" s="6" t="n">
+        <v>9183600</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>4415169</v>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v>1815521</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -1715,6 +2050,15 @@
       <c r="G40" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H40" s="6" t="n">
+        <v>6300900</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>3000419</v>
+      </c>
+      <c r="J40" s="6" t="n">
+        <v>947865</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -1748,6 +2092,15 @@
       <c r="G41" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H41" s="6" t="n">
+        <v>13706000</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>6526660</v>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v>2250525</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -1781,6 +2134,15 @@
       <c r="G42" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H42" s="6" t="n">
+        <v>13202000</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>6286660</v>
+      </c>
+      <c r="J42" s="6" t="n">
+        <v>2039841</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -1814,6 +2176,15 @@
       <c r="G43" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H43" s="6" t="n">
+        <v>5720400</v>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v>2723991</v>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>909544</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -1847,6 +2218,15 @@
       <c r="G44" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H44" s="6" t="n">
+        <v>6033500</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>2900742</v>
+      </c>
+      <c r="J44" s="6" t="n">
+        <v>1259904</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -1880,6 +2260,15 @@
       <c r="G45" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H45" s="6" t="n">
+        <v>9316000</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>4436170</v>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>1664276</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -1913,6 +2302,15 @@
       <c r="G46" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H46" s="6" t="n">
+        <v>2408850</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>1158122</v>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>523309</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -1946,6 +2344,15 @@
       <c r="G47" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H47" s="6" t="n">
+        <v>6516900</v>
+      </c>
+      <c r="I47" s="6" t="n">
+        <v>3133125</v>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v>1528614</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -1979,6 +2386,15 @@
       <c r="G48" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H48" s="6" t="n">
+        <v>6930000</v>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v>3300016</v>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>1200424</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -2012,6 +2428,15 @@
       <c r="G49" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H49" s="6" t="n">
+        <v>6648600</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>3196457</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>1312481</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -2045,6 +2470,15 @@
       <c r="G50" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H50" s="6" t="n">
+        <v>5680800</v>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>2731139</v>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>1171144</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -2078,6 +2512,15 @@
       <c r="G51" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H51" s="6" t="n">
+        <v>6300000</v>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v>3000015</v>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>1001160</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -2111,6 +2554,15 @@
       <c r="G52" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H52" s="6" t="n">
+        <v>14312100</v>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>6815292</v>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>2854874</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -2144,6 +2596,15 @@
       <c r="G53" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H53" s="6" t="n">
+        <v>7359300</v>
+      </c>
+      <c r="I53" s="6" t="n">
+        <v>3504412</v>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>1209436</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -2177,6 +2638,15 @@
       <c r="G54" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H54" s="6" t="n">
+        <v>1652400</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>786873</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>287352</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -2210,6 +2680,15 @@
       <c r="G55" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H55" s="6" t="n">
+        <v>1436750</v>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>690748</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>328687</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -2243,6 +2722,15 @@
       <c r="G56" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H56" s="6" t="n">
+        <v>18445500</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>8783583</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>4148926</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -2276,6 +2764,15 @@
       <c r="G57" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H57" s="6" t="n">
+        <v>18049500</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>8595011</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>3616318</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -2309,6 +2806,15 @@
       <c r="G58" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H58" s="6" t="n">
+        <v>1191000</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>567154</v>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>247291</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -2342,6 +2848,15 @@
       <c r="G59" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H59" s="6" t="n">
+        <v>9372500</v>
+      </c>
+      <c r="I59" s="6" t="n">
+        <v>4463110</v>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>1971787</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -2375,6 +2890,15 @@
       <c r="G60" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H60" s="6" t="n">
+        <v>3681000</v>
+      </c>
+      <c r="I60" s="6" t="n">
+        <v>1769714</v>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>779673</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -2408,6 +2932,15 @@
       <c r="G61" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H61" s="6" t="n">
+        <v>10830000</v>
+      </c>
+      <c r="I61" s="6" t="n">
+        <v>5157138</v>
+      </c>
+      <c r="J61" s="6" t="n">
+        <v>1953371</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -2441,6 +2974,15 @@
       <c r="G62" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H62" s="6" t="n">
+        <v>10746000</v>
+      </c>
+      <c r="I62" s="6" t="n">
+        <v>5117138</v>
+      </c>
+      <c r="J62" s="6" t="n">
+        <v>2062587</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -2474,6 +3016,15 @@
       <c r="G63" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H63" s="6" t="n">
+        <v>8402500</v>
+      </c>
+      <c r="I63" s="6" t="n">
+        <v>4039653</v>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>1576141</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -2507,6 +3058,15 @@
       <c r="G64" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H64" s="6" t="n">
+        <v>11018700</v>
+      </c>
+      <c r="I64" s="6" t="n">
+        <v>5247005</v>
+      </c>
+      <c r="J64" s="6" t="n">
+        <v>2088912</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -2540,6 +3100,15 @@
       <c r="G65" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H65" s="6" t="n">
+        <v>8325000</v>
+      </c>
+      <c r="I65" s="6" t="n">
+        <v>4002394</v>
+      </c>
+      <c r="J65" s="6" t="n">
+        <v>1561604</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -2573,6 +3142,15 @@
       <c r="G66" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H66" s="6" t="n">
+        <v>5613400</v>
+      </c>
+      <c r="I66" s="6" t="n">
+        <v>2673035</v>
+      </c>
+      <c r="J66" s="6" t="n">
+        <v>974916</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -2606,6 +3184,15 @@
       <c r="G67" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H67" s="6" t="n">
+        <v>7262200</v>
+      </c>
+      <c r="I67" s="6" t="n">
+        <v>3491435</v>
+      </c>
+      <c r="J67" s="6" t="n">
+        <v>1361729</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -2639,6 +3226,15 @@
       <c r="G68" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H68" s="6" t="n">
+        <v>7240200</v>
+      </c>
+      <c r="I68" s="6" t="n">
+        <v>3447717</v>
+      </c>
+      <c r="J68" s="6" t="n">
+        <v>890610</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -2672,6 +3268,15 @@
       <c r="G69" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H69" s="6" t="n">
+        <v>11280500</v>
+      </c>
+      <c r="I69" s="6" t="n">
+        <v>5371677</v>
+      </c>
+      <c r="J69" s="6" t="n">
+        <v>2247076</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -2705,6 +3310,15 @@
       <c r="G70" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H70" s="6" t="n">
+        <v>5351600</v>
+      </c>
+      <c r="I70" s="6" t="n">
+        <v>2548369</v>
+      </c>
+      <c r="J70" s="6" t="n">
+        <v>842090</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -2738,6 +3352,15 @@
       <c r="G71" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H71" s="6" t="n">
+        <v>6901400</v>
+      </c>
+      <c r="I71" s="6" t="n">
+        <v>3286384</v>
+      </c>
+      <c r="J71" s="6" t="n">
+        <v>900194</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -2771,6 +3394,15 @@
       <c r="G72" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H72" s="6" t="n">
+        <v>3112000</v>
+      </c>
+      <c r="I72" s="6" t="n">
+        <v>1496156</v>
+      </c>
+      <c r="J72" s="6" t="n">
+        <v>593054</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -2804,6 +3436,15 @@
       <c r="G73" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H73" s="6" t="n">
+        <v>11643200</v>
+      </c>
+      <c r="I73" s="6" t="n">
+        <v>5544369</v>
+      </c>
+      <c r="J73" s="6" t="n">
+        <v>2147711</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -2837,6 +3478,15 @@
       <c r="G74" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H74" s="6" t="n">
+        <v>2943000</v>
+      </c>
+      <c r="I74" s="6" t="n">
+        <v>1401427</v>
+      </c>
+      <c r="J74" s="6" t="n">
+        <v>482593</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -2870,6 +3520,15 @@
       <c r="G75" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H75" s="6" t="n">
+        <v>1172800</v>
+      </c>
+      <c r="I75" s="6" t="n">
+        <v>558487</v>
+      </c>
+      <c r="J75" s="6" t="n">
+        <v>195271</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -2903,6 +3562,15 @@
       <c r="G76" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H76" s="6" t="n">
+        <v>5864000</v>
+      </c>
+      <c r="I76" s="6" t="n">
+        <v>2792378</v>
+      </c>
+      <c r="J76" s="6" t="n">
+        <v>1180716</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -2936,6 +3604,15 @@
       <c r="G77" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H77" s="6" t="n">
+        <v>5808000</v>
+      </c>
+      <c r="I77" s="6" t="n">
+        <v>2765712</v>
+      </c>
+      <c r="J77" s="6" t="n">
+        <v>1146093</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -2969,6 +3646,15 @@
       <c r="G78" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H78" s="6" t="n">
+        <v>8151000</v>
+      </c>
+      <c r="I78" s="6" t="n">
+        <v>3881425</v>
+      </c>
+      <c r="J78" s="6" t="n">
+        <v>1326113</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -3002,6 +3688,15 @@
       <c r="G79" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H79" s="6" t="n">
+        <v>3043200</v>
+      </c>
+      <c r="I79" s="6" t="n">
+        <v>1449146</v>
+      </c>
+      <c r="J79" s="6" t="n">
+        <v>580389</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -3035,6 +3730,15 @@
       <c r="G80" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H80" s="6" t="n">
+        <v>2019200</v>
+      </c>
+      <c r="I80" s="6" t="n">
+        <v>961518</v>
+      </c>
+      <c r="J80" s="6" t="n">
+        <v>414617</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -3068,6 +3772,15 @@
       <c r="G81" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H81" s="6" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="I81" s="6" t="n">
+        <v>1428575</v>
+      </c>
+      <c r="J81" s="6" t="n">
+        <v>537475</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -3101,6 +3814,15 @@
       <c r="G82" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H82" s="6" t="n">
+        <v>7410000</v>
+      </c>
+      <c r="I82" s="6" t="n">
+        <v>3528568</v>
+      </c>
+      <c r="J82" s="6" t="n">
+        <v>1261775</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -3134,6 +3856,15 @@
       <c r="G83" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H83" s="6" t="n">
+        <v>2459000</v>
+      </c>
+      <c r="I83" s="6" t="n">
+        <v>1170951</v>
+      </c>
+      <c r="J83" s="6" t="n">
+        <v>367178</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -3167,6 +3898,15 @@
       <c r="G84" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H84" s="6" t="n">
+        <v>3679500</v>
+      </c>
+      <c r="I84" s="6" t="n">
+        <v>1752153</v>
+      </c>
+      <c r="J84" s="6" t="n">
+        <v>653479</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -3200,6 +3940,15 @@
       <c r="G85" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H85" s="6" t="n">
+        <v>9306200</v>
+      </c>
+      <c r="I85" s="6" t="n">
+        <v>4431514</v>
+      </c>
+      <c r="J85" s="6" t="n">
+        <v>1514413</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -3233,6 +3982,15 @@
       <c r="G86" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H86" s="6" t="n">
+        <v>1708700</v>
+      </c>
+      <c r="I86" s="6" t="n">
+        <v>813659</v>
+      </c>
+      <c r="J86" s="6" t="n">
+        <v>303221</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -3266,6 +4024,15 @@
       <c r="G87" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H87" s="6" t="n">
+        <v>3619500</v>
+      </c>
+      <c r="I87" s="6" t="n">
+        <v>1740135</v>
+      </c>
+      <c r="J87" s="6" t="n">
+        <v>724262</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -3299,6 +4066,15 @@
       <c r="G88" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H88" s="6" t="n">
+        <v>940400</v>
+      </c>
+      <c r="I88" s="6" t="n">
+        <v>447818</v>
+      </c>
+      <c r="J88" s="6" t="n">
+        <v>158152</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -3332,6 +4108,15 @@
       <c r="G89" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H89" s="6" t="n">
+        <v>3660800</v>
+      </c>
+      <c r="I89" s="6" t="n">
+        <v>1759998</v>
+      </c>
+      <c r="J89" s="6" t="n">
+        <v>738155</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -3365,6 +4150,15 @@
       <c r="G90" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H90" s="6" t="n">
+        <v>6168400</v>
+      </c>
+      <c r="I90" s="6" t="n">
+        <v>2937326</v>
+      </c>
+      <c r="J90" s="6" t="n">
+        <v>1102646</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -3398,6 +4192,15 @@
       <c r="G91" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H91" s="6" t="n">
+        <v>5447500</v>
+      </c>
+      <c r="I91" s="6" t="n">
+        <v>2594056</v>
+      </c>
+      <c r="J91" s="6" t="n">
+        <v>1123383</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -3431,6 +4234,15 @@
       <c r="G92" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H92" s="6" t="n">
+        <v>977400</v>
+      </c>
+      <c r="I92" s="6" t="n">
+        <v>465438</v>
+      </c>
+      <c r="J92" s="6" t="n">
+        <v>144416</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
@@ -3464,6 +4276,15 @@
       <c r="G93" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H93" s="6" t="n">
+        <v>1496600</v>
+      </c>
+      <c r="I93" s="6" t="n">
+        <v>712660</v>
+      </c>
+      <c r="J93" s="6" t="n">
+        <v>279864</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -3497,6 +4318,15 @@
       <c r="G94" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H94" s="6" t="n">
+        <v>8967000</v>
+      </c>
+      <c r="I94" s="6" t="n">
+        <v>4270000</v>
+      </c>
+      <c r="J94" s="6" t="n">
+        <v>1431133</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
@@ -3530,6 +4360,15 @@
       <c r="G95" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H95" s="6" t="n">
+        <v>7448000</v>
+      </c>
+      <c r="I95" s="6" t="n">
+        <v>3546674</v>
+      </c>
+      <c r="J95" s="6" t="n">
+        <v>1280524</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
@@ -3563,6 +4402,15 @@
       <c r="G96" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H96" s="6" t="n">
+        <v>5894000</v>
+      </c>
+      <c r="I96" s="6" t="n">
+        <v>2806660</v>
+      </c>
+      <c r="J96" s="6" t="n">
+        <v>941167</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
@@ -3596,6 +4444,15 @@
       <c r="G97" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H97" s="6" t="n">
+        <v>5745600</v>
+      </c>
+      <c r="I97" s="6" t="n">
+        <v>2735993</v>
+      </c>
+      <c r="J97" s="6" t="n">
+        <v>1101267</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -3629,6 +4486,15 @@
       <c r="G98" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H98" s="6" t="n">
+        <v>896400</v>
+      </c>
+      <c r="I98" s="6" t="n">
+        <v>426866</v>
+      </c>
+      <c r="J98" s="6" t="n">
+        <v>161252</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -3662,6 +4528,15 @@
       <c r="G99" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H99" s="6" t="n">
+        <v>2331600</v>
+      </c>
+      <c r="I99" s="6" t="n">
+        <v>1120956</v>
+      </c>
+      <c r="J99" s="6" t="n">
+        <v>396333</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
@@ -3695,6 +4570,15 @@
       <c r="G100" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H100" s="6" t="n">
+        <v>2911500</v>
+      </c>
+      <c r="I100" s="6" t="n">
+        <v>1386437</v>
+      </c>
+      <c r="J100" s="6" t="n">
+        <v>467723</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
@@ -3728,6 +4612,15 @@
       <c r="G101" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H101" s="6" t="n">
+        <v>4254800</v>
+      </c>
+      <c r="I101" s="6" t="n">
+        <v>2026097</v>
+      </c>
+      <c r="J101" s="6" t="n">
+        <v>729640</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
@@ -3761,6 +4654,15 @@
       <c r="G102" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H102" s="6" t="n">
+        <v>6608000</v>
+      </c>
+      <c r="I102" s="6" t="n">
+        <v>3146673</v>
+      </c>
+      <c r="J102" s="6" t="n">
+        <v>1150245</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
@@ -3794,6 +4696,15 @@
       <c r="G103" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H103" s="6" t="n">
+        <v>1504000</v>
+      </c>
+      <c r="I103" s="6" t="n">
+        <v>716186</v>
+      </c>
+      <c r="J103" s="6" t="n">
+        <v>290009</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -3827,6 +4738,15 @@
       <c r="G104" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H104" s="6" t="n">
+        <v>4052400</v>
+      </c>
+      <c r="I104" s="6" t="n">
+        <v>1948265</v>
+      </c>
+      <c r="J104" s="6" t="n">
+        <v>793570</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -3860,6 +4780,15 @@
       <c r="G105" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H105" s="6" t="n">
+        <v>3680600</v>
+      </c>
+      <c r="I105" s="6" t="n">
+        <v>1752668</v>
+      </c>
+      <c r="J105" s="6" t="n">
+        <v>809615</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -3893,6 +4822,15 @@
       <c r="G106" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H106" s="6" t="n">
+        <v>735300</v>
+      </c>
+      <c r="I106" s="6" t="n">
+        <v>350150</v>
+      </c>
+      <c r="J106" s="6" t="n">
+        <v>125295</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
@@ -3926,6 +4864,15 @@
       <c r="G107" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H107" s="6" t="n">
+        <v>1288800</v>
+      </c>
+      <c r="I107" s="6" t="n">
+        <v>613710</v>
+      </c>
+      <c r="J107" s="6" t="n">
+        <v>200263</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
@@ -3959,6 +4906,15 @@
       <c r="G108" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H108" s="6" t="n">
+        <v>3513400</v>
+      </c>
+      <c r="I108" s="6" t="n">
+        <v>1673049</v>
+      </c>
+      <c r="J108" s="6" t="n">
+        <v>583528</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
@@ -3992,6 +4948,15 @@
       <c r="G109" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H109" s="6" t="n">
+        <v>1437300</v>
+      </c>
+      <c r="I109" s="6" t="n">
+        <v>691006</v>
+      </c>
+      <c r="J109" s="6" t="n">
+        <v>306608</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -4025,6 +4990,15 @@
       <c r="G110" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H110" s="6" t="n">
+        <v>5383000</v>
+      </c>
+      <c r="I110" s="6" t="n">
+        <v>2563338</v>
+      </c>
+      <c r="J110" s="6" t="n">
+        <v>825752</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
@@ -4058,6 +5032,15 @@
       <c r="G111" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H111" s="6" t="n">
+        <v>3271400</v>
+      </c>
+      <c r="I111" s="6" t="n">
+        <v>1572785</v>
+      </c>
+      <c r="J111" s="6" t="n">
+        <v>703381</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
@@ -4091,6 +5074,15 @@
       <c r="G112" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H112" s="6" t="n">
+        <v>4736000</v>
+      </c>
+      <c r="I112" s="6" t="n">
+        <v>2255239</v>
+      </c>
+      <c r="J112" s="6" t="n">
+        <v>1154326</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
@@ -4124,6 +5116,15 @@
       <c r="G113" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H113" s="6" t="n">
+        <v>3245000</v>
+      </c>
+      <c r="I113" s="6" t="n">
+        <v>1560093</v>
+      </c>
+      <c r="J113" s="6" t="n">
+        <v>691701</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
@@ -4157,6 +5158,15 @@
       <c r="G114" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H114" s="6" t="n">
+        <v>581600</v>
+      </c>
+      <c r="I114" s="6" t="n">
+        <v>306111</v>
+      </c>
+      <c r="J114" s="6" t="n">
+        <v>121118</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
@@ -4190,6 +5200,15 @@
       <c r="G115" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H115" s="6" t="n">
+        <v>1447000</v>
+      </c>
+      <c r="I115" s="6" t="n">
+        <v>695674</v>
+      </c>
+      <c r="J115" s="6" t="n">
+        <v>286636</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
@@ -4223,6 +5242,15 @@
       <c r="G116" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H116" s="6" t="n">
+        <v>2599200</v>
+      </c>
+      <c r="I116" s="6" t="n">
+        <v>1249609</v>
+      </c>
+      <c r="J116" s="6" t="n">
+        <v>530381</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
@@ -4256,6 +5284,15 @@
       <c r="G117" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H117" s="6" t="n">
+        <v>774950</v>
+      </c>
+      <c r="I117" s="6" t="n">
+        <v>372568</v>
+      </c>
+      <c r="J117" s="6" t="n">
+        <v>137166</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -4289,6 +5326,15 @@
       <c r="G118" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H118" s="6" t="n">
+        <v>2509200</v>
+      </c>
+      <c r="I118" s="6" t="n">
+        <v>1194853</v>
+      </c>
+      <c r="J118" s="6" t="n">
+        <v>355289</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
@@ -4322,6 +5368,15 @@
       <c r="G119" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H119" s="6" t="n">
+        <v>1773200</v>
+      </c>
+      <c r="I119" s="6" t="n">
+        <v>844384</v>
+      </c>
+      <c r="J119" s="6" t="n">
+        <v>368853</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
@@ -4355,6 +5410,15 @@
       <c r="G120" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H120" s="6" t="n">
+        <v>1225800</v>
+      </c>
+      <c r="I120" s="6" t="n">
+        <v>583712</v>
+      </c>
+      <c r="J120" s="6" t="n">
+        <v>195719</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
@@ -4388,6 +5452,15 @@
       <c r="G121" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H121" s="6" t="n">
+        <v>5404000</v>
+      </c>
+      <c r="I121" s="6" t="n">
+        <v>2573331</v>
+      </c>
+      <c r="J121" s="6" t="n">
+        <v>1019411</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
@@ -4421,6 +5494,15 @@
       <c r="G122" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H122" s="6" t="n">
+        <v>2688000</v>
+      </c>
+      <c r="I122" s="6" t="n">
+        <v>1292310</v>
+      </c>
+      <c r="J122" s="6" t="n">
+        <v>555126</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
@@ -4454,6 +5536,15 @@
       <c r="G123" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H123" s="6" t="n">
+        <v>1590000</v>
+      </c>
+      <c r="I123" s="6" t="n">
+        <v>757145</v>
+      </c>
+      <c r="J123" s="6" t="n">
+        <v>306857</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
@@ -4487,6 +5578,15 @@
       <c r="G124" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H124" s="6" t="n">
+        <v>656500</v>
+      </c>
+      <c r="I124" s="6" t="n">
+        <v>312625</v>
+      </c>
+      <c r="J124" s="6" t="n">
+        <v>137458</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
@@ -4520,6 +5620,15 @@
       <c r="G125" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H125" s="6" t="n">
+        <v>3477600</v>
+      </c>
+      <c r="I125" s="6" t="n">
+        <v>1655994</v>
+      </c>
+      <c r="J125" s="6" t="n">
+        <v>573881</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
@@ -4553,6 +5662,15 @@
       <c r="G126" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H126" s="6" t="n">
+        <v>3600800</v>
+      </c>
+      <c r="I126" s="6" t="n">
+        <v>1714662</v>
+      </c>
+      <c r="J126" s="6" t="n">
+        <v>633149</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
@@ -4586,6 +5704,15 @@
       <c r="G127" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H127" s="6" t="n">
+        <v>494000</v>
+      </c>
+      <c r="I127" s="6" t="n">
+        <v>235243</v>
+      </c>
+      <c r="J127" s="6" t="n">
+        <v>85820</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
@@ -4619,6 +5746,15 @@
       <c r="G128" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H128" s="6" t="n">
+        <v>2199600</v>
+      </c>
+      <c r="I128" s="6" t="n">
+        <v>1057494</v>
+      </c>
+      <c r="J128" s="6" t="n">
+        <v>455048</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
@@ -4652,6 +5788,15 @@
       <c r="G129" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H129" s="6" t="n">
+        <v>4872000</v>
+      </c>
+      <c r="I129" s="6" t="n">
+        <v>2319998</v>
+      </c>
+      <c r="J129" s="6" t="n">
+        <v>845560</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
@@ -4685,6 +5830,15 @@
       <c r="G130" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H130" s="6" t="n">
+        <v>2668600</v>
+      </c>
+      <c r="I130" s="6" t="n">
+        <v>1270763</v>
+      </c>
+      <c r="J130" s="6" t="n">
+        <v>443085</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
@@ -4718,6 +5872,15 @@
       <c r="G131" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H131" s="6" t="n">
+        <v>711600</v>
+      </c>
+      <c r="I131" s="6" t="n">
+        <v>342114</v>
+      </c>
+      <c r="J131" s="6" t="n">
+        <v>126902</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
@@ -4751,6 +5914,15 @@
       <c r="G132" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H132" s="6" t="n">
+        <v>2122200</v>
+      </c>
+      <c r="I132" s="6" t="n">
+        <v>1020283</v>
+      </c>
+      <c r="J132" s="6" t="n">
+        <v>391440</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
@@ -4784,6 +5956,15 @@
       <c r="G133" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H133" s="6" t="n">
+        <v>2354000</v>
+      </c>
+      <c r="I133" s="6" t="n">
+        <v>1131733</v>
+      </c>
+      <c r="J133" s="6" t="n">
+        <v>486148</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
@@ -4817,6 +5998,15 @@
       <c r="G134" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H134" s="6" t="n">
+        <v>1044900</v>
+      </c>
+      <c r="I134" s="6" t="n">
+        <v>502353</v>
+      </c>
+      <c r="J134" s="6" t="n">
+        <v>193980</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
@@ -4850,6 +6040,15 @@
       <c r="G135" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H135" s="6" t="n">
+        <v>5179500</v>
+      </c>
+      <c r="I135" s="6" t="n">
+        <v>2466432</v>
+      </c>
+      <c r="J135" s="6" t="n">
+        <v>976773</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
@@ -4883,6 +6082,15 @@
       <c r="G136" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H136" s="6" t="n">
+        <v>1806400</v>
+      </c>
+      <c r="I136" s="6" t="n">
+        <v>868461</v>
+      </c>
+      <c r="J136" s="6" t="n">
+        <v>284790</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
@@ -4916,6 +6124,15 @@
       <c r="G137" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H137" s="6" t="n">
+        <v>2450800</v>
+      </c>
+      <c r="I137" s="6" t="n">
+        <v>1167049</v>
+      </c>
+      <c r="J137" s="6" t="n">
+        <v>501645</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
@@ -4949,6 +6166,15 @@
       <c r="G138" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H138" s="6" t="n">
+        <v>2424400</v>
+      </c>
+      <c r="I138" s="6" t="n">
+        <v>1165574</v>
+      </c>
+      <c r="J138" s="6" t="n">
+        <v>460460</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
@@ -4982,6 +6208,15 @@
       <c r="G139" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H139" s="6" t="n">
+        <v>875200</v>
+      </c>
+      <c r="I139" s="6" t="n">
+        <v>416759</v>
+      </c>
+      <c r="J139" s="6" t="n">
+        <v>149025</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
@@ -5015,6 +6250,15 @@
       <c r="G140" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H140" s="6" t="n">
+        <v>374850</v>
+      </c>
+      <c r="I140" s="6" t="n">
+        <v>180217</v>
+      </c>
+      <c r="J140" s="6" t="n">
+        <v>76609</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
@@ -5048,6 +6292,15 @@
       <c r="G141" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H141" s="6" t="n">
+        <v>848000</v>
+      </c>
+      <c r="I141" s="6" t="n">
+        <v>403807</v>
+      </c>
+      <c r="J141" s="6" t="n">
+        <v>149587</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -5081,6 +6334,15 @@
       <c r="G142" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H142" s="6" t="n">
+        <v>521000</v>
+      </c>
+      <c r="I142" s="6" t="n">
+        <v>250476</v>
+      </c>
+      <c r="J142" s="6" t="n">
+        <v>105138</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
@@ -5114,6 +6376,15 @@
       <c r="G143" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H143" s="6" t="n">
+        <v>823200</v>
+      </c>
+      <c r="I143" s="6" t="n">
+        <v>395774</v>
+      </c>
+      <c r="J143" s="6" t="n">
+        <v>177163</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
@@ -5147,6 +6418,15 @@
       <c r="G144" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H144" s="6" t="n">
+        <v>3510500</v>
+      </c>
+      <c r="I144" s="6" t="n">
+        <v>1671670</v>
+      </c>
+      <c r="J144" s="6" t="n">
+        <v>554930</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
@@ -5180,6 +6460,15 @@
       <c r="G145" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H145" s="6" t="n">
+        <v>1288300</v>
+      </c>
+      <c r="I145" s="6" t="n">
+        <v>619375</v>
+      </c>
+      <c r="J145" s="6" t="n">
+        <v>257363</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
@@ -5213,6 +6502,15 @@
       <c r="G146" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H146" s="6" t="n">
+        <v>445050</v>
+      </c>
+      <c r="I146" s="6" t="n">
+        <v>213970</v>
+      </c>
+      <c r="J146" s="6" t="n">
+        <v>88535</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
@@ -5246,6 +6544,15 @@
       <c r="G147" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H147" s="6" t="n">
+        <v>389200</v>
+      </c>
+      <c r="I147" s="6" t="n">
+        <v>187118</v>
+      </c>
+      <c r="J147" s="6" t="n">
+        <v>68606</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
@@ -5279,6 +6586,15 @@
       <c r="G148" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H148" s="6" t="n">
+        <v>382400</v>
+      </c>
+      <c r="I148" s="6" t="n">
+        <v>182099</v>
+      </c>
+      <c r="J148" s="6" t="n">
+        <v>70782</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
@@ -5312,6 +6628,15 @@
       <c r="G149" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H149" s="6" t="n">
+        <v>469500</v>
+      </c>
+      <c r="I149" s="6" t="n">
+        <v>247107</v>
+      </c>
+      <c r="J149" s="6" t="n">
+        <v>96398</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
@@ -5345,6 +6670,15 @@
       <c r="G150" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H150" s="6" t="n">
+        <v>2345200</v>
+      </c>
+      <c r="I150" s="6" t="n">
+        <v>1116766</v>
+      </c>
+      <c r="J150" s="6" t="n">
+        <v>319705</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
@@ -5378,6 +6712,15 @@
       <c r="G151" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H151" s="6" t="n">
+        <v>806400</v>
+      </c>
+      <c r="I151" s="6" t="n">
+        <v>383999</v>
+      </c>
+      <c r="J151" s="6" t="n">
+        <v>141989</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
@@ -5411,6 +6754,15 @@
       <c r="G152" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H152" s="6" t="n">
+        <v>1603800</v>
+      </c>
+      <c r="I152" s="6" t="n">
+        <v>763712</v>
+      </c>
+      <c r="J152" s="6" t="n">
+        <v>280237</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
@@ -5444,6 +6796,15 @@
       <c r="G153" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H153" s="6" t="n">
+        <v>1942600</v>
+      </c>
+      <c r="I153" s="6" t="n">
+        <v>925048</v>
+      </c>
+      <c r="J153" s="6" t="n">
+        <v>356238</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
@@ -5477,6 +6838,15 @@
       <c r="G154" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H154" s="6" t="n">
+        <v>1324500</v>
+      </c>
+      <c r="I154" s="6" t="n">
+        <v>636775</v>
+      </c>
+      <c r="J154" s="6" t="n">
+        <v>200044</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
@@ -5510,6 +6880,15 @@
       <c r="G155" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H155" s="6" t="n">
+        <v>1732000</v>
+      </c>
+      <c r="I155" s="6" t="n">
+        <v>832694</v>
+      </c>
+      <c r="J155" s="6" t="n">
+        <v>372086</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
@@ -5543,6 +6922,15 @@
       <c r="G156" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H156" s="6" t="n">
+        <v>2249000</v>
+      </c>
+      <c r="I156" s="6" t="n">
+        <v>1070956</v>
+      </c>
+      <c r="J156" s="6" t="n">
+        <v>331918</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
@@ -5576,6 +6964,15 @@
       <c r="G157" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H157" s="6" t="n">
+        <v>1108900</v>
+      </c>
+      <c r="I157" s="6" t="n">
+        <v>533125</v>
+      </c>
+      <c r="J157" s="6" t="n">
+        <v>214146</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
@@ -5609,6 +7006,15 @@
       <c r="G158" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H158" s="6" t="n">
+        <v>1512000</v>
+      </c>
+      <c r="I158" s="6" t="n">
+        <v>719998</v>
+      </c>
+      <c r="J158" s="6" t="n">
+        <v>250690</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
@@ -5642,6 +7048,15 @@
       <c r="G159" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H159" s="6" t="n">
+        <v>1843600</v>
+      </c>
+      <c r="I159" s="6" t="n">
+        <v>970312</v>
+      </c>
+      <c r="J159" s="6" t="n">
+        <v>459928</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
@@ -5675,6 +7090,15 @@
       <c r="G160" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H160" s="6" t="n">
+        <v>1608000</v>
+      </c>
+      <c r="I160" s="6" t="n">
+        <v>773078</v>
+      </c>
+      <c r="J160" s="6" t="n">
+        <v>314227</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
@@ -5708,6 +7132,15 @@
       <c r="G161" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H161" s="6" t="n">
+        <v>1556000</v>
+      </c>
+      <c r="I161" s="6" t="n">
+        <v>748078</v>
+      </c>
+      <c r="J161" s="6" t="n">
+        <v>324869</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
@@ -5741,6 +7174,15 @@
       <c r="G162" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H162" s="6" t="n">
+        <v>775000</v>
+      </c>
+      <c r="I162" s="6" t="n">
+        <v>369047</v>
+      </c>
+      <c r="J162" s="6" t="n">
+        <v>135300</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
@@ -5774,6 +7216,15 @@
       <c r="G163" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H163" s="6" t="n">
+        <v>4240500</v>
+      </c>
+      <c r="I163" s="6" t="n">
+        <v>2231845</v>
+      </c>
+      <c r="J163" s="6" t="n">
+        <v>961129</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
@@ -5807,6 +7258,15 @@
       <c r="G164" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H164" s="6" t="n">
+        <v>1132500</v>
+      </c>
+      <c r="I164" s="6" t="n">
+        <v>539289</v>
+      </c>
+      <c r="J164" s="6" t="n">
+        <v>247059</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
@@ -5840,6 +7300,15 @@
       <c r="G165" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H165" s="6" t="n">
+        <v>945100</v>
+      </c>
+      <c r="I165" s="6" t="n">
+        <v>454375</v>
+      </c>
+      <c r="J165" s="6" t="n">
+        <v>239190</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
@@ -5873,6 +7342,15 @@
       <c r="G166" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H166" s="6" t="n">
+        <v>1434000</v>
+      </c>
+      <c r="I166" s="6" t="n">
+        <v>682856</v>
+      </c>
+      <c r="J166" s="6" t="n">
+        <v>240181</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
@@ -5906,6 +7384,15 @@
       <c r="G167" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H167" s="6" t="n">
+        <v>714000</v>
+      </c>
+      <c r="I167" s="6" t="n">
+        <v>340000</v>
+      </c>
+      <c r="J167" s="6" t="n">
+        <v>130084</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
@@ -5939,6 +7426,15 @@
       <c r="G168" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H168" s="6" t="n">
+        <v>3199500</v>
+      </c>
+      <c r="I168" s="6" t="n">
+        <v>1523573</v>
+      </c>
+      <c r="J168" s="6" t="n">
+        <v>695984</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
@@ -5972,6 +7468,15 @@
       <c r="G169" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H169" s="6" t="n">
+        <v>843600</v>
+      </c>
+      <c r="I169" s="6" t="n">
+        <v>401715</v>
+      </c>
+      <c r="J169" s="6" t="n">
+        <v>173690</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
@@ -6005,6 +7510,15 @@
       <c r="G170" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H170" s="6" t="n">
+        <v>1263600</v>
+      </c>
+      <c r="I170" s="6" t="n">
+        <v>607497</v>
+      </c>
+      <c r="J170" s="6" t="n">
+        <v>260730</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
@@ -6038,6 +7552,15 @@
       <c r="G171" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H171" s="6" t="n">
+        <v>1023000</v>
+      </c>
+      <c r="I171" s="6" t="n">
+        <v>487146</v>
+      </c>
+      <c r="J171" s="6" t="n">
+        <v>194834</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
@@ -6071,6 +7594,15 @@
       <c r="G172" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H172" s="6" t="n">
+        <v>1159400</v>
+      </c>
+      <c r="I172" s="6" t="n">
+        <v>557405</v>
+      </c>
+      <c r="J172" s="6" t="n">
+        <v>253997</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
@@ -6104,6 +7636,15 @@
       <c r="G173" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H173" s="6" t="n">
+        <v>2105600</v>
+      </c>
+      <c r="I173" s="6" t="n">
+        <v>1002667</v>
+      </c>
+      <c r="J173" s="6" t="n">
+        <v>324414</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
@@ -6137,6 +7678,15 @@
       <c r="G174" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H174" s="6" t="n">
+        <v>1445400</v>
+      </c>
+      <c r="I174" s="6" t="n">
+        <v>688286</v>
+      </c>
+      <c r="J174" s="6" t="n">
+        <v>267544</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
@@ -6170,6 +7720,15 @@
       <c r="G175" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H175" s="6" t="n">
+        <v>958500</v>
+      </c>
+      <c r="I175" s="6" t="n">
+        <v>460815</v>
+      </c>
+      <c r="J175" s="6" t="n">
+        <v>165814</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
@@ -6203,6 +7762,15 @@
       <c r="G176" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H176" s="6" t="n">
+        <v>1084600</v>
+      </c>
+      <c r="I176" s="6" t="n">
+        <v>521444</v>
+      </c>
+      <c r="J176" s="6" t="n">
+        <v>227689</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
@@ -6236,6 +7804,15 @@
       <c r="G177" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H177" s="6" t="n">
+        <v>951000</v>
+      </c>
+      <c r="I177" s="6" t="n">
+        <v>452860</v>
+      </c>
+      <c r="J177" s="6" t="n">
+        <v>170819</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
@@ -6269,6 +7846,15 @@
       <c r="G178" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H178" s="6" t="n">
+        <v>347050</v>
+      </c>
+      <c r="I178" s="6" t="n">
+        <v>165259</v>
+      </c>
+      <c r="J178" s="6" t="n">
+        <v>59314</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
@@ -6302,6 +7888,15 @@
       <c r="G179" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H179" s="6" t="n">
+        <v>2817000</v>
+      </c>
+      <c r="I179" s="6" t="n">
+        <v>1341430</v>
+      </c>
+      <c r="J179" s="6" t="n">
+        <v>577554</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
@@ -6335,6 +7930,15 @@
       <c r="G180" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H180" s="6" t="n">
+        <v>1238000</v>
+      </c>
+      <c r="I180" s="6" t="n">
+        <v>589523</v>
+      </c>
+      <c r="J180" s="6" t="n">
+        <v>220630</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
@@ -6368,6 +7972,15 @@
       <c r="G181" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H181" s="6" t="n">
+        <v>1361800</v>
+      </c>
+      <c r="I181" s="6" t="n">
+        <v>654710</v>
+      </c>
+      <c r="J181" s="6" t="n">
+        <v>259138</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
@@ -6401,6 +8014,15 @@
       <c r="G182" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H182" s="6" t="n">
+        <v>216300</v>
+      </c>
+      <c r="I182" s="6" t="n">
+        <v>103002</v>
+      </c>
+      <c r="J182" s="6" t="n">
+        <v>39441</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
@@ -6434,6 +8056,15 @@
       <c r="G183" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H183" s="6" t="n">
+        <v>1625400</v>
+      </c>
+      <c r="I183" s="6" t="n">
+        <v>773997</v>
+      </c>
+      <c r="J183" s="6" t="n">
+        <v>267697</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
@@ -6467,6 +8098,15 @@
       <c r="G184" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H184" s="6" t="n">
+        <v>1291400</v>
+      </c>
+      <c r="I184" s="6" t="n">
+        <v>679681</v>
+      </c>
+      <c r="J184" s="6" t="n">
+        <v>331133</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
@@ -6500,6 +8140,15 @@
       <c r="G185" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H185" s="6" t="n">
+        <v>2044000</v>
+      </c>
+      <c r="I185" s="6" t="n">
+        <v>982691</v>
+      </c>
+      <c r="J185" s="6" t="n">
+        <v>429380</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
@@ -6533,6 +8182,15 @@
       <c r="G186" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H186" s="6" t="n">
+        <v>1820800</v>
+      </c>
+      <c r="I186" s="6" t="n">
+        <v>867048</v>
+      </c>
+      <c r="J186" s="6" t="n">
+        <v>367033</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
@@ -6566,6 +8224,15 @@
       <c r="G187" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H187" s="6" t="n">
+        <v>1988000</v>
+      </c>
+      <c r="I187" s="6" t="n">
+        <v>946669</v>
+      </c>
+      <c r="J187" s="6" t="n">
+        <v>287016</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
@@ -6599,6 +8266,15 @@
       <c r="G188" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H188" s="6" t="n">
+        <v>820500</v>
+      </c>
+      <c r="I188" s="6" t="n">
+        <v>394469</v>
+      </c>
+      <c r="J188" s="6" t="n">
+        <v>154582</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
@@ -6632,6 +8308,15 @@
       <c r="G189" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H189" s="6" t="n">
+        <v>1734400</v>
+      </c>
+      <c r="I189" s="6" t="n">
+        <v>833845</v>
+      </c>
+      <c r="J189" s="6" t="n">
+        <v>371942</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
@@ -6665,6 +8350,15 @@
       <c r="G190" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H190" s="6" t="n">
+        <v>690300</v>
+      </c>
+      <c r="I190" s="6" t="n">
+        <v>328716</v>
+      </c>
+      <c r="J190" s="6" t="n">
+        <v>109296</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
@@ -6698,6 +8392,15 @@
       <c r="G191" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H191" s="6" t="n">
+        <v>1133000</v>
+      </c>
+      <c r="I191" s="6" t="n">
+        <v>544710</v>
+      </c>
+      <c r="J191" s="6" t="n">
+        <v>215600</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
@@ -6731,6 +8434,15 @@
       <c r="G192" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H192" s="6" t="n">
+        <v>748500</v>
+      </c>
+      <c r="I192" s="6" t="n">
+        <v>359854</v>
+      </c>
+      <c r="J192" s="6" t="n">
+        <v>138278</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
@@ -6764,6 +8476,15 @@
       <c r="G193" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H193" s="6" t="n">
+        <v>876600</v>
+      </c>
+      <c r="I193" s="6" t="n">
+        <v>417427</v>
+      </c>
+      <c r="J193" s="6" t="n">
+        <v>128193</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
@@ -6797,6 +8518,15 @@
       <c r="G194" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H194" s="6" t="n">
+        <v>617500</v>
+      </c>
+      <c r="I194" s="6" t="n">
+        <v>294049</v>
+      </c>
+      <c r="J194" s="6" t="n">
+        <v>100667</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
@@ -6830,6 +8560,15 @@
       <c r="G195" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H195" s="6" t="n">
+        <v>679500</v>
+      </c>
+      <c r="I195" s="6" t="n">
+        <v>326681</v>
+      </c>
+      <c r="J195" s="6" t="n">
+        <v>128244</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
@@ -6863,6 +8602,15 @@
       <c r="G196" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H196" s="6" t="n">
+        <v>436000</v>
+      </c>
+      <c r="I196" s="6" t="n">
+        <v>209616</v>
+      </c>
+      <c r="J196" s="6" t="n">
+        <v>82600</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
@@ -6896,6 +8644,15 @@
       <c r="G197" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H197" s="6" t="n">
+        <v>1209600</v>
+      </c>
+      <c r="I197" s="6" t="n">
+        <v>581537</v>
+      </c>
+      <c r="J197" s="6" t="n">
+        <v>252629</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
@@ -6929,6 +8686,15 @@
       <c r="G198" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H198" s="6" t="n">
+        <v>1110200</v>
+      </c>
+      <c r="I198" s="6" t="n">
+        <v>533750</v>
+      </c>
+      <c r="J198" s="6" t="n">
+        <v>239983</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
@@ -6962,6 +8728,15 @@
       <c r="G199" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H199" s="6" t="n">
+        <v>1107600</v>
+      </c>
+      <c r="I199" s="6" t="n">
+        <v>532500</v>
+      </c>
+      <c r="J199" s="6" t="n">
+        <v>203671</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
@@ -6995,6 +8770,15 @@
       <c r="G200" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H200" s="6" t="n">
+        <v>1473500</v>
+      </c>
+      <c r="I200" s="6" t="n">
+        <v>701668</v>
+      </c>
+      <c r="J200" s="6" t="n">
+        <v>225387</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
@@ -7028,6 +8812,15 @@
       <c r="G201" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H201" s="6" t="n">
+        <v>1084200</v>
+      </c>
+      <c r="I201" s="6" t="n">
+        <v>521250</v>
+      </c>
+      <c r="J201" s="6" t="n">
+        <v>199368</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
@@ -7061,6 +8854,15 @@
       <c r="G202" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H202" s="6" t="n">
+        <v>2040000</v>
+      </c>
+      <c r="I202" s="6" t="n">
+        <v>971428</v>
+      </c>
+      <c r="J202" s="6" t="n">
+        <v>492370</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
@@ -7094,6 +8896,15 @@
       <c r="G203" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H203" s="6" t="n">
+        <v>886600</v>
+      </c>
+      <c r="I203" s="6" t="n">
+        <v>422191</v>
+      </c>
+      <c r="J203" s="6" t="n">
+        <v>157408</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="5" t="inlineStr">
@@ -7127,6 +8938,15 @@
       <c r="G204" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H204" s="6" t="n">
+        <v>633600</v>
+      </c>
+      <c r="I204" s="6" t="n">
+        <v>304615</v>
+      </c>
+      <c r="J204" s="6" t="n">
+        <v>121592</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="5" t="inlineStr">
@@ -7160,6 +8980,15 @@
       <c r="G205" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H205" s="6" t="n">
+        <v>663000</v>
+      </c>
+      <c r="I205" s="6" t="n">
+        <v>318751</v>
+      </c>
+      <c r="J205" s="6" t="n">
+        <v>120920</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
@@ -7193,6 +9022,15 @@
       <c r="G206" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H206" s="6" t="n">
+        <v>1212800</v>
+      </c>
+      <c r="I206" s="6" t="n">
+        <v>577524</v>
+      </c>
+      <c r="J206" s="6" t="n">
+        <v>304822</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
@@ -7226,6 +9064,15 @@
       <c r="G207" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H207" s="6" t="n">
+        <v>907500</v>
+      </c>
+      <c r="I207" s="6" t="n">
+        <v>432144</v>
+      </c>
+      <c r="J207" s="6" t="n">
+        <v>163368</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="5" t="inlineStr">
@@ -7259,6 +9106,15 @@
       <c r="G208" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H208" s="6" t="n">
+        <v>434400</v>
+      </c>
+      <c r="I208" s="6" t="n">
+        <v>208845</v>
+      </c>
+      <c r="J208" s="6" t="n">
+        <v>80440</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
@@ -7292,6 +9148,15 @@
       <c r="G209" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H209" s="6" t="n">
+        <v>2223000</v>
+      </c>
+      <c r="I209" s="6" t="n">
+        <v>1169999</v>
+      </c>
+      <c r="J209" s="6" t="n">
+        <v>546602</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
@@ -7325,6 +9190,15 @@
       <c r="G210" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H210" s="6" t="n">
+        <v>273600</v>
+      </c>
+      <c r="I210" s="6" t="n">
+        <v>131540</v>
+      </c>
+      <c r="J210" s="6" t="n">
+        <v>53178</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
@@ -7358,6 +9232,15 @@
       <c r="G211" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H211" s="6" t="n">
+        <v>269600</v>
+      </c>
+      <c r="I211" s="6" t="n">
+        <v>129617</v>
+      </c>
+      <c r="J211" s="6" t="n">
+        <v>70045</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="5" t="inlineStr">
@@ -7391,6 +9274,15 @@
       <c r="G212" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H212" s="6" t="n">
+        <v>233800</v>
+      </c>
+      <c r="I212" s="6" t="n">
+        <v>112404</v>
+      </c>
+      <c r="J212" s="6" t="n">
+        <v>60424</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
@@ -7424,6 +9316,15 @@
       <c r="G213" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H213" s="6" t="n">
+        <v>481500</v>
+      </c>
+      <c r="I213" s="6" t="n">
+        <v>229287</v>
+      </c>
+      <c r="J213" s="6" t="n">
+        <v>75371</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
@@ -7457,6 +9358,15 @@
       <c r="G214" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H214" s="6" t="n">
+        <v>206050</v>
+      </c>
+      <c r="I214" s="6" t="n">
+        <v>99062</v>
+      </c>
+      <c r="J214" s="6" t="n">
+        <v>37853</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
@@ -7490,6 +9400,15 @@
       <c r="G215" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H215" s="6" t="n">
+        <v>460500</v>
+      </c>
+      <c r="I215" s="6" t="n">
+        <v>221393</v>
+      </c>
+      <c r="J215" s="6" t="n">
+        <v>84250</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
@@ -7523,6 +9442,15 @@
       <c r="G216" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H216" s="6" t="n">
+        <v>396500</v>
+      </c>
+      <c r="I216" s="6" t="n">
+        <v>190625</v>
+      </c>
+      <c r="J216" s="6" t="n">
+        <v>76604</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
@@ -7556,6 +9484,15 @@
       <c r="G217" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H217" s="6" t="n">
+        <v>430500</v>
+      </c>
+      <c r="I217" s="6" t="n">
+        <v>205001</v>
+      </c>
+      <c r="J217" s="6" t="n">
+        <v>84338</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
@@ -7589,6 +9526,15 @@
       <c r="G218" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H218" s="6" t="n">
+        <v>424500</v>
+      </c>
+      <c r="I218" s="6" t="n">
+        <v>202144</v>
+      </c>
+      <c r="J218" s="6" t="n">
+        <v>75422</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
@@ -7622,6 +9568,15 @@
       <c r="G219" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H219" s="6" t="n">
+        <v>680000</v>
+      </c>
+      <c r="I219" s="6" t="n">
+        <v>323811</v>
+      </c>
+      <c r="J219" s="6" t="n">
+        <v>130019</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
@@ -7655,6 +9610,15 @@
       <c r="G220" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H220" s="6" t="n">
+        <v>384000</v>
+      </c>
+      <c r="I220" s="6" t="n">
+        <v>182858</v>
+      </c>
+      <c r="J220" s="6" t="n">
+        <v>75333</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
@@ -7688,6 +9652,15 @@
       <c r="G221" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H221" s="6" t="n">
+        <v>451000</v>
+      </c>
+      <c r="I221" s="6" t="n">
+        <v>214762</v>
+      </c>
+      <c r="J221" s="6" t="n">
+        <v>69563</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
@@ -7721,6 +9694,15 @@
       <c r="G222" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H222" s="6" t="n">
+        <v>882000</v>
+      </c>
+      <c r="I222" s="6" t="n">
+        <v>420001</v>
+      </c>
+      <c r="J222" s="6" t="n">
+        <v>187984</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
@@ -7754,6 +9736,15 @@
       <c r="G223" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H223" s="6" t="n">
+        <v>250900</v>
+      </c>
+      <c r="I223" s="6" t="n">
+        <v>120625</v>
+      </c>
+      <c r="J223" s="6" t="n">
+        <v>50493</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
@@ -7787,6 +9778,15 @@
       <c r="G224" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H224" s="6" t="n">
+        <v>75600</v>
+      </c>
+      <c r="I224" s="6" t="n">
+        <v>36347</v>
+      </c>
+      <c r="J224" s="6" t="n">
+        <v>12232</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="5" t="inlineStr">
@@ -7820,6 +9820,15 @@
       <c r="G225" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H225" s="6" t="n">
+        <v>1598000</v>
+      </c>
+      <c r="I225" s="6" t="n">
+        <v>841052</v>
+      </c>
+      <c r="J225" s="6" t="n">
+        <v>364916</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="5" t="inlineStr">
@@ -7853,6 +9862,15 @@
       <c r="G226" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H226" s="6" t="n">
+        <v>920000</v>
+      </c>
+      <c r="I226" s="6" t="n">
+        <v>438095</v>
+      </c>
+      <c r="J226" s="6" t="n">
+        <v>236699</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
@@ -7886,6 +9904,15 @@
       <c r="G227" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H227" s="6" t="n">
+        <v>218400</v>
+      </c>
+      <c r="I227" s="6" t="n">
+        <v>104999</v>
+      </c>
+      <c r="J227" s="6" t="n">
+        <v>44896</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="5" t="inlineStr">
@@ -7919,6 +9946,15 @@
       <c r="G228" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H228" s="6" t="n">
+        <v>291600</v>
+      </c>
+      <c r="I228" s="6" t="n">
+        <v>140192</v>
+      </c>
+      <c r="J228" s="6" t="n">
+        <v>56533</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
@@ -7952,6 +9988,15 @@
       <c r="G229" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H229" s="6" t="n">
+        <v>1368500</v>
+      </c>
+      <c r="I229" s="6" t="n">
+        <v>720262</v>
+      </c>
+      <c r="J229" s="6" t="n">
+        <v>339213</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
@@ -7985,6 +10030,15 @@
       <c r="G230" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H230" s="6" t="n">
+        <v>79500</v>
+      </c>
+      <c r="I230" s="6" t="n">
+        <v>38220</v>
+      </c>
+      <c r="J230" s="6" t="n">
+        <v>15445</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
@@ -8018,6 +10072,15 @@
       <c r="G231" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H231" s="6" t="n">
+        <v>225000</v>
+      </c>
+      <c r="I231" s="6" t="n">
+        <v>107144</v>
+      </c>
+      <c r="J231" s="6" t="n">
+        <v>43578</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
@@ -8051,6 +10114,15 @@
       <c r="G232" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H232" s="6" t="n">
+        <v>99200</v>
+      </c>
+      <c r="I232" s="6" t="n">
+        <v>47238</v>
+      </c>
+      <c r="J232" s="6" t="n">
+        <v>21758</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
@@ -8084,6 +10156,15 @@
       <c r="G233" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H233" s="6" t="n">
+        <v>195500</v>
+      </c>
+      <c r="I233" s="6" t="n">
+        <v>93095</v>
+      </c>
+      <c r="J233" s="6" t="n">
+        <v>30452</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="5" t="inlineStr">
@@ -8117,6 +10198,15 @@
       <c r="G234" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H234" s="6" t="n">
+        <v>420000</v>
+      </c>
+      <c r="I234" s="6" t="n">
+        <v>200000</v>
+      </c>
+      <c r="J234" s="6" t="n">
+        <v>83557</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="5" t="inlineStr">
@@ -8150,6 +10240,15 @@
       <c r="G235" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H235" s="6" t="n">
+        <v>274400</v>
+      </c>
+      <c r="I235" s="6" t="n">
+        <v>130666</v>
+      </c>
+      <c r="J235" s="6" t="n">
+        <v>45631</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
@@ -8183,6 +10282,15 @@
       <c r="G236" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H236" s="6" t="n">
+        <v>533500</v>
+      </c>
+      <c r="I236" s="6" t="n">
+        <v>280790</v>
+      </c>
+      <c r="J236" s="6" t="n">
+        <v>124245</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="5" t="inlineStr">
@@ -8216,6 +10324,15 @@
       <c r="G237" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H237" s="6" t="n">
+        <v>297600</v>
+      </c>
+      <c r="I237" s="6" t="n">
+        <v>141714</v>
+      </c>
+      <c r="J237" s="6" t="n">
+        <v>61224</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="5" t="inlineStr">
@@ -8249,6 +10366,15 @@
       <c r="G238" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H238" s="6" t="n">
+        <v>559000</v>
+      </c>
+      <c r="I238" s="6" t="n">
+        <v>294210</v>
+      </c>
+      <c r="J238" s="6" t="n">
+        <v>143630</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="5" t="inlineStr">
@@ -8282,6 +10408,15 @@
       <c r="G239" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H239" s="6" t="n">
+        <v>180400</v>
+      </c>
+      <c r="I239" s="6" t="n">
+        <v>85905</v>
+      </c>
+      <c r="J239" s="6" t="n">
+        <v>25928</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="5" t="inlineStr">
@@ -8315,6 +10450,15 @@
       <c r="G240" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H240" s="6" t="n">
+        <v>539000</v>
+      </c>
+      <c r="I240" s="6" t="n">
+        <v>256666</v>
+      </c>
+      <c r="J240" s="6" t="n">
+        <v>119403</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
@@ -8348,6 +10492,15 @@
       <c r="G241" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H241" s="6" t="n">
+        <v>444000</v>
+      </c>
+      <c r="I241" s="6" t="n">
+        <v>211428</v>
+      </c>
+      <c r="J241" s="6" t="n">
+        <v>96340</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
@@ -8381,6 +10534,15 @@
       <c r="G242" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H242" s="6" t="n">
+        <v>414000</v>
+      </c>
+      <c r="I242" s="6" t="n">
+        <v>197143</v>
+      </c>
+      <c r="J242" s="6" t="n">
+        <v>86550</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
@@ -8414,6 +10576,15 @@
       <c r="G243" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H243" s="6" t="n">
+        <v>441000</v>
+      </c>
+      <c r="I243" s="6" t="n">
+        <v>210000</v>
+      </c>
+      <c r="J243" s="6" t="n">
+        <v>89543</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="5" t="inlineStr">
@@ -8447,6 +10618,15 @@
       <c r="G244" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H244" s="6" t="n">
+        <v>122500</v>
+      </c>
+      <c r="I244" s="6" t="n">
+        <v>58334</v>
+      </c>
+      <c r="J244" s="6" t="n">
+        <v>18620</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="5" t="inlineStr">
@@ -8480,6 +10660,15 @@
       <c r="G245" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H245" s="6" t="n">
+        <v>312000</v>
+      </c>
+      <c r="I245" s="6" t="n">
+        <v>164210</v>
+      </c>
+      <c r="J245" s="6" t="n">
+        <v>78414</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="5" t="inlineStr">
@@ -8513,6 +10702,15 @@
       <c r="G246" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H246" s="6" t="n">
+        <v>192000</v>
+      </c>
+      <c r="I246" s="6" t="n">
+        <v>91428</v>
+      </c>
+      <c r="J246" s="6" t="n">
+        <v>40335</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
@@ -8546,6 +10744,15 @@
       <c r="G247" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H247" s="6" t="n">
+        <v>96800</v>
+      </c>
+      <c r="I247" s="6" t="n">
+        <v>46095</v>
+      </c>
+      <c r="J247" s="6" t="n">
+        <v>18649</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="5" t="inlineStr">
@@ -8579,6 +10786,15 @@
       <c r="G248" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H248" s="6" t="n">
+        <v>76000</v>
+      </c>
+      <c r="I248" s="6" t="n">
+        <v>36539</v>
+      </c>
+      <c r="J248" s="6" t="n">
+        <v>14893</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
@@ -8612,6 +10828,15 @@
       <c r="G249" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H249" s="6" t="n">
+        <v>40800</v>
+      </c>
+      <c r="I249" s="6" t="n">
+        <v>19428</v>
+      </c>
+      <c r="J249" s="6" t="n">
+        <v>6216</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="5" t="inlineStr">
@@ -8645,6 +10870,15 @@
       <c r="G250" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H250" s="6" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I250" s="6" t="n">
+        <v>19048</v>
+      </c>
+      <c r="J250" s="6" t="n">
+        <v>5471</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="5" t="inlineStr">
@@ -8678,6 +10912,15 @@
       <c r="G251" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H251" s="6" t="n">
+        <v>36000</v>
+      </c>
+      <c r="I251" s="6" t="n">
+        <v>17143</v>
+      </c>
+      <c r="J251" s="6" t="n">
+        <v>5064</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="5" t="inlineStr">
@@ -8711,6 +10954,15 @@
       <c r="G252" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H252" s="6" t="n">
+        <v>34000</v>
+      </c>
+      <c r="I252" s="6" t="n">
+        <v>16190</v>
+      </c>
+      <c r="J252" s="6" t="n">
+        <v>5593</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
@@ -8744,6 +10996,15 @@
       <c r="G253" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H253" s="6" t="n">
+        <v>33000</v>
+      </c>
+      <c r="I253" s="6" t="n">
+        <v>15714</v>
+      </c>
+      <c r="J253" s="6" t="n">
+        <v>6391</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
@@ -8777,6 +11038,15 @@
       <c r="G254" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H254" s="6" t="n">
+        <v>37500</v>
+      </c>
+      <c r="I254" s="6" t="n">
+        <v>17857</v>
+      </c>
+      <c r="J254" s="6" t="n">
+        <v>6139</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
@@ -8810,6 +11080,15 @@
       <c r="G255" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H255" s="6" t="n">
+        <v>65000</v>
+      </c>
+      <c r="I255" s="6" t="n">
+        <v>34210</v>
+      </c>
+      <c r="J255" s="6" t="n">
+        <v>17066</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
@@ -8843,6 +11122,15 @@
       <c r="G256" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H256" s="6" t="n">
+        <v>19800</v>
+      </c>
+      <c r="I256" s="6" t="n">
+        <v>9429</v>
+      </c>
+      <c r="J256" s="6" t="n">
+        <v>2477</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
@@ -8876,6 +11164,15 @@
       <c r="G257" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H257" s="6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I257" s="6" t="n">
+        <v>3810</v>
+      </c>
+      <c r="J257" s="6" t="n">
+        <v>1186</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
@@ -8909,11 +11206,20 @@
       <c r="G258" s="5" t="b">
         <v>1</v>
       </c>
+      <c r="H258" s="6" t="n">
+        <v>2100</v>
+      </c>
+      <c r="I258" s="6" t="n">
+        <v>1010</v>
+      </c>
+      <c r="J258" s="6" t="n">
+        <v>413</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8925,7 +11231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8934,6 +11240,9 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8946,7 +11255,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>These franchises carry real stock but the FW27 plan hasn't fixed an exit season yet ("REVIEW"). Not ranked above -- ranking these would mean guessing a business decision that hasn't been made (REG-INV-010). Sorted by units in stock, descending.</t>
+          <t>These franchises carry real stock but the FW27 plan hasn't fixed an exit season yet ("REVIEW"). Not ranked above -- ranking these would mean guessing a business decision that hasn't been made (REG-INV-010). Sorted by units in stock, descending. Value columns per REG-INV-014: Retail/Wholesale Value = units x the FW27 plan's own Target RRP/WP for that franchise; Est. Cost Value = units x Landed Cost RECONSTRUCTED as WP x (1-GM0%) since the plan's own Landed Cost field is broken (#ERROR!, REG-INV-011). One planned price per franchise applied uniformly across all sizes/colors in stock -- not a per-SKU actual. Target RRP is a planned price, not realized/discounted revenue -- read Retail Value as a ceiling, not expected recovery.</t>
         </is>
       </c>
     </row>
@@ -8981,6 +11290,21 @@
           <t>Active?</t>
         </is>
       </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Retail Value (RRP, SEK)</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Wholesale Value (WP, SEK)</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Est. Cost Value (SEK)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -9005,6 +11329,15 @@
       <c r="F6" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G6" s="6" t="n">
+        <v>5107500</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2455516</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>923164</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -9029,6 +11362,15 @@
       <c r="F7" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G7" s="6" t="n">
+        <v>5194200</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>2473431</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>792706</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -9053,6 +11395,15 @@
       <c r="F8" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G8" s="6" t="n">
+        <v>5210000</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>2480960</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>691388</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -9077,6 +11428,15 @@
       <c r="F9" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G9" s="6" t="n">
+        <v>4727500</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>2251198</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>664762</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -9101,6 +11461,15 @@
       <c r="F10" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G10" s="6" t="n">
+        <v>3667500</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1746434</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>584526</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -9125,6 +11494,15 @@
       <c r="F11" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G11" s="6" t="n">
+        <v>1885500</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>906486</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>303792</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -9149,6 +11527,15 @@
       <c r="F12" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G12" s="6" t="n">
+        <v>2842000</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1353330</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>369805</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -9173,6 +11560,15 @@
       <c r="F13" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G13" s="6" t="n">
+        <v>2385000</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1135718</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>367471</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -9197,6 +11593,15 @@
       <c r="F14" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G14" s="6" t="n">
+        <v>1938200</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>922953</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>276026</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -9221,6 +11626,15 @@
       <c r="F15" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G15" s="6" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>785715</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>238208</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -9245,6 +11659,15 @@
       <c r="F16" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G16" s="6" t="n">
+        <v>1870000</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>890479</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>311108</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -9269,6 +11692,15 @@
       <c r="F17" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G17" s="6" t="n">
+        <v>2485000</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>1183336</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>469473</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -9293,6 +11725,15 @@
       <c r="F18" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G18" s="6" t="n">
+        <v>2471000</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1176669</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>443777</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -9317,6 +11758,15 @@
       <c r="F19" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G19" s="6" t="n">
+        <v>1366000</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>650476</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>191015</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -9341,6 +11791,15 @@
       <c r="F20" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G20" s="6" t="n">
+        <v>1102200</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>524858</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>148306</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -9365,6 +11824,15 @@
       <c r="F21" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G21" s="6" t="n">
+        <v>1288000</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>613332</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>159266</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -9389,6 +11857,15 @@
       <c r="F22" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G22" s="6" t="n">
+        <v>1696000</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>807618</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>351102</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -9413,6 +11890,15 @@
       <c r="F23" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G23" s="6" t="n">
+        <v>806000</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>383809</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>124128</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -9437,6 +11923,15 @@
       <c r="F24" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G24" s="6" t="n">
+        <v>722000</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>343809</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>112979</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -9461,6 +11956,15 @@
       <c r="F25" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G25" s="6" t="n">
+        <v>812700</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>386999</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>139170</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -9485,6 +11989,15 @@
       <c r="F26" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G26" s="6" t="n">
+        <v>282150</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>134357</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>53715</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -9509,6 +12022,15 @@
       <c r="F27" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G27" s="6" t="n">
+        <v>692500</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>329763</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>123503</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -9533,6 +12055,15 @@
       <c r="F28" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G28" s="6" t="n">
+        <v>1064000</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>506666</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>205203</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -9557,6 +12088,15 @@
       <c r="F29" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G29" s="6" t="n">
+        <v>683100</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>325285</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>104135</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -9581,6 +12121,15 @@
       <c r="F30" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G30" s="6" t="n">
+        <v>430000</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>204762</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>61041</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -9605,6 +12154,15 @@
       <c r="F31" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G31" s="6" t="n">
+        <v>254800</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>122501</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>45556</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -9629,6 +12187,15 @@
       <c r="F32" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G32" s="6" t="n">
+        <v>650000</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>312500</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>148199</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -9653,6 +12220,15 @@
       <c r="F33" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G33" s="6" t="n">
+        <v>363000</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>174519</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>81992</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -9677,6 +12253,15 @@
       <c r="F34" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G34" s="6" t="n">
+        <v>399000</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>191827</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>95012</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -9701,11 +12286,20 @@
       <c r="F35" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="G35" s="6" t="n">
+        <v>212500</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>102164</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>50028</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19463,4 +22057,442 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Inventory Value by Priority Tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sums Sheets 2-3's value columns per tier (REG-INV-014). "Not on FW27 Plan" (Sheet 4) has no price source and is shown separately below with units only, not zero SEK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Priority Tier</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Retail Value (RRP, SEK)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Wholesale Value (WP, SEK)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Est. Cost Value (SEK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Exiting FW27 (last season offered)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>21941</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>56466900</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>26892731</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>11971993</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Exiting FW27 or SS28 (ambiguous — treat as near-term)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>5102</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>8052600</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>3834557</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1353679</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>One season left (exits after SS28)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>4702</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>25705700</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>12245383</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>6124528</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Long runway (continues through FW28+)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>345898</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>630702650</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>301891021</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>117671489</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Pending Review (exit season = REVIEW)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>23130</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>54257350</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>25877467</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>8630556</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Not on FW27 Plan (Sheet 4 — no price source)</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>127190</v>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Inventory Value by Activity (merchandising category, column AN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Same Sheets 2-3 rows, grouped by the FW27 plan's "NEW MAPPING: Activity" field (column AN) instead of tier. Sorted by Retail Value, descending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Retail Value (RRP, SEK)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Wholesale Value (WP, SEK)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Est. Cost Value (SEK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Active Essentials</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>133516</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>231030400</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>110094359</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>41785944</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Daily Essentials</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>129806</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>180271250</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>86225584</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>33036293</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Trekking</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>34784</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>76087600</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>36319093</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>14545337</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Day Hiking</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>30148</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>75590600</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>36236938</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>14063535</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Trail Run &amp; Fast Hike</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>27151</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>74729100</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>35656190</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>16097165</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>23130</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>54257350</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>25877467</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>8630556</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Mountaineering</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>6164</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>33084700</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>15754621</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>7592625</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Hiking</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>8718</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>23329200</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>11109139</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>3901056</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Freeride</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>4542</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>20693500</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>10557526</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>4860882</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>All Mountain</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>2128</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>3386900</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>1612816</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>689607</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Ski Touring</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>686</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>2724600</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>1297428</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>549244</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/inventory_analysis/Project_Bob_Sell_Down_Priority_11092026.xlsx
+++ b/data/inventory_analysis/Project_Bob_Sell_Down_Priority_11092026.xlsx
@@ -74,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -86,6 +86,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -488,7 +489,7 @@
     <row r="9" ht="75" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Value estimate (REG-INV-014, Sheets 2-3 only -- 400,773 of 527,963 total units, 76%): 775,185,200 SEK at Target RRP, 370,741,160 SEK at WP, 145,752,246 SEK estimated landed cost (reconstructed -- see Sheet 2's own note and REG-INV-014). Sheet 4 (Not on FW27 Plan) has no price source anywhere in this data and is NOT included in these totals -- not zero, just unknown. See Sheet 6 for the breakdown by priority tier and by Activity.</t>
+          <t>Value estimate (Sheets 2-3, REG-INV-014 -- 400,773 of 527,963 total units, 76%): 775,185,200 SEK at Target RRP, 370,741,160 SEK at WP, 145,752,246 SEK estimated landed cost (reconstructed -- see Sheet 2's own note and REG-INV-014). Sheet 4 (Not on FW27 Plan) has no RRP/cost source at all, but 100,966 of its 127,190 units get a fallback Historical ASP value from actual FY25 sales (75,897,156 SEK, REG-INV-015) -- the remaining 26,224 units have no price source of any kind. See Sheet 6 for the breakdown by priority tier and by Activity.</t>
         </is>
       </c>
     </row>
@@ -12311,7 +12312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F405"/>
+  <dimension ref="A1:H405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -12320,6 +12321,8 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12332,7 +12335,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>NOT safe to blanket-label "retired before FW27" (REG-INV-012): cross-checked against SS27 (the season immediately before FW27) below. 54 franchises (41,566 units) were still Active there and need a real merch check -- likely explanations include a genuine drop, but also a name change too large for Base+Gender matching to catch (e.g. "Rosson Softshell Hood" -&gt; "Rosson Mid II Hood", confirmed both exist, neither name matches the other). Rows with "SS27 Active? = False" or blank (not in SS27 either) are the safer default for "likely already retired." Sorted by units in stock, descending.</t>
+          <t>NOT safe to blanket-label "retired before FW27" (REG-INV-012): cross-checked against SS27 (the season immediately before FW27) below. 54 franchises (41,566 units) were still Active there and need a real merch check -- likely explanations include a genuine drop, but also a name change too large for Base+Gender matching to catch (e.g. "Rosson Softshell Hood" -&gt; "Rosson Mid II Hood", confirmed both exist, neither name matches the other). Rows with "SS27 Active? = False" or blank (not in SS27 either) are the safer default for "likely already retired." Value columns (REG-INV-015) are a DIFFERENT basis from Sheets 2-3's Target-RRP value: Historical ASP = that franchise's actual FY25 Sales_2025 / Units_2025 from the SS26 tiering workbook, gated by the same 50,000 SEK/year reliability floor used everywhere in that workstream (REG-004) -- blank where unreliable or the franchise isn't in that workbook at all. A REALIZED average price, not a planned one, but still no cost/margin figure exists for this bucket. Sorted by units in stock, descending.</t>
         </is>
       </c>
     </row>
@@ -12367,6 +12370,16 @@
           <t>SS27 Status</t>
         </is>
       </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Historical ASP (SEK/unit)</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Est. Value at Historical ASP (SEK)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -12389,6 +12402,12 @@
       </c>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
+      <c r="G6" s="7" t="n">
+        <v>527.84</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2605440</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -12411,6 +12430,12 @@
       </c>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
+      <c r="G7" s="7" t="n">
+        <v>83.45999999999999</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>313234</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -12433,6 +12458,12 @@
       </c>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
+      <c r="G8" s="7" t="n">
+        <v>1423.24</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>3919612</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -12461,6 +12492,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G9" s="7" t="n">
+        <v>278.86</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>735906</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -12489,6 +12526,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G10" s="7" t="n">
+        <v>1138.6</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>2874956</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -12511,6 +12554,12 @@
       </c>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
+      <c r="G11" s="7" t="n">
+        <v>201.88</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>492378</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -12539,6 +12588,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G12" s="7" t="n">
+        <v>678.77</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1535367</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -12567,6 +12622,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G13" s="7" t="n">
+        <v>686.98</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1338228</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -12589,6 +12650,12 @@
       </c>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
+      <c r="G14" s="7" t="n">
+        <v>569.12</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1098398</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -12617,6 +12684,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G15" s="7" t="n">
+        <v>346.21</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>659183</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -12667,6 +12740,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G17" s="7" t="n">
+        <v>361.47</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>626436</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -12695,6 +12774,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G18" s="7" t="n">
+        <v>366.71</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>597003</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -12723,6 +12808,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G19" s="7" t="n">
+        <v>479.71</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>753629</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -12751,6 +12842,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G20" s="7" t="n">
+        <v>1171.85</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>1826910</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -12779,6 +12876,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G21" s="7" t="n">
+        <v>299.8</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>435313</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -12801,6 +12904,12 @@
       </c>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
+      <c r="G22" s="7" t="n">
+        <v>384.33</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>556899</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -12823,6 +12932,12 @@
       </c>
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
+      <c r="G23" s="7" t="n">
+        <v>388.26</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>556375</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -12911,6 +13026,12 @@
       </c>
       <c r="E27" s="5" t="n"/>
       <c r="F27" s="5" t="n"/>
+      <c r="G27" s="7" t="n">
+        <v>734.4400000000001</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>907030</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -12939,6 +13060,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G28" s="7" t="n">
+        <v>383.1</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>469301</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -12961,6 +13088,12 @@
       </c>
       <c r="E29" s="5" t="n"/>
       <c r="F29" s="5" t="n"/>
+      <c r="G29" s="7" t="n">
+        <v>577.17</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>700684</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -13011,6 +13144,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G31" s="7" t="n">
+        <v>669.01</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>761329</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -13039,6 +13178,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G32" s="7" t="n">
+        <v>485.79</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>540688</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -13089,6 +13234,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G34" s="7" t="n">
+        <v>355.33</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>368123</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -13111,6 +13262,12 @@
       </c>
       <c r="E35" s="5" t="n"/>
       <c r="F35" s="5" t="n"/>
+      <c r="G35" s="7" t="n">
+        <v>942.14</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>975110</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -13167,6 +13324,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G37" s="7" t="n">
+        <v>347.62</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>344490</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -13195,6 +13358,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G38" s="7" t="n">
+        <v>410.85</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>393182</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -13217,6 +13386,12 @@
       </c>
       <c r="E39" s="5" t="n"/>
       <c r="F39" s="5" t="n"/>
+      <c r="G39" s="7" t="n">
+        <v>121.48</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>115527</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -13239,6 +13414,12 @@
       </c>
       <c r="E40" s="5" t="n"/>
       <c r="F40" s="5" t="n"/>
+      <c r="G40" s="7" t="n">
+        <v>683.21</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>642219</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -13267,6 +13448,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G41" s="7" t="n">
+        <v>991.03</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>918687</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -13311,6 +13498,12 @@
       </c>
       <c r="E43" s="5" t="n"/>
       <c r="F43" s="5" t="n"/>
+      <c r="G43" s="7" t="n">
+        <v>914.89</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>801446</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -13361,6 +13554,12 @@
       </c>
       <c r="E45" s="5" t="n"/>
       <c r="F45" s="5" t="n"/>
+      <c r="G45" s="7" t="n">
+        <v>1199.45</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>1041118</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -13383,6 +13582,12 @@
       </c>
       <c r="E46" s="5" t="n"/>
       <c r="F46" s="5" t="n"/>
+      <c r="G46" s="7" t="n">
+        <v>755.35</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>653374</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -13405,6 +13610,12 @@
       </c>
       <c r="E47" s="5" t="n"/>
       <c r="F47" s="5" t="n"/>
+      <c r="G47" s="7" t="n">
+        <v>410.03</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>353033</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -13433,6 +13644,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G48" s="7" t="n">
+        <v>692.1900000000001</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>584212</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -13455,6 +13672,12 @@
       </c>
       <c r="E49" s="5" t="n"/>
       <c r="F49" s="5" t="n"/>
+      <c r="G49" s="7" t="n">
+        <v>248.19</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>205498</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -13483,6 +13706,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G50" s="7" t="n">
+        <v>278.03</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>222148</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -13527,6 +13756,12 @@
       </c>
       <c r="E52" s="5" t="n"/>
       <c r="F52" s="5" t="n"/>
+      <c r="G52" s="7" t="n">
+        <v>563.72</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>439138</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -13577,6 +13812,12 @@
       </c>
       <c r="E54" s="5" t="n"/>
       <c r="F54" s="5" t="n"/>
+      <c r="G54" s="7" t="n">
+        <v>1116.02</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>857102</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -13621,6 +13862,12 @@
       </c>
       <c r="E56" s="5" t="n"/>
       <c r="F56" s="5" t="n"/>
+      <c r="G56" s="7" t="n">
+        <v>292.19</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>221771</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -13643,6 +13890,12 @@
       </c>
       <c r="E57" s="5" t="n"/>
       <c r="F57" s="5" t="n"/>
+      <c r="G57" s="7" t="n">
+        <v>607.77</v>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>458256</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -13671,6 +13924,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G58" s="7" t="n">
+        <v>361.91</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>272153</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -13693,6 +13952,12 @@
       </c>
       <c r="E59" s="5" t="n"/>
       <c r="F59" s="5" t="n"/>
+      <c r="G59" s="7" t="n">
+        <v>2816.33</v>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>2070003</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -13715,6 +13980,12 @@
       </c>
       <c r="E60" s="5" t="n"/>
       <c r="F60" s="5" t="n"/>
+      <c r="G60" s="7" t="n">
+        <v>349.27</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>256364</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -13803,6 +14074,12 @@
       </c>
       <c r="E64" s="5" t="n"/>
       <c r="F64" s="5" t="n"/>
+      <c r="G64" s="7" t="n">
+        <v>412.06</v>
+      </c>
+      <c r="H64" s="6" t="n">
+        <v>287621</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -13831,6 +14108,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G65" s="7" t="n">
+        <v>305.74</v>
+      </c>
+      <c r="H65" s="6" t="n">
+        <v>210962</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -13853,6 +14136,12 @@
       </c>
       <c r="E66" s="5" t="n"/>
       <c r="F66" s="5" t="n"/>
+      <c r="G66" s="7" t="n">
+        <v>339.14</v>
+      </c>
+      <c r="H66" s="6" t="n">
+        <v>222134</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -13881,6 +14170,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G67" s="7" t="n">
+        <v>178.2</v>
+      </c>
+      <c r="H67" s="6" t="n">
+        <v>114940</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -13903,6 +14198,12 @@
       </c>
       <c r="E68" s="5" t="n"/>
       <c r="F68" s="5" t="n"/>
+      <c r="G68" s="7" t="n">
+        <v>4456.65</v>
+      </c>
+      <c r="H68" s="6" t="n">
+        <v>2865628</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -13947,6 +14248,12 @@
       </c>
       <c r="E70" s="5" t="n"/>
       <c r="F70" s="5" t="n"/>
+      <c r="G70" s="7" t="n">
+        <v>416.98</v>
+      </c>
+      <c r="H70" s="6" t="n">
+        <v>263950</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -13969,6 +14276,12 @@
       </c>
       <c r="E71" s="5" t="n"/>
       <c r="F71" s="5" t="n"/>
+      <c r="G71" s="7" t="n">
+        <v>179.58</v>
+      </c>
+      <c r="H71" s="6" t="n">
+        <v>113137</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -13991,6 +14304,12 @@
       </c>
       <c r="E72" s="5" t="n"/>
       <c r="F72" s="5" t="n"/>
+      <c r="G72" s="7" t="n">
+        <v>701.52</v>
+      </c>
+      <c r="H72" s="6" t="n">
+        <v>439149</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -14013,6 +14332,12 @@
       </c>
       <c r="E73" s="5" t="n"/>
       <c r="F73" s="5" t="n"/>
+      <c r="G73" s="7" t="n">
+        <v>422.09</v>
+      </c>
+      <c r="H73" s="6" t="n">
+        <v>259584</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -14035,6 +14360,12 @@
       </c>
       <c r="E74" s="5" t="n"/>
       <c r="F74" s="5" t="n"/>
+      <c r="G74" s="7" t="n">
+        <v>1164.44</v>
+      </c>
+      <c r="H74" s="6" t="n">
+        <v>702159</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -14057,6 +14388,12 @@
       </c>
       <c r="E75" s="5" t="n"/>
       <c r="F75" s="5" t="n"/>
+      <c r="G75" s="7" t="n">
+        <v>323.54</v>
+      </c>
+      <c r="H75" s="6" t="n">
+        <v>195095</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -14079,6 +14416,12 @@
       </c>
       <c r="E76" s="5" t="n"/>
       <c r="F76" s="5" t="n"/>
+      <c r="G76" s="7" t="n">
+        <v>657.24</v>
+      </c>
+      <c r="H76" s="6" t="n">
+        <v>391059</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -14101,6 +14444,12 @@
       </c>
       <c r="E77" s="5" t="n"/>
       <c r="F77" s="5" t="n"/>
+      <c r="G77" s="7" t="n">
+        <v>198.69</v>
+      </c>
+      <c r="H77" s="6" t="n">
+        <v>115839</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -14145,6 +14494,12 @@
       </c>
       <c r="E79" s="5" t="n"/>
       <c r="F79" s="5" t="n"/>
+      <c r="G79" s="7" t="n">
+        <v>900.9299999999999</v>
+      </c>
+      <c r="H79" s="6" t="n">
+        <v>515331</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -14173,6 +14528,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G80" s="7" t="n">
+        <v>193.17</v>
+      </c>
+      <c r="H80" s="6" t="n">
+        <v>109334</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -14195,6 +14556,12 @@
       </c>
       <c r="E81" s="5" t="n"/>
       <c r="F81" s="5" t="n"/>
+      <c r="G81" s="7" t="n">
+        <v>337.21</v>
+      </c>
+      <c r="H81" s="6" t="n">
+        <v>189510</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -14223,6 +14590,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G82" s="7" t="n">
+        <v>185.73</v>
+      </c>
+      <c r="H82" s="6" t="n">
+        <v>104011</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -14295,6 +14668,12 @@
           <t>NEW</t>
         </is>
       </c>
+      <c r="G85" s="7" t="n">
+        <v>485.64</v>
+      </c>
+      <c r="H85" s="6" t="n">
+        <v>254961</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -14345,6 +14724,12 @@
       </c>
       <c r="E87" s="5" t="n"/>
       <c r="F87" s="5" t="n"/>
+      <c r="G87" s="7" t="n">
+        <v>495.54</v>
+      </c>
+      <c r="H87" s="6" t="n">
+        <v>251732</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -14367,6 +14752,12 @@
       </c>
       <c r="E88" s="5" t="n"/>
       <c r="F88" s="5" t="n"/>
+      <c r="G88" s="7" t="n">
+        <v>285.34</v>
+      </c>
+      <c r="H88" s="6" t="n">
+        <v>142385</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -14389,6 +14780,12 @@
       </c>
       <c r="E89" s="5" t="n"/>
       <c r="F89" s="5" t="n"/>
+      <c r="G89" s="7" t="n">
+        <v>690.71</v>
+      </c>
+      <c r="H89" s="6" t="n">
+        <v>343283</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -14417,6 +14814,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G90" s="7" t="n">
+        <v>278.52</v>
+      </c>
+      <c r="H90" s="6" t="n">
+        <v>136752</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -14439,6 +14842,12 @@
       </c>
       <c r="E91" s="5" t="n"/>
       <c r="F91" s="5" t="n"/>
+      <c r="G91" s="7" t="n">
+        <v>774.67</v>
+      </c>
+      <c r="H91" s="6" t="n">
+        <v>378041</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -14483,6 +14892,12 @@
       </c>
       <c r="E93" s="5" t="n"/>
       <c r="F93" s="5" t="n"/>
+      <c r="G93" s="7" t="n">
+        <v>1991.33</v>
+      </c>
+      <c r="H93" s="6" t="n">
+        <v>937914</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -14505,6 +14920,12 @@
       </c>
       <c r="E94" s="5" t="n"/>
       <c r="F94" s="5" t="n"/>
+      <c r="G94" s="7" t="n">
+        <v>460.27</v>
+      </c>
+      <c r="H94" s="6" t="n">
+        <v>206201</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
@@ -14527,6 +14948,12 @@
       </c>
       <c r="E95" s="5" t="n"/>
       <c r="F95" s="5" t="n"/>
+      <c r="G95" s="7" t="n">
+        <v>779.24</v>
+      </c>
+      <c r="H95" s="6" t="n">
+        <v>347540</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
@@ -14549,6 +14976,12 @@
       </c>
       <c r="E96" s="5" t="n"/>
       <c r="F96" s="5" t="n"/>
+      <c r="G96" s="7" t="n">
+        <v>885.0599999999999</v>
+      </c>
+      <c r="H96" s="6" t="n">
+        <v>394738</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
@@ -14571,6 +15004,12 @@
       </c>
       <c r="E97" s="5" t="n"/>
       <c r="F97" s="5" t="n"/>
+      <c r="G97" s="7" t="n">
+        <v>711.12</v>
+      </c>
+      <c r="H97" s="6" t="n">
+        <v>315739</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -14593,6 +15032,12 @@
       </c>
       <c r="E98" s="5" t="n"/>
       <c r="F98" s="5" t="n"/>
+      <c r="G98" s="7" t="n">
+        <v>2578.71</v>
+      </c>
+      <c r="H98" s="6" t="n">
+        <v>1129475</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -14615,6 +15060,12 @@
       </c>
       <c r="E99" s="5" t="n"/>
       <c r="F99" s="5" t="n"/>
+      <c r="G99" s="7" t="n">
+        <v>341.99</v>
+      </c>
+      <c r="H99" s="6" t="n">
+        <v>143293</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
@@ -14665,6 +15116,12 @@
       </c>
       <c r="E101" s="5" t="n"/>
       <c r="F101" s="5" t="n"/>
+      <c r="G101" s="7" t="n">
+        <v>305.3</v>
+      </c>
+      <c r="H101" s="6" t="n">
+        <v>126701</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
@@ -14687,6 +15144,12 @@
       </c>
       <c r="E102" s="5" t="n"/>
       <c r="F102" s="5" t="n"/>
+      <c r="G102" s="7" t="n">
+        <v>142.38</v>
+      </c>
+      <c r="H102" s="6" t="n">
+        <v>57520</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
@@ -14709,6 +15172,12 @@
       </c>
       <c r="E103" s="5" t="n"/>
       <c r="F103" s="5" t="n"/>
+      <c r="G103" s="7" t="n">
+        <v>839.89</v>
+      </c>
+      <c r="H103" s="6" t="n">
+        <v>320837</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -14737,6 +15206,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G104" s="7" t="n">
+        <v>503.74</v>
+      </c>
+      <c r="H104" s="6" t="n">
+        <v>191926</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -14787,6 +15262,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G106" s="7" t="n">
+        <v>596.0700000000001</v>
+      </c>
+      <c r="H106" s="6" t="n">
+        <v>221737</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
@@ -14837,6 +15318,12 @@
       </c>
       <c r="E108" s="5" t="n"/>
       <c r="F108" s="5" t="n"/>
+      <c r="G108" s="7" t="n">
+        <v>32137.95</v>
+      </c>
+      <c r="H108" s="6" t="n">
+        <v>11923180</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
@@ -14887,6 +15374,12 @@
       </c>
       <c r="E110" s="5" t="n"/>
       <c r="F110" s="5" t="n"/>
+      <c r="G110" s="7" t="n">
+        <v>343.63</v>
+      </c>
+      <c r="H110" s="6" t="n">
+        <v>124394</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
@@ -14937,6 +15430,12 @@
       </c>
       <c r="E112" s="5" t="n"/>
       <c r="F112" s="5" t="n"/>
+      <c r="G112" s="7" t="n">
+        <v>1020.75</v>
+      </c>
+      <c r="H112" s="6" t="n">
+        <v>366451</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
@@ -14981,6 +15480,12 @@
       </c>
       <c r="E114" s="5" t="n"/>
       <c r="F114" s="5" t="n"/>
+      <c r="G114" s="7" t="n">
+        <v>294.6</v>
+      </c>
+      <c r="H114" s="6" t="n">
+        <v>104877</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
@@ -15031,6 +15536,12 @@
       </c>
       <c r="E116" s="5" t="n"/>
       <c r="F116" s="5" t="n"/>
+      <c r="G116" s="7" t="n">
+        <v>387.51</v>
+      </c>
+      <c r="H116" s="6" t="n">
+        <v>134465</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
@@ -15053,6 +15564,12 @@
       </c>
       <c r="E117" s="5" t="n"/>
       <c r="F117" s="5" t="n"/>
+      <c r="G117" s="7" t="n">
+        <v>265.66</v>
+      </c>
+      <c r="H117" s="6" t="n">
+        <v>91918</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -15075,6 +15592,12 @@
       </c>
       <c r="E118" s="5" t="n"/>
       <c r="F118" s="5" t="n"/>
+      <c r="G118" s="7" t="n">
+        <v>520.67</v>
+      </c>
+      <c r="H118" s="6" t="n">
+        <v>178070</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
@@ -15103,6 +15626,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G119" s="7" t="n">
+        <v>214.43</v>
+      </c>
+      <c r="H119" s="6" t="n">
+        <v>72905</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
@@ -15159,6 +15688,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G121" s="7" t="n">
+        <v>520.8099999999999</v>
+      </c>
+      <c r="H121" s="6" t="n">
+        <v>171867</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
@@ -15181,6 +15716,12 @@
       </c>
       <c r="E122" s="5" t="n"/>
       <c r="F122" s="5" t="n"/>
+      <c r="G122" s="7" t="n">
+        <v>425.52</v>
+      </c>
+      <c r="H122" s="6" t="n">
+        <v>139145</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
@@ -15247,6 +15788,12 @@
       </c>
       <c r="E125" s="5" t="n"/>
       <c r="F125" s="5" t="n"/>
+      <c r="G125" s="7" t="n">
+        <v>148.46</v>
+      </c>
+      <c r="H125" s="6" t="n">
+        <v>44091</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
@@ -15275,6 +15822,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G126" s="7" t="n">
+        <v>306.12</v>
+      </c>
+      <c r="H126" s="6" t="n">
+        <v>90611</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
@@ -15303,6 +15856,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G127" s="7" t="n">
+        <v>640.6</v>
+      </c>
+      <c r="H127" s="6" t="n">
+        <v>188976</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
@@ -15325,6 +15884,12 @@
       </c>
       <c r="E128" s="5" t="n"/>
       <c r="F128" s="5" t="n"/>
+      <c r="G128" s="7" t="n">
+        <v>473.62</v>
+      </c>
+      <c r="H128" s="6" t="n">
+        <v>137350</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
@@ -15347,6 +15912,12 @@
       </c>
       <c r="E129" s="5" t="n"/>
       <c r="F129" s="5" t="n"/>
+      <c r="G129" s="7" t="n">
+        <v>291.61</v>
+      </c>
+      <c r="H129" s="6" t="n">
+        <v>84568</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
@@ -15369,6 +15940,12 @@
       </c>
       <c r="E130" s="5" t="n"/>
       <c r="F130" s="5" t="n"/>
+      <c r="G130" s="7" t="n">
+        <v>261.86</v>
+      </c>
+      <c r="H130" s="6" t="n">
+        <v>73845</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
@@ -15391,6 +15968,12 @@
       </c>
       <c r="E131" s="5" t="n"/>
       <c r="F131" s="5" t="n"/>
+      <c r="G131" s="7" t="n">
+        <v>912.63</v>
+      </c>
+      <c r="H131" s="6" t="n">
+        <v>250974</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
@@ -15441,6 +16024,12 @@
       </c>
       <c r="E133" s="5" t="n"/>
       <c r="F133" s="5" t="n"/>
+      <c r="G133" s="7" t="n">
+        <v>814.24</v>
+      </c>
+      <c r="H133" s="6" t="n">
+        <v>214960</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
@@ -15463,6 +16052,12 @@
       </c>
       <c r="E134" s="5" t="n"/>
       <c r="F134" s="5" t="n"/>
+      <c r="G134" s="7" t="n">
+        <v>407.13</v>
+      </c>
+      <c r="H134" s="6" t="n">
+        <v>106260</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
@@ -15485,6 +16080,12 @@
       </c>
       <c r="E135" s="5" t="n"/>
       <c r="F135" s="5" t="n"/>
+      <c r="G135" s="7" t="n">
+        <v>478.15</v>
+      </c>
+      <c r="H135" s="6" t="n">
+        <v>123362</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
@@ -15513,6 +16114,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G136" s="7" t="n">
+        <v>190.8</v>
+      </c>
+      <c r="H136" s="6" t="n">
+        <v>48655</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
@@ -15535,6 +16142,12 @@
       </c>
       <c r="E137" s="5" t="n"/>
       <c r="F137" s="5" t="n"/>
+      <c r="G137" s="7" t="n">
+        <v>342.87</v>
+      </c>
+      <c r="H137" s="6" t="n">
+        <v>86060</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
@@ -15557,6 +16170,12 @@
       </c>
       <c r="E138" s="5" t="n"/>
       <c r="F138" s="5" t="n"/>
+      <c r="G138" s="7" t="n">
+        <v>541.4</v>
+      </c>
+      <c r="H138" s="6" t="n">
+        <v>135350</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
@@ -15607,6 +16226,12 @@
       </c>
       <c r="E140" s="5" t="n"/>
       <c r="F140" s="5" t="n"/>
+      <c r="G140" s="7" t="n">
+        <v>752.59</v>
+      </c>
+      <c r="H140" s="6" t="n">
+        <v>186642</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
@@ -15657,6 +16282,12 @@
       </c>
       <c r="E142" s="5" t="n"/>
       <c r="F142" s="5" t="n"/>
+      <c r="G142" s="7" t="n">
+        <v>716.0700000000001</v>
+      </c>
+      <c r="H142" s="6" t="n">
+        <v>172574</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
@@ -15679,6 +16310,12 @@
       </c>
       <c r="E143" s="5" t="n"/>
       <c r="F143" s="5" t="n"/>
+      <c r="G143" s="7" t="n">
+        <v>841.8</v>
+      </c>
+      <c r="H143" s="6" t="n">
+        <v>202032</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
@@ -15723,6 +16360,12 @@
       </c>
       <c r="E145" s="5" t="n"/>
       <c r="F145" s="5" t="n"/>
+      <c r="G145" s="7" t="n">
+        <v>919.78</v>
+      </c>
+      <c r="H145" s="6" t="n">
+        <v>216149</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
@@ -15745,6 +16388,12 @@
       </c>
       <c r="E146" s="5" t="n"/>
       <c r="F146" s="5" t="n"/>
+      <c r="G146" s="7" t="n">
+        <v>505.59</v>
+      </c>
+      <c r="H146" s="6" t="n">
+        <v>118309</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
@@ -15767,6 +16416,12 @@
       </c>
       <c r="E147" s="5" t="n"/>
       <c r="F147" s="5" t="n"/>
+      <c r="G147" s="7" t="n">
+        <v>368.39</v>
+      </c>
+      <c r="H147" s="6" t="n">
+        <v>85466</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
@@ -15789,6 +16444,12 @@
       </c>
       <c r="E148" s="5" t="n"/>
       <c r="F148" s="5" t="n"/>
+      <c r="G148" s="7" t="n">
+        <v>148.4</v>
+      </c>
+      <c r="H148" s="6" t="n">
+        <v>33242</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
@@ -15811,6 +16472,12 @@
       </c>
       <c r="E149" s="5" t="n"/>
       <c r="F149" s="5" t="n"/>
+      <c r="G149" s="7" t="n">
+        <v>4226.17</v>
+      </c>
+      <c r="H149" s="6" t="n">
+        <v>921306</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
@@ -15855,6 +16522,12 @@
       </c>
       <c r="E151" s="5" t="n"/>
       <c r="F151" s="5" t="n"/>
+      <c r="G151" s="7" t="n">
+        <v>1514.56</v>
+      </c>
+      <c r="H151" s="6" t="n">
+        <v>316544</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
@@ -15899,6 +16572,12 @@
       </c>
       <c r="E153" s="5" t="n"/>
       <c r="F153" s="5" t="n"/>
+      <c r="G153" s="7" t="n">
+        <v>334.83</v>
+      </c>
+      <c r="H153" s="6" t="n">
+        <v>67970</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
@@ -15921,6 +16600,12 @@
       </c>
       <c r="E154" s="5" t="n"/>
       <c r="F154" s="5" t="n"/>
+      <c r="G154" s="7" t="n">
+        <v>669.45</v>
+      </c>
+      <c r="H154" s="6" t="n">
+        <v>133890</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
@@ -15943,6 +16628,12 @@
       </c>
       <c r="E155" s="5" t="n"/>
       <c r="F155" s="5" t="n"/>
+      <c r="G155" s="7" t="n">
+        <v>935.22</v>
+      </c>
+      <c r="H155" s="6" t="n">
+        <v>185173</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
@@ -16015,6 +16706,12 @@
       </c>
       <c r="E158" s="5" t="n"/>
       <c r="F158" s="5" t="n"/>
+      <c r="G158" s="7" t="n">
+        <v>781.55</v>
+      </c>
+      <c r="H158" s="6" t="n">
+        <v>144587</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
@@ -16043,6 +16740,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G159" s="7" t="n">
+        <v>513.4</v>
+      </c>
+      <c r="H159" s="6" t="n">
+        <v>94465</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
@@ -16065,6 +16768,12 @@
       </c>
       <c r="E160" s="5" t="n"/>
       <c r="F160" s="5" t="n"/>
+      <c r="G160" s="7" t="n">
+        <v>714.88</v>
+      </c>
+      <c r="H160" s="6" t="n">
+        <v>129393</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
@@ -16115,6 +16824,12 @@
       </c>
       <c r="E162" s="5" t="n"/>
       <c r="F162" s="5" t="n"/>
+      <c r="G162" s="7" t="n">
+        <v>506.65</v>
+      </c>
+      <c r="H162" s="6" t="n">
+        <v>87651</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
@@ -16137,6 +16852,12 @@
       </c>
       <c r="E163" s="5" t="n"/>
       <c r="F163" s="5" t="n"/>
+      <c r="G163" s="7" t="n">
+        <v>1069.1</v>
+      </c>
+      <c r="H163" s="6" t="n">
+        <v>181748</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
@@ -16159,6 +16880,12 @@
       </c>
       <c r="E164" s="5" t="n"/>
       <c r="F164" s="5" t="n"/>
+      <c r="G164" s="7" t="n">
+        <v>401.36</v>
+      </c>
+      <c r="H164" s="6" t="n">
+        <v>65823</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
@@ -16181,6 +16908,12 @@
       </c>
       <c r="E165" s="5" t="n"/>
       <c r="F165" s="5" t="n"/>
+      <c r="G165" s="7" t="n">
+        <v>4273.9</v>
+      </c>
+      <c r="H165" s="6" t="n">
+        <v>688099</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
@@ -16203,6 +16936,12 @@
       </c>
       <c r="E166" s="5" t="n"/>
       <c r="F166" s="5" t="n"/>
+      <c r="G166" s="7" t="n">
+        <v>1056.6</v>
+      </c>
+      <c r="H166" s="6" t="n">
+        <v>168000</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
@@ -16231,6 +16970,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G167" s="7" t="n">
+        <v>819.97</v>
+      </c>
+      <c r="H167" s="6" t="n">
+        <v>129555</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
@@ -16253,6 +16998,12 @@
       </c>
       <c r="E168" s="5" t="n"/>
       <c r="F168" s="5" t="n"/>
+      <c r="G168" s="7" t="n">
+        <v>492.25</v>
+      </c>
+      <c r="H168" s="6" t="n">
+        <v>76790</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
@@ -16281,6 +17032,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G169" s="7" t="n">
+        <v>774.26</v>
+      </c>
+      <c r="H169" s="6" t="n">
+        <v>120010</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
@@ -16303,6 +17060,12 @@
       </c>
       <c r="E170" s="5" t="n"/>
       <c r="F170" s="5" t="n"/>
+      <c r="G170" s="7" t="n">
+        <v>202.41</v>
+      </c>
+      <c r="H170" s="6" t="n">
+        <v>31171</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
@@ -16347,6 +17110,12 @@
       </c>
       <c r="E172" s="5" t="n"/>
       <c r="F172" s="5" t="n"/>
+      <c r="G172" s="7" t="n">
+        <v>508.32</v>
+      </c>
+      <c r="H172" s="6" t="n">
+        <v>77773</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
@@ -16369,6 +17138,12 @@
       </c>
       <c r="E173" s="5" t="n"/>
       <c r="F173" s="5" t="n"/>
+      <c r="G173" s="7" t="n">
+        <v>543.41</v>
+      </c>
+      <c r="H173" s="6" t="n">
+        <v>80967</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
@@ -16391,6 +17166,12 @@
       </c>
       <c r="E174" s="5" t="n"/>
       <c r="F174" s="5" t="n"/>
+      <c r="G174" s="7" t="n">
+        <v>421.16</v>
+      </c>
+      <c r="H174" s="6" t="n">
+        <v>62752</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
@@ -16413,6 +17194,12 @@
       </c>
       <c r="E175" s="5" t="n"/>
       <c r="F175" s="5" t="n"/>
+      <c r="G175" s="7" t="n">
+        <v>810.6799999999999</v>
+      </c>
+      <c r="H175" s="6" t="n">
+        <v>120791</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
@@ -16435,6 +17222,12 @@
       </c>
       <c r="E176" s="5" t="n"/>
       <c r="F176" s="5" t="n"/>
+      <c r="G176" s="7" t="n">
+        <v>314.28</v>
+      </c>
+      <c r="H176" s="6" t="n">
+        <v>46513</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
@@ -16479,6 +17272,12 @@
       </c>
       <c r="E178" s="5" t="n"/>
       <c r="F178" s="5" t="n"/>
+      <c r="G178" s="7" t="n">
+        <v>605.39</v>
+      </c>
+      <c r="H178" s="6" t="n">
+        <v>88993</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
@@ -16501,6 +17300,12 @@
       </c>
       <c r="E179" s="5" t="n"/>
       <c r="F179" s="5" t="n"/>
+      <c r="G179" s="7" t="n">
+        <v>364.79</v>
+      </c>
+      <c r="H179" s="6" t="n">
+        <v>52895</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
@@ -16545,6 +17350,12 @@
       </c>
       <c r="E181" s="5" t="n"/>
       <c r="F181" s="5" t="n"/>
+      <c r="G181" s="7" t="n">
+        <v>469.52</v>
+      </c>
+      <c r="H181" s="6" t="n">
+        <v>66203</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
@@ -16589,6 +17400,12 @@
       </c>
       <c r="E183" s="5" t="n"/>
       <c r="F183" s="5" t="n"/>
+      <c r="G183" s="7" t="n">
+        <v>991.46</v>
+      </c>
+      <c r="H183" s="6" t="n">
+        <v>136822</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
@@ -16611,6 +17428,12 @@
       </c>
       <c r="E184" s="5" t="n"/>
       <c r="F184" s="5" t="n"/>
+      <c r="G184" s="7" t="n">
+        <v>387.1</v>
+      </c>
+      <c r="H184" s="6" t="n">
+        <v>53420</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
@@ -16661,6 +17484,12 @@
       </c>
       <c r="E186" s="5" t="n"/>
       <c r="F186" s="5" t="n"/>
+      <c r="G186" s="7" t="n">
+        <v>397.38</v>
+      </c>
+      <c r="H186" s="6" t="n">
+        <v>53250</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
@@ -16683,6 +17512,12 @@
       </c>
       <c r="E187" s="5" t="n"/>
       <c r="F187" s="5" t="n"/>
+      <c r="G187" s="7" t="n">
+        <v>793.67</v>
+      </c>
+      <c r="H187" s="6" t="n">
+        <v>105558</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
@@ -16705,6 +17540,12 @@
       </c>
       <c r="E188" s="5" t="n"/>
       <c r="F188" s="5" t="n"/>
+      <c r="G188" s="7" t="n">
+        <v>684.51</v>
+      </c>
+      <c r="H188" s="6" t="n">
+        <v>88986</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
@@ -16727,6 +17568,12 @@
       </c>
       <c r="E189" s="5" t="n"/>
       <c r="F189" s="5" t="n"/>
+      <c r="G189" s="7" t="n">
+        <v>1370.79</v>
+      </c>
+      <c r="H189" s="6" t="n">
+        <v>176832</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
@@ -16749,6 +17596,12 @@
       </c>
       <c r="E190" s="5" t="n"/>
       <c r="F190" s="5" t="n"/>
+      <c r="G190" s="7" t="n">
+        <v>441.89</v>
+      </c>
+      <c r="H190" s="6" t="n">
+        <v>56121</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
@@ -16771,6 +17624,12 @@
       </c>
       <c r="E191" s="5" t="n"/>
       <c r="F191" s="5" t="n"/>
+      <c r="G191" s="7" t="n">
+        <v>1210.73</v>
+      </c>
+      <c r="H191" s="6" t="n">
+        <v>153763</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
@@ -16793,6 +17652,12 @@
       </c>
       <c r="E192" s="5" t="n"/>
       <c r="F192" s="5" t="n"/>
+      <c r="G192" s="7" t="n">
+        <v>639.74</v>
+      </c>
+      <c r="H192" s="6" t="n">
+        <v>81247</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
@@ -16815,6 +17680,12 @@
       </c>
       <c r="E193" s="5" t="n"/>
       <c r="F193" s="5" t="n"/>
+      <c r="G193" s="7" t="n">
+        <v>1249.73</v>
+      </c>
+      <c r="H193" s="6" t="n">
+        <v>154966</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
@@ -16837,6 +17708,12 @@
       </c>
       <c r="E194" s="5" t="n"/>
       <c r="F194" s="5" t="n"/>
+      <c r="G194" s="7" t="n">
+        <v>237.45</v>
+      </c>
+      <c r="H194" s="6" t="n">
+        <v>29444</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
@@ -16859,6 +17736,12 @@
       </c>
       <c r="E195" s="5" t="n"/>
       <c r="F195" s="5" t="n"/>
+      <c r="G195" s="7" t="n">
+        <v>306.25</v>
+      </c>
+      <c r="H195" s="6" t="n">
+        <v>35831</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
@@ -16881,6 +17764,12 @@
       </c>
       <c r="E196" s="5" t="n"/>
       <c r="F196" s="5" t="n"/>
+      <c r="G196" s="7" t="n">
+        <v>441.24</v>
+      </c>
+      <c r="H196" s="6" t="n">
+        <v>51184</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
@@ -16903,6 +17792,12 @@
       </c>
       <c r="E197" s="5" t="n"/>
       <c r="F197" s="5" t="n"/>
+      <c r="G197" s="7" t="n">
+        <v>65.73999999999999</v>
+      </c>
+      <c r="H197" s="6" t="n">
+        <v>7428</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
@@ -16925,6 +17820,12 @@
       </c>
       <c r="E198" s="5" t="n"/>
       <c r="F198" s="5" t="n"/>
+      <c r="G198" s="7" t="n">
+        <v>1773.67</v>
+      </c>
+      <c r="H198" s="6" t="n">
+        <v>200425</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
@@ -16947,6 +17848,12 @@
       </c>
       <c r="E199" s="5" t="n"/>
       <c r="F199" s="5" t="n"/>
+      <c r="G199" s="7" t="n">
+        <v>349.03</v>
+      </c>
+      <c r="H199" s="6" t="n">
+        <v>37346</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
@@ -16997,6 +17904,12 @@
       </c>
       <c r="E201" s="5" t="n"/>
       <c r="F201" s="5" t="n"/>
+      <c r="G201" s="7" t="n">
+        <v>645.5</v>
+      </c>
+      <c r="H201" s="6" t="n">
+        <v>65841</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
@@ -17019,6 +17932,12 @@
       </c>
       <c r="E202" s="5" t="n"/>
       <c r="F202" s="5" t="n"/>
+      <c r="G202" s="7" t="n">
+        <v>439.81</v>
+      </c>
+      <c r="H202" s="6" t="n">
+        <v>44861</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
@@ -17047,6 +17966,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G203" s="7" t="n">
+        <v>497.9</v>
+      </c>
+      <c r="H203" s="6" t="n">
+        <v>50786</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="5" t="inlineStr">
@@ -17069,6 +17994,12 @@
       </c>
       <c r="E204" s="5" t="n"/>
       <c r="F204" s="5" t="n"/>
+      <c r="G204" s="7" t="n">
+        <v>166.25</v>
+      </c>
+      <c r="H204" s="6" t="n">
+        <v>16791</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="5" t="inlineStr">
@@ -17113,6 +18044,12 @@
       </c>
       <c r="E206" s="5" t="n"/>
       <c r="F206" s="5" t="n"/>
+      <c r="G206" s="7" t="n">
+        <v>3056.56</v>
+      </c>
+      <c r="H206" s="6" t="n">
+        <v>293430</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
@@ -17135,6 +18072,12 @@
       </c>
       <c r="E207" s="5" t="n"/>
       <c r="F207" s="5" t="n"/>
+      <c r="G207" s="7" t="n">
+        <v>1319.52</v>
+      </c>
+      <c r="H207" s="6" t="n">
+        <v>126674</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="5" t="inlineStr">
@@ -17179,6 +18122,12 @@
       </c>
       <c r="E209" s="5" t="n"/>
       <c r="F209" s="5" t="n"/>
+      <c r="G209" s="7" t="n">
+        <v>953.28</v>
+      </c>
+      <c r="H209" s="6" t="n">
+        <v>87701</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
@@ -17201,6 +18150,12 @@
       </c>
       <c r="E210" s="5" t="n"/>
       <c r="F210" s="5" t="n"/>
+      <c r="G210" s="7" t="n">
+        <v>881.91</v>
+      </c>
+      <c r="H210" s="6" t="n">
+        <v>80254</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
@@ -17223,6 +18178,12 @@
       </c>
       <c r="E211" s="5" t="n"/>
       <c r="F211" s="5" t="n"/>
+      <c r="G211" s="7" t="n">
+        <v>1406</v>
+      </c>
+      <c r="H211" s="6" t="n">
+        <v>126540</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="5" t="inlineStr">
@@ -17245,6 +18206,12 @@
       </c>
       <c r="E212" s="5" t="n"/>
       <c r="F212" s="5" t="n"/>
+      <c r="G212" s="7" t="n">
+        <v>1194.1</v>
+      </c>
+      <c r="H212" s="6" t="n">
+        <v>106275</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
@@ -17267,6 +18234,12 @@
       </c>
       <c r="E213" s="5" t="n"/>
       <c r="F213" s="5" t="n"/>
+      <c r="G213" s="7" t="n">
+        <v>478.91</v>
+      </c>
+      <c r="H213" s="6" t="n">
+        <v>41666</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
@@ -17289,6 +18262,12 @@
       </c>
       <c r="E214" s="5" t="n"/>
       <c r="F214" s="5" t="n"/>
+      <c r="G214" s="7" t="n">
+        <v>716.59</v>
+      </c>
+      <c r="H214" s="6" t="n">
+        <v>62343</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
@@ -17311,6 +18290,12 @@
       </c>
       <c r="E215" s="5" t="n"/>
       <c r="F215" s="5" t="n"/>
+      <c r="G215" s="7" t="n">
+        <v>704.73</v>
+      </c>
+      <c r="H215" s="6" t="n">
+        <v>60607</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
@@ -17333,6 +18318,12 @@
       </c>
       <c r="E216" s="5" t="n"/>
       <c r="F216" s="5" t="n"/>
+      <c r="G216" s="7" t="n">
+        <v>265.86</v>
+      </c>
+      <c r="H216" s="6" t="n">
+        <v>22598</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
@@ -17355,6 +18346,12 @@
       </c>
       <c r="E217" s="5" t="n"/>
       <c r="F217" s="5" t="n"/>
+      <c r="G217" s="7" t="n">
+        <v>550.8</v>
+      </c>
+      <c r="H217" s="6" t="n">
+        <v>46268</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
@@ -17383,6 +18380,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G218" s="7" t="n">
+        <v>371.48</v>
+      </c>
+      <c r="H218" s="6" t="n">
+        <v>31204</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
@@ -17405,6 +18408,12 @@
       </c>
       <c r="E219" s="5" t="n"/>
       <c r="F219" s="5" t="n"/>
+      <c r="G219" s="7" t="n">
+        <v>1367.91</v>
+      </c>
+      <c r="H219" s="6" t="n">
+        <v>114904</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
@@ -17449,6 +18458,12 @@
       </c>
       <c r="E221" s="5" t="n"/>
       <c r="F221" s="5" t="n"/>
+      <c r="G221" s="7" t="n">
+        <v>187.45</v>
+      </c>
+      <c r="H221" s="6" t="n">
+        <v>15371</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
@@ -17471,6 +18486,12 @@
       </c>
       <c r="E222" s="5" t="n"/>
       <c r="F222" s="5" t="n"/>
+      <c r="G222" s="7" t="n">
+        <v>406.27</v>
+      </c>
+      <c r="H222" s="6" t="n">
+        <v>33314</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
@@ -17537,6 +18558,12 @@
       </c>
       <c r="E225" s="5" t="n"/>
       <c r="F225" s="5" t="n"/>
+      <c r="G225" s="7" t="n">
+        <v>272.13</v>
+      </c>
+      <c r="H225" s="6" t="n">
+        <v>21498</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="5" t="inlineStr">
@@ -17559,6 +18586,12 @@
       </c>
       <c r="E226" s="5" t="n"/>
       <c r="F226" s="5" t="n"/>
+      <c r="G226" s="7" t="n">
+        <v>257.26</v>
+      </c>
+      <c r="H226" s="6" t="n">
+        <v>20323</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
@@ -17603,6 +18636,12 @@
       </c>
       <c r="E228" s="5" t="n"/>
       <c r="F228" s="5" t="n"/>
+      <c r="G228" s="7" t="n">
+        <v>2668.2</v>
+      </c>
+      <c r="H228" s="6" t="n">
+        <v>202783</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
@@ -17625,6 +18664,12 @@
       </c>
       <c r="E229" s="5" t="n"/>
       <c r="F229" s="5" t="n"/>
+      <c r="G229" s="7" t="n">
+        <v>817.8200000000001</v>
+      </c>
+      <c r="H229" s="6" t="n">
+        <v>62154</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
@@ -17647,6 +18692,12 @@
       </c>
       <c r="E230" s="5" t="n"/>
       <c r="F230" s="5" t="n"/>
+      <c r="G230" s="7" t="n">
+        <v>467.55</v>
+      </c>
+      <c r="H230" s="6" t="n">
+        <v>33196</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
@@ -17675,6 +18726,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G231" s="7" t="n">
+        <v>2174.76</v>
+      </c>
+      <c r="H231" s="6" t="n">
+        <v>150058</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
@@ -17697,6 +18754,12 @@
       </c>
       <c r="E232" s="5" t="n"/>
       <c r="F232" s="5" t="n"/>
+      <c r="G232" s="7" t="n">
+        <v>594.23</v>
+      </c>
+      <c r="H232" s="6" t="n">
+        <v>40408</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
@@ -17741,6 +18804,12 @@
       </c>
       <c r="E234" s="5" t="n"/>
       <c r="F234" s="5" t="n"/>
+      <c r="G234" s="7" t="n">
+        <v>1194.97</v>
+      </c>
+      <c r="H234" s="6" t="n">
+        <v>77673</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="5" t="inlineStr">
@@ -17785,6 +18854,12 @@
       </c>
       <c r="E236" s="5" t="n"/>
       <c r="F236" s="5" t="n"/>
+      <c r="G236" s="7" t="n">
+        <v>930.3200000000001</v>
+      </c>
+      <c r="H236" s="6" t="n">
+        <v>58610</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="5" t="inlineStr">
@@ -17807,6 +18882,12 @@
       </c>
       <c r="E237" s="5" t="n"/>
       <c r="F237" s="5" t="n"/>
+      <c r="G237" s="7" t="n">
+        <v>198.18</v>
+      </c>
+      <c r="H237" s="6" t="n">
+        <v>12485</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="5" t="inlineStr">
@@ -17829,6 +18910,12 @@
       </c>
       <c r="E238" s="5" t="n"/>
       <c r="F238" s="5" t="n"/>
+      <c r="G238" s="7" t="n">
+        <v>1480.76</v>
+      </c>
+      <c r="H238" s="6" t="n">
+        <v>91807</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="5" t="inlineStr">
@@ -17851,6 +18938,12 @@
       </c>
       <c r="E239" s="5" t="n"/>
       <c r="F239" s="5" t="n"/>
+      <c r="G239" s="7" t="n">
+        <v>1594.88</v>
+      </c>
+      <c r="H239" s="6" t="n">
+        <v>98883</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="5" t="inlineStr">
@@ -17873,6 +18966,12 @@
       </c>
       <c r="E240" s="5" t="n"/>
       <c r="F240" s="5" t="n"/>
+      <c r="G240" s="7" t="n">
+        <v>632.8099999999999</v>
+      </c>
+      <c r="H240" s="6" t="n">
+        <v>39234</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
@@ -17895,6 +18994,12 @@
       </c>
       <c r="E241" s="5" t="n"/>
       <c r="F241" s="5" t="n"/>
+      <c r="G241" s="7" t="n">
+        <v>1116.94</v>
+      </c>
+      <c r="H241" s="6" t="n">
+        <v>68134</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
@@ -17917,6 +19022,12 @@
       </c>
       <c r="E242" s="5" t="n"/>
       <c r="F242" s="5" t="n"/>
+      <c r="G242" s="7" t="n">
+        <v>2649.89</v>
+      </c>
+      <c r="H242" s="6" t="n">
+        <v>161643</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
@@ -17939,6 +19050,12 @@
       </c>
       <c r="E243" s="5" t="n"/>
       <c r="F243" s="5" t="n"/>
+      <c r="G243" s="7" t="n">
+        <v>611.79</v>
+      </c>
+      <c r="H243" s="6" t="n">
+        <v>37319</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="5" t="inlineStr">
@@ -17961,6 +19078,12 @@
       </c>
       <c r="E244" s="5" t="n"/>
       <c r="F244" s="5" t="n"/>
+      <c r="G244" s="7" t="n">
+        <v>1131.83</v>
+      </c>
+      <c r="H244" s="6" t="n">
+        <v>67910</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="5" t="inlineStr">
@@ -17983,6 +19106,12 @@
       </c>
       <c r="E245" s="5" t="n"/>
       <c r="F245" s="5" t="n"/>
+      <c r="G245" s="7" t="n">
+        <v>406.49</v>
+      </c>
+      <c r="H245" s="6" t="n">
+        <v>23576</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="5" t="inlineStr">
@@ -18005,6 +19134,12 @@
       </c>
       <c r="E246" s="5" t="n"/>
       <c r="F246" s="5" t="n"/>
+      <c r="G246" s="7" t="n">
+        <v>751.47</v>
+      </c>
+      <c r="H246" s="6" t="n">
+        <v>42082</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
@@ -18027,6 +19162,12 @@
       </c>
       <c r="E247" s="5" t="n"/>
       <c r="F247" s="5" t="n"/>
+      <c r="G247" s="7" t="n">
+        <v>262.1</v>
+      </c>
+      <c r="H247" s="6" t="n">
+        <v>14678</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="5" t="inlineStr">
@@ -18071,6 +19212,12 @@
       </c>
       <c r="E249" s="5" t="n"/>
       <c r="F249" s="5" t="n"/>
+      <c r="G249" s="7" t="n">
+        <v>1331.8</v>
+      </c>
+      <c r="H249" s="6" t="n">
+        <v>70586</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="5" t="inlineStr">
@@ -18093,6 +19240,12 @@
       </c>
       <c r="E250" s="5" t="n"/>
       <c r="F250" s="5" t="n"/>
+      <c r="G250" s="7" t="n">
+        <v>3302.65</v>
+      </c>
+      <c r="H250" s="6" t="n">
+        <v>171738</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="5" t="inlineStr">
@@ -18115,6 +19268,12 @@
       </c>
       <c r="E251" s="5" t="n"/>
       <c r="F251" s="5" t="n"/>
+      <c r="G251" s="7" t="n">
+        <v>1677.91</v>
+      </c>
+      <c r="H251" s="6" t="n">
+        <v>87252</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="5" t="inlineStr">
@@ -18137,6 +19296,12 @@
       </c>
       <c r="E252" s="5" t="n"/>
       <c r="F252" s="5" t="n"/>
+      <c r="G252" s="7" t="n">
+        <v>814.3099999999999</v>
+      </c>
+      <c r="H252" s="6" t="n">
+        <v>42344</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
@@ -18159,6 +19324,12 @@
       </c>
       <c r="E253" s="5" t="n"/>
       <c r="F253" s="5" t="n"/>
+      <c r="G253" s="7" t="n">
+        <v>403.8</v>
+      </c>
+      <c r="H253" s="6" t="n">
+        <v>20594</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
@@ -18181,6 +19352,12 @@
       </c>
       <c r="E254" s="5" t="n"/>
       <c r="F254" s="5" t="n"/>
+      <c r="G254" s="7" t="n">
+        <v>517.37</v>
+      </c>
+      <c r="H254" s="6" t="n">
+        <v>25868</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
@@ -18225,6 +19402,12 @@
       </c>
       <c r="E256" s="5" t="n"/>
       <c r="F256" s="5" t="n"/>
+      <c r="G256" s="7" t="n">
+        <v>714.45</v>
+      </c>
+      <c r="H256" s="6" t="n">
+        <v>35008</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
@@ -18247,6 +19430,12 @@
       </c>
       <c r="E257" s="5" t="n"/>
       <c r="F257" s="5" t="n"/>
+      <c r="G257" s="7" t="n">
+        <v>340.89</v>
+      </c>
+      <c r="H257" s="6" t="n">
+        <v>16703</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
@@ -18269,6 +19458,12 @@
       </c>
       <c r="E258" s="5" t="n"/>
       <c r="F258" s="5" t="n"/>
+      <c r="G258" s="7" t="n">
+        <v>320.74</v>
+      </c>
+      <c r="H258" s="6" t="n">
+        <v>15716</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
@@ -18291,6 +19486,12 @@
       </c>
       <c r="E259" s="5" t="n"/>
       <c r="F259" s="5" t="n"/>
+      <c r="G259" s="7" t="n">
+        <v>1570.43</v>
+      </c>
+      <c r="H259" s="6" t="n">
+        <v>75380</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
@@ -18341,6 +19542,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G261" s="7" t="n">
+        <v>306.01</v>
+      </c>
+      <c r="H261" s="6" t="n">
+        <v>14077</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
@@ -18363,6 +19570,12 @@
       </c>
       <c r="E262" s="5" t="n"/>
       <c r="F262" s="5" t="n"/>
+      <c r="G262" s="7" t="n">
+        <v>476.35</v>
+      </c>
+      <c r="H262" s="6" t="n">
+        <v>20959</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="5" t="inlineStr">
@@ -18385,6 +19598,12 @@
       </c>
       <c r="E263" s="5" t="n"/>
       <c r="F263" s="5" t="n"/>
+      <c r="G263" s="7" t="n">
+        <v>332.96</v>
+      </c>
+      <c r="H263" s="6" t="n">
+        <v>14650</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="5" t="inlineStr">
@@ -18413,6 +19632,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G264" s="7" t="n">
+        <v>2191.2</v>
+      </c>
+      <c r="H264" s="6" t="n">
+        <v>96413</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="5" t="inlineStr">
@@ -18435,6 +19660,12 @@
       </c>
       <c r="E265" s="5" t="n"/>
       <c r="F265" s="5" t="n"/>
+      <c r="G265" s="7" t="n">
+        <v>327.19</v>
+      </c>
+      <c r="H265" s="6" t="n">
+        <v>14069</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="5" t="inlineStr">
@@ -18457,6 +19688,12 @@
       </c>
       <c r="E266" s="5" t="n"/>
       <c r="F266" s="5" t="n"/>
+      <c r="G266" s="7" t="n">
+        <v>382.81</v>
+      </c>
+      <c r="H266" s="6" t="n">
+        <v>16461</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
@@ -18479,6 +19716,12 @@
       </c>
       <c r="E267" s="5" t="n"/>
       <c r="F267" s="5" t="n"/>
+      <c r="G267" s="7" t="n">
+        <v>1999.04</v>
+      </c>
+      <c r="H267" s="6" t="n">
+        <v>85959</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="5" t="inlineStr">
@@ -18523,6 +19766,12 @@
       </c>
       <c r="E269" s="5" t="n"/>
       <c r="F269" s="5" t="n"/>
+      <c r="G269" s="7" t="n">
+        <v>589.55</v>
+      </c>
+      <c r="H269" s="6" t="n">
+        <v>23582</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="5" t="inlineStr">
@@ -18545,6 +19794,12 @@
       </c>
       <c r="E270" s="5" t="n"/>
       <c r="F270" s="5" t="n"/>
+      <c r="G270" s="7" t="n">
+        <v>1039.11</v>
+      </c>
+      <c r="H270" s="6" t="n">
+        <v>41564</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
@@ -18567,6 +19822,12 @@
       </c>
       <c r="E271" s="5" t="n"/>
       <c r="F271" s="5" t="n"/>
+      <c r="G271" s="7" t="n">
+        <v>497.36</v>
+      </c>
+      <c r="H271" s="6" t="n">
+        <v>19895</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
@@ -18589,6 +19850,12 @@
       </c>
       <c r="E272" s="5" t="n"/>
       <c r="F272" s="5" t="n"/>
+      <c r="G272" s="7" t="n">
+        <v>510.99</v>
+      </c>
+      <c r="H272" s="6" t="n">
+        <v>20439</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
@@ -18611,6 +19878,12 @@
       </c>
       <c r="E273" s="5" t="n"/>
       <c r="F273" s="5" t="n"/>
+      <c r="G273" s="7" t="n">
+        <v>890</v>
+      </c>
+      <c r="H273" s="6" t="n">
+        <v>32930</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
@@ -18633,6 +19906,12 @@
       </c>
       <c r="E274" s="5" t="n"/>
       <c r="F274" s="5" t="n"/>
+      <c r="G274" s="7" t="n">
+        <v>450.32</v>
+      </c>
+      <c r="H274" s="6" t="n">
+        <v>16212</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
@@ -18655,6 +19934,12 @@
       </c>
       <c r="E275" s="5" t="n"/>
       <c r="F275" s="5" t="n"/>
+      <c r="G275" s="7" t="n">
+        <v>1143.8</v>
+      </c>
+      <c r="H275" s="6" t="n">
+        <v>40033</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="5" t="inlineStr">
@@ -18705,6 +19990,12 @@
       </c>
       <c r="E277" s="5" t="n"/>
       <c r="F277" s="5" t="n"/>
+      <c r="G277" s="7" t="n">
+        <v>888.45</v>
+      </c>
+      <c r="H277" s="6" t="n">
+        <v>30207</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="5" t="inlineStr">
@@ -18727,6 +20018,12 @@
       </c>
       <c r="E278" s="5" t="n"/>
       <c r="F278" s="5" t="n"/>
+      <c r="G278" s="7" t="n">
+        <v>332.89</v>
+      </c>
+      <c r="H278" s="6" t="n">
+        <v>11318</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
@@ -18749,6 +20046,12 @@
       </c>
       <c r="E279" s="5" t="n"/>
       <c r="F279" s="5" t="n"/>
+      <c r="G279" s="7" t="n">
+        <v>459.18</v>
+      </c>
+      <c r="H279" s="6" t="n">
+        <v>15612</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
@@ -18771,6 +20074,12 @@
       </c>
       <c r="E280" s="5" t="n"/>
       <c r="F280" s="5" t="n"/>
+      <c r="G280" s="7" t="n">
+        <v>650.59</v>
+      </c>
+      <c r="H280" s="6" t="n">
+        <v>21469</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
@@ -18793,6 +20102,12 @@
       </c>
       <c r="E281" s="5" t="n"/>
       <c r="F281" s="5" t="n"/>
+      <c r="G281" s="7" t="n">
+        <v>415.14</v>
+      </c>
+      <c r="H281" s="6" t="n">
+        <v>13284</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
@@ -18815,6 +20130,12 @@
       </c>
       <c r="E282" s="5" t="n"/>
       <c r="F282" s="5" t="n"/>
+      <c r="G282" s="7" t="n">
+        <v>320.47</v>
+      </c>
+      <c r="H282" s="6" t="n">
+        <v>10255</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
@@ -18837,6 +20158,12 @@
       </c>
       <c r="E283" s="5" t="n"/>
       <c r="F283" s="5" t="n"/>
+      <c r="G283" s="7" t="n">
+        <v>140.69</v>
+      </c>
+      <c r="H283" s="6" t="n">
+        <v>4361</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
@@ -18859,6 +20186,12 @@
       </c>
       <c r="E284" s="5" t="n"/>
       <c r="F284" s="5" t="n"/>
+      <c r="G284" s="7" t="n">
+        <v>535.38</v>
+      </c>
+      <c r="H284" s="6" t="n">
+        <v>16597</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
@@ -18881,6 +20214,12 @@
       </c>
       <c r="E285" s="5" t="n"/>
       <c r="F285" s="5" t="n"/>
+      <c r="G285" s="7" t="n">
+        <v>1815.22</v>
+      </c>
+      <c r="H285" s="6" t="n">
+        <v>54457</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
@@ -18903,6 +20242,12 @@
       </c>
       <c r="E286" s="5" t="n"/>
       <c r="F286" s="5" t="n"/>
+      <c r="G286" s="7" t="n">
+        <v>1262.32</v>
+      </c>
+      <c r="H286" s="6" t="n">
+        <v>37870</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
@@ -18925,6 +20270,12 @@
       </c>
       <c r="E287" s="5" t="n"/>
       <c r="F287" s="5" t="n"/>
+      <c r="G287" s="7" t="n">
+        <v>2235</v>
+      </c>
+      <c r="H287" s="6" t="n">
+        <v>64815</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
@@ -18947,6 +20298,12 @@
       </c>
       <c r="E288" s="5" t="n"/>
       <c r="F288" s="5" t="n"/>
+      <c r="G288" s="7" t="n">
+        <v>371.72</v>
+      </c>
+      <c r="H288" s="6" t="n">
+        <v>10780</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
@@ -18969,6 +20326,12 @@
       </c>
       <c r="E289" s="5" t="n"/>
       <c r="F289" s="5" t="n"/>
+      <c r="G289" s="7" t="n">
+        <v>1017.69</v>
+      </c>
+      <c r="H289" s="6" t="n">
+        <v>28495</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
@@ -18991,6 +20354,12 @@
       </c>
       <c r="E290" s="5" t="n"/>
       <c r="F290" s="5" t="n"/>
+      <c r="G290" s="7" t="n">
+        <v>273.3</v>
+      </c>
+      <c r="H290" s="6" t="n">
+        <v>7653</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="5" t="inlineStr">
@@ -19013,6 +20382,12 @@
       </c>
       <c r="E291" s="5" t="n"/>
       <c r="F291" s="5" t="n"/>
+      <c r="G291" s="7" t="n">
+        <v>2074.22</v>
+      </c>
+      <c r="H291" s="6" t="n">
+        <v>53930</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
@@ -19035,6 +20410,12 @@
       </c>
       <c r="E292" s="5" t="n"/>
       <c r="F292" s="5" t="n"/>
+      <c r="G292" s="7" t="n">
+        <v>1011.53</v>
+      </c>
+      <c r="H292" s="6" t="n">
+        <v>26300</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
@@ -19079,6 +20460,12 @@
       </c>
       <c r="E294" s="5" t="n"/>
       <c r="F294" s="5" t="n"/>
+      <c r="G294" s="7" t="n">
+        <v>911.03</v>
+      </c>
+      <c r="H294" s="6" t="n">
+        <v>22776</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
@@ -19101,6 +20488,12 @@
       </c>
       <c r="E295" s="5" t="n"/>
       <c r="F295" s="5" t="n"/>
+      <c r="G295" s="7" t="n">
+        <v>178.73</v>
+      </c>
+      <c r="H295" s="6" t="n">
+        <v>4468</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
@@ -19145,6 +20538,12 @@
       </c>
       <c r="E297" s="5" t="n"/>
       <c r="F297" s="5" t="n"/>
+      <c r="G297" s="7" t="n">
+        <v>996.25</v>
+      </c>
+      <c r="H297" s="6" t="n">
+        <v>24906</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="5" t="inlineStr">
@@ -19167,6 +20566,12 @@
       </c>
       <c r="E298" s="5" t="n"/>
       <c r="F298" s="5" t="n"/>
+      <c r="G298" s="7" t="n">
+        <v>1078.7</v>
+      </c>
+      <c r="H298" s="6" t="n">
+        <v>25889</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="5" t="inlineStr">
@@ -19189,6 +20594,12 @@
       </c>
       <c r="E299" s="5" t="n"/>
       <c r="F299" s="5" t="n"/>
+      <c r="G299" s="7" t="n">
+        <v>710.5</v>
+      </c>
+      <c r="H299" s="6" t="n">
+        <v>17052</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="5" t="inlineStr">
@@ -19211,6 +20622,12 @@
       </c>
       <c r="E300" s="5" t="n"/>
       <c r="F300" s="5" t="n"/>
+      <c r="G300" s="7" t="n">
+        <v>488.11</v>
+      </c>
+      <c r="H300" s="6" t="n">
+        <v>11715</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
@@ -19233,6 +20650,12 @@
       </c>
       <c r="E301" s="5" t="n"/>
       <c r="F301" s="5" t="n"/>
+      <c r="G301" s="7" t="n">
+        <v>121.41</v>
+      </c>
+      <c r="H301" s="6" t="n">
+        <v>2914</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="5" t="inlineStr">
@@ -19255,6 +20678,12 @@
       </c>
       <c r="E302" s="5" t="n"/>
       <c r="F302" s="5" t="n"/>
+      <c r="G302" s="7" t="n">
+        <v>334.72</v>
+      </c>
+      <c r="H302" s="6" t="n">
+        <v>8033</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="5" t="inlineStr">
@@ -19277,6 +20706,12 @@
       </c>
       <c r="E303" s="5" t="n"/>
       <c r="F303" s="5" t="n"/>
+      <c r="G303" s="7" t="n">
+        <v>156.81</v>
+      </c>
+      <c r="H303" s="6" t="n">
+        <v>3763</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="5" t="inlineStr">
@@ -19299,6 +20734,12 @@
       </c>
       <c r="E304" s="5" t="n"/>
       <c r="F304" s="5" t="n"/>
+      <c r="G304" s="7" t="n">
+        <v>957.17</v>
+      </c>
+      <c r="H304" s="6" t="n">
+        <v>22972</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="5" t="inlineStr">
@@ -19321,6 +20762,12 @@
       </c>
       <c r="E305" s="5" t="n"/>
       <c r="F305" s="5" t="n"/>
+      <c r="G305" s="7" t="n">
+        <v>549.59</v>
+      </c>
+      <c r="H305" s="6" t="n">
+        <v>12641</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="5" t="inlineStr">
@@ -19343,6 +20790,12 @@
       </c>
       <c r="E306" s="5" t="n"/>
       <c r="F306" s="5" t="n"/>
+      <c r="G306" s="7" t="n">
+        <v>366.51</v>
+      </c>
+      <c r="H306" s="6" t="n">
+        <v>8430</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="5" t="inlineStr">
@@ -19365,6 +20818,12 @@
       </c>
       <c r="E307" s="5" t="n"/>
       <c r="F307" s="5" t="n"/>
+      <c r="G307" s="7" t="n">
+        <v>334.77</v>
+      </c>
+      <c r="H307" s="6" t="n">
+        <v>7365</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="5" t="inlineStr">
@@ -19387,6 +20846,12 @@
       </c>
       <c r="E308" s="5" t="n"/>
       <c r="F308" s="5" t="n"/>
+      <c r="G308" s="7" t="n">
+        <v>2812.92</v>
+      </c>
+      <c r="H308" s="6" t="n">
+        <v>61884</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="5" t="inlineStr">
@@ -19409,6 +20874,12 @@
       </c>
       <c r="E309" s="5" t="n"/>
       <c r="F309" s="5" t="n"/>
+      <c r="G309" s="7" t="n">
+        <v>397.95</v>
+      </c>
+      <c r="H309" s="6" t="n">
+        <v>8755</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="5" t="inlineStr">
@@ -19431,6 +20902,12 @@
       </c>
       <c r="E310" s="5" t="n"/>
       <c r="F310" s="5" t="n"/>
+      <c r="G310" s="7" t="n">
+        <v>640.92</v>
+      </c>
+      <c r="H310" s="6" t="n">
+        <v>13459</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="5" t="inlineStr">
@@ -19453,6 +20930,12 @@
       </c>
       <c r="E311" s="5" t="n"/>
       <c r="F311" s="5" t="n"/>
+      <c r="G311" s="7" t="n">
+        <v>849.05</v>
+      </c>
+      <c r="H311" s="6" t="n">
+        <v>17830</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="5" t="inlineStr">
@@ -19475,6 +20958,12 @@
       </c>
       <c r="E312" s="5" t="n"/>
       <c r="F312" s="5" t="n"/>
+      <c r="G312" s="7" t="n">
+        <v>2148.81</v>
+      </c>
+      <c r="H312" s="6" t="n">
+        <v>45125</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="5" t="inlineStr">
@@ -19497,6 +20986,12 @@
       </c>
       <c r="E313" s="5" t="n"/>
       <c r="F313" s="5" t="n"/>
+      <c r="G313" s="7" t="n">
+        <v>1091.58</v>
+      </c>
+      <c r="H313" s="6" t="n">
+        <v>22923</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="5" t="inlineStr">
@@ -19519,6 +21014,12 @@
       </c>
       <c r="E314" s="5" t="n"/>
       <c r="F314" s="5" t="n"/>
+      <c r="G314" s="7" t="n">
+        <v>161.64</v>
+      </c>
+      <c r="H314" s="6" t="n">
+        <v>3394</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="5" t="inlineStr">
@@ -19541,6 +21042,12 @@
       </c>
       <c r="E315" s="5" t="n"/>
       <c r="F315" s="5" t="n"/>
+      <c r="G315" s="7" t="n">
+        <v>355.83</v>
+      </c>
+      <c r="H315" s="6" t="n">
+        <v>7472</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="5" t="inlineStr">
@@ -19585,6 +21092,12 @@
       </c>
       <c r="E317" s="5" t="n"/>
       <c r="F317" s="5" t="n"/>
+      <c r="G317" s="7" t="n">
+        <v>937.54</v>
+      </c>
+      <c r="H317" s="6" t="n">
+        <v>19688</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="5" t="inlineStr">
@@ -19651,6 +21164,12 @@
       </c>
       <c r="E320" s="5" t="n"/>
       <c r="F320" s="5" t="n"/>
+      <c r="G320" s="7" t="n">
+        <v>2051.57</v>
+      </c>
+      <c r="H320" s="6" t="n">
+        <v>38980</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="5" t="inlineStr">
@@ -19695,6 +21214,12 @@
       </c>
       <c r="E322" s="5" t="n"/>
       <c r="F322" s="5" t="n"/>
+      <c r="G322" s="7" t="n">
+        <v>662.22</v>
+      </c>
+      <c r="H322" s="6" t="n">
+        <v>12582</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="5" t="inlineStr">
@@ -19717,6 +21242,12 @@
       </c>
       <c r="E323" s="5" t="n"/>
       <c r="F323" s="5" t="n"/>
+      <c r="G323" s="7" t="n">
+        <v>611.0599999999999</v>
+      </c>
+      <c r="H323" s="6" t="n">
+        <v>11610</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="5" t="inlineStr">
@@ -19739,6 +21270,12 @@
       </c>
       <c r="E324" s="5" t="n"/>
       <c r="F324" s="5" t="n"/>
+      <c r="G324" s="7" t="n">
+        <v>1013.87</v>
+      </c>
+      <c r="H324" s="6" t="n">
+        <v>18250</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="5" t="inlineStr">
@@ -19761,6 +21298,12 @@
       </c>
       <c r="E325" s="5" t="n"/>
       <c r="F325" s="5" t="n"/>
+      <c r="G325" s="7" t="n">
+        <v>682.96</v>
+      </c>
+      <c r="H325" s="6" t="n">
+        <v>11610</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="5" t="inlineStr">
@@ -19783,6 +21326,12 @@
       </c>
       <c r="E326" s="5" t="n"/>
       <c r="F326" s="5" t="n"/>
+      <c r="G326" s="7" t="n">
+        <v>394.84</v>
+      </c>
+      <c r="H326" s="6" t="n">
+        <v>6317</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="5" t="inlineStr">
@@ -19811,6 +21360,12 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="G327" s="7" t="n">
+        <v>452.94</v>
+      </c>
+      <c r="H327" s="6" t="n">
+        <v>7247</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="5" t="inlineStr">
@@ -19833,6 +21388,12 @@
       </c>
       <c r="E328" s="5" t="n"/>
       <c r="F328" s="5" t="n"/>
+      <c r="G328" s="7" t="n">
+        <v>1225.05</v>
+      </c>
+      <c r="H328" s="6" t="n">
+        <v>19601</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="5" t="inlineStr">
@@ -19855,6 +21416,12 @@
       </c>
       <c r="E329" s="5" t="n"/>
       <c r="F329" s="5" t="n"/>
+      <c r="G329" s="7" t="n">
+        <v>334.56</v>
+      </c>
+      <c r="H329" s="6" t="n">
+        <v>5353</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="5" t="inlineStr">
@@ -19877,6 +21444,12 @@
       </c>
       <c r="E330" s="5" t="n"/>
       <c r="F330" s="5" t="n"/>
+      <c r="G330" s="7" t="n">
+        <v>572.03</v>
+      </c>
+      <c r="H330" s="6" t="n">
+        <v>9152</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="5" t="inlineStr">
@@ -19899,6 +21472,12 @@
       </c>
       <c r="E331" s="5" t="n"/>
       <c r="F331" s="5" t="n"/>
+      <c r="G331" s="7" t="n">
+        <v>513.04</v>
+      </c>
+      <c r="H331" s="6" t="n">
+        <v>7696</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="5" t="inlineStr">
@@ -19921,6 +21500,12 @@
       </c>
       <c r="E332" s="5" t="n"/>
       <c r="F332" s="5" t="n"/>
+      <c r="G332" s="7" t="n">
+        <v>278.22</v>
+      </c>
+      <c r="H332" s="6" t="n">
+        <v>4173</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="5" t="inlineStr">
@@ -19987,6 +21572,12 @@
       </c>
       <c r="E335" s="5" t="n"/>
       <c r="F335" s="5" t="n"/>
+      <c r="G335" s="7" t="n">
+        <v>650.41</v>
+      </c>
+      <c r="H335" s="6" t="n">
+        <v>9106</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="5" t="inlineStr">
@@ -20009,6 +21600,12 @@
       </c>
       <c r="E336" s="5" t="n"/>
       <c r="F336" s="5" t="n"/>
+      <c r="G336" s="7" t="n">
+        <v>239.35</v>
+      </c>
+      <c r="H336" s="6" t="n">
+        <v>3351</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="5" t="inlineStr">
@@ -20031,6 +21628,12 @@
       </c>
       <c r="E337" s="5" t="n"/>
       <c r="F337" s="5" t="n"/>
+      <c r="G337" s="7" t="n">
+        <v>1426.89</v>
+      </c>
+      <c r="H337" s="6" t="n">
+        <v>19976</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="5" t="inlineStr">
@@ -20053,6 +21656,12 @@
       </c>
       <c r="E338" s="5" t="n"/>
       <c r="F338" s="5" t="n"/>
+      <c r="G338" s="7" t="n">
+        <v>1443.33</v>
+      </c>
+      <c r="H338" s="6" t="n">
+        <v>20207</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="5" t="inlineStr">
@@ -20097,6 +21706,12 @@
       </c>
       <c r="E340" s="5" t="n"/>
       <c r="F340" s="5" t="n"/>
+      <c r="G340" s="7" t="n">
+        <v>522.63</v>
+      </c>
+      <c r="H340" s="6" t="n">
+        <v>6794</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="5" t="inlineStr">
@@ -20119,6 +21734,12 @@
       </c>
       <c r="E341" s="5" t="n"/>
       <c r="F341" s="5" t="n"/>
+      <c r="G341" s="7" t="n">
+        <v>1121.72</v>
+      </c>
+      <c r="H341" s="6" t="n">
+        <v>12339</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="5" t="inlineStr">
@@ -20141,6 +21762,12 @@
       </c>
       <c r="E342" s="5" t="n"/>
       <c r="F342" s="5" t="n"/>
+      <c r="G342" s="7" t="n">
+        <v>553.86</v>
+      </c>
+      <c r="H342" s="6" t="n">
+        <v>6092</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="5" t="inlineStr">
@@ -20163,6 +21790,12 @@
       </c>
       <c r="E343" s="5" t="n"/>
       <c r="F343" s="5" t="n"/>
+      <c r="G343" s="7" t="n">
+        <v>395.51</v>
+      </c>
+      <c r="H343" s="6" t="n">
+        <v>4351</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="5" t="inlineStr">
@@ -20185,6 +21818,12 @@
       </c>
       <c r="E344" s="5" t="n"/>
       <c r="F344" s="5" t="n"/>
+      <c r="G344" s="7" t="n">
+        <v>492.71</v>
+      </c>
+      <c r="H344" s="6" t="n">
+        <v>5420</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="5" t="inlineStr">
@@ -20207,6 +21846,12 @@
       </c>
       <c r="E345" s="5" t="n"/>
       <c r="F345" s="5" t="n"/>
+      <c r="G345" s="7" t="n">
+        <v>193.85</v>
+      </c>
+      <c r="H345" s="6" t="n">
+        <v>2132</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="5" t="inlineStr">
@@ -20229,6 +21874,12 @@
       </c>
       <c r="E346" s="5" t="n"/>
       <c r="F346" s="5" t="n"/>
+      <c r="G346" s="7" t="n">
+        <v>2452.99</v>
+      </c>
+      <c r="H346" s="6" t="n">
+        <v>24530</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="5" t="inlineStr">
@@ -20251,6 +21902,12 @@
       </c>
       <c r="E347" s="5" t="n"/>
       <c r="F347" s="5" t="n"/>
+      <c r="G347" s="7" t="n">
+        <v>559.09</v>
+      </c>
+      <c r="H347" s="6" t="n">
+        <v>5591</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="5" t="inlineStr">
@@ -20295,6 +21952,12 @@
       </c>
       <c r="E349" s="5" t="n"/>
       <c r="F349" s="5" t="n"/>
+      <c r="G349" s="7" t="n">
+        <v>539.37</v>
+      </c>
+      <c r="H349" s="6" t="n">
+        <v>5394</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="5" t="inlineStr">
@@ -20317,6 +21980,12 @@
       </c>
       <c r="E350" s="5" t="n"/>
       <c r="F350" s="5" t="n"/>
+      <c r="G350" s="7" t="n">
+        <v>2388.64</v>
+      </c>
+      <c r="H350" s="6" t="n">
+        <v>21498</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="5" t="inlineStr">
@@ -20361,6 +22030,12 @@
       </c>
       <c r="E352" s="5" t="n"/>
       <c r="F352" s="5" t="n"/>
+      <c r="G352" s="7" t="n">
+        <v>318.02</v>
+      </c>
+      <c r="H352" s="6" t="n">
+        <v>2544</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="5" t="inlineStr">
@@ -20383,6 +22058,12 @@
       </c>
       <c r="E353" s="5" t="n"/>
       <c r="F353" s="5" t="n"/>
+      <c r="G353" s="7" t="n">
+        <v>321.64</v>
+      </c>
+      <c r="H353" s="6" t="n">
+        <v>2573</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="5" t="inlineStr">
@@ -20405,6 +22086,12 @@
       </c>
       <c r="E354" s="5" t="n"/>
       <c r="F354" s="5" t="n"/>
+      <c r="G354" s="7" t="n">
+        <v>155.43</v>
+      </c>
+      <c r="H354" s="6" t="n">
+        <v>1243</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="5" t="inlineStr">
@@ -20427,6 +22114,12 @@
       </c>
       <c r="E355" s="5" t="n"/>
       <c r="F355" s="5" t="n"/>
+      <c r="G355" s="7" t="n">
+        <v>728.46</v>
+      </c>
+      <c r="H355" s="6" t="n">
+        <v>5828</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="5" t="inlineStr">
@@ -20449,6 +22142,12 @@
       </c>
       <c r="E356" s="5" t="n"/>
       <c r="F356" s="5" t="n"/>
+      <c r="G356" s="7" t="n">
+        <v>339.76</v>
+      </c>
+      <c r="H356" s="6" t="n">
+        <v>2718</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="5" t="inlineStr">
@@ -20471,6 +22170,12 @@
       </c>
       <c r="E357" s="5" t="n"/>
       <c r="F357" s="5" t="n"/>
+      <c r="G357" s="7" t="n">
+        <v>650.23</v>
+      </c>
+      <c r="H357" s="6" t="n">
+        <v>5202</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="5" t="inlineStr">
@@ -20515,6 +22220,12 @@
       </c>
       <c r="E359" s="5" t="n"/>
       <c r="F359" s="5" t="n"/>
+      <c r="G359" s="7" t="n">
+        <v>833.78</v>
+      </c>
+      <c r="H359" s="6" t="n">
+        <v>5836</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="5" t="inlineStr">
@@ -20537,6 +22248,12 @@
       </c>
       <c r="E360" s="5" t="n"/>
       <c r="F360" s="5" t="n"/>
+      <c r="G360" s="7" t="n">
+        <v>679.38</v>
+      </c>
+      <c r="H360" s="6" t="n">
+        <v>4756</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="5" t="inlineStr">
@@ -20603,6 +22320,12 @@
       </c>
       <c r="E363" s="5" t="n"/>
       <c r="F363" s="5" t="n"/>
+      <c r="G363" s="7" t="n">
+        <v>267.12</v>
+      </c>
+      <c r="H363" s="6" t="n">
+        <v>1603</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="5" t="inlineStr">
@@ -20625,6 +22348,12 @@
       </c>
       <c r="E364" s="5" t="n"/>
       <c r="F364" s="5" t="n"/>
+      <c r="G364" s="7" t="n">
+        <v>342.87</v>
+      </c>
+      <c r="H364" s="6" t="n">
+        <v>2057</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="5" t="inlineStr">
@@ -20647,6 +22376,12 @@
       </c>
       <c r="E365" s="5" t="n"/>
       <c r="F365" s="5" t="n"/>
+      <c r="G365" s="7" t="n">
+        <v>714.61</v>
+      </c>
+      <c r="H365" s="6" t="n">
+        <v>4288</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="5" t="inlineStr">
@@ -20691,6 +22426,12 @@
       </c>
       <c r="E367" s="5" t="n"/>
       <c r="F367" s="5" t="n"/>
+      <c r="G367" s="7" t="n">
+        <v>983.65</v>
+      </c>
+      <c r="H367" s="6" t="n">
+        <v>4918</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="5" t="inlineStr">
@@ -20713,6 +22454,12 @@
       </c>
       <c r="E368" s="5" t="n"/>
       <c r="F368" s="5" t="n"/>
+      <c r="G368" s="7" t="n">
+        <v>715.74</v>
+      </c>
+      <c r="H368" s="6" t="n">
+        <v>3579</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="5" t="inlineStr">
@@ -20735,6 +22482,12 @@
       </c>
       <c r="E369" s="5" t="n"/>
       <c r="F369" s="5" t="n"/>
+      <c r="G369" s="7" t="n">
+        <v>520.38</v>
+      </c>
+      <c r="H369" s="6" t="n">
+        <v>2082</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="5" t="inlineStr">
@@ -20757,6 +22510,12 @@
       </c>
       <c r="E370" s="5" t="n"/>
       <c r="F370" s="5" t="n"/>
+      <c r="G370" s="7" t="n">
+        <v>673.5700000000001</v>
+      </c>
+      <c r="H370" s="6" t="n">
+        <v>2694</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="5" t="inlineStr">
@@ -20779,6 +22538,12 @@
       </c>
       <c r="E371" s="5" t="n"/>
       <c r="F371" s="5" t="n"/>
+      <c r="G371" s="7" t="n">
+        <v>163.63</v>
+      </c>
+      <c r="H371" s="6" t="n">
+        <v>491</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="5" t="inlineStr">
@@ -20801,6 +22566,12 @@
       </c>
       <c r="E372" s="5" t="n"/>
       <c r="F372" s="5" t="n"/>
+      <c r="G372" s="7" t="n">
+        <v>312.8</v>
+      </c>
+      <c r="H372" s="6" t="n">
+        <v>938</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="5" t="inlineStr">
@@ -20823,6 +22594,12 @@
       </c>
       <c r="E373" s="5" t="n"/>
       <c r="F373" s="5" t="n"/>
+      <c r="G373" s="7" t="n">
+        <v>580.29</v>
+      </c>
+      <c r="H373" s="6" t="n">
+        <v>1161</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="5" t="inlineStr">
@@ -20867,6 +22644,12 @@
       </c>
       <c r="E375" s="5" t="n"/>
       <c r="F375" s="5" t="n"/>
+      <c r="G375" s="7" t="n">
+        <v>629.37</v>
+      </c>
+      <c r="H375" s="6" t="n">
+        <v>1259</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="5" t="inlineStr">
@@ -20889,6 +22672,12 @@
       </c>
       <c r="E376" s="5" t="n"/>
       <c r="F376" s="5" t="n"/>
+      <c r="G376" s="7" t="n">
+        <v>356.02</v>
+      </c>
+      <c r="H376" s="6" t="n">
+        <v>712</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="5" t="inlineStr">
@@ -20911,6 +22700,12 @@
       </c>
       <c r="E377" s="5" t="n"/>
       <c r="F377" s="5" t="n"/>
+      <c r="G377" s="7" t="n">
+        <v>1060.83</v>
+      </c>
+      <c r="H377" s="6" t="n">
+        <v>2122</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="5" t="inlineStr">
@@ -20933,6 +22728,12 @@
       </c>
       <c r="E378" s="5" t="n"/>
       <c r="F378" s="5" t="n"/>
+      <c r="G378" s="7" t="n">
+        <v>205.31</v>
+      </c>
+      <c r="H378" s="6" t="n">
+        <v>411</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="5" t="inlineStr">
@@ -20955,6 +22756,12 @@
       </c>
       <c r="E379" s="5" t="n"/>
       <c r="F379" s="5" t="n"/>
+      <c r="G379" s="7" t="n">
+        <v>928.34</v>
+      </c>
+      <c r="H379" s="6" t="n">
+        <v>1857</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="5" t="inlineStr">
@@ -20977,6 +22784,12 @@
       </c>
       <c r="E380" s="5" t="n"/>
       <c r="F380" s="5" t="n"/>
+      <c r="G380" s="7" t="n">
+        <v>566.62</v>
+      </c>
+      <c r="H380" s="6" t="n">
+        <v>1133</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="5" t="inlineStr">
@@ -20999,6 +22812,12 @@
       </c>
       <c r="E381" s="5" t="n"/>
       <c r="F381" s="5" t="n"/>
+      <c r="G381" s="7" t="n">
+        <v>961.37</v>
+      </c>
+      <c r="H381" s="6" t="n">
+        <v>1923</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="5" t="inlineStr">
@@ -21043,6 +22862,12 @@
       </c>
       <c r="E383" s="5" t="n"/>
       <c r="F383" s="5" t="n"/>
+      <c r="G383" s="7" t="n">
+        <v>373.04</v>
+      </c>
+      <c r="H383" s="6" t="n">
+        <v>746</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="5" t="inlineStr">
@@ -21065,6 +22890,12 @@
       </c>
       <c r="E384" s="5" t="n"/>
       <c r="F384" s="5" t="n"/>
+      <c r="G384" s="7" t="n">
+        <v>805.1900000000001</v>
+      </c>
+      <c r="H384" s="6" t="n">
+        <v>1610</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="5" t="inlineStr">
@@ -21087,6 +22918,12 @@
       </c>
       <c r="E385" s="5" t="n"/>
       <c r="F385" s="5" t="n"/>
+      <c r="G385" s="7" t="n">
+        <v>592.14</v>
+      </c>
+      <c r="H385" s="6" t="n">
+        <v>1184</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="5" t="inlineStr">
@@ -21109,6 +22946,12 @@
       </c>
       <c r="E386" s="5" t="n"/>
       <c r="F386" s="5" t="n"/>
+      <c r="G386" s="7" t="n">
+        <v>738.88</v>
+      </c>
+      <c r="H386" s="6" t="n">
+        <v>1478</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="5" t="inlineStr">
@@ -21131,6 +22974,12 @@
       </c>
       <c r="E387" s="5" t="n"/>
       <c r="F387" s="5" t="n"/>
+      <c r="G387" s="7" t="n">
+        <v>2619.87</v>
+      </c>
+      <c r="H387" s="6" t="n">
+        <v>2620</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="5" t="inlineStr">
@@ -21153,6 +23002,12 @@
       </c>
       <c r="E388" s="5" t="n"/>
       <c r="F388" s="5" t="n"/>
+      <c r="G388" s="7" t="n">
+        <v>300.73</v>
+      </c>
+      <c r="H388" s="6" t="n">
+        <v>301</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="5" t="inlineStr">
@@ -21175,6 +23030,12 @@
       </c>
       <c r="E389" s="5" t="n"/>
       <c r="F389" s="5" t="n"/>
+      <c r="G389" s="7" t="n">
+        <v>862.96</v>
+      </c>
+      <c r="H389" s="6" t="n">
+        <v>863</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="5" t="inlineStr">
@@ -21219,6 +23080,12 @@
       </c>
       <c r="E391" s="5" t="n"/>
       <c r="F391" s="5" t="n"/>
+      <c r="G391" s="7" t="n">
+        <v>465.59</v>
+      </c>
+      <c r="H391" s="6" t="n">
+        <v>466</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="5" t="inlineStr">
@@ -21241,6 +23108,12 @@
       </c>
       <c r="E392" s="5" t="n"/>
       <c r="F392" s="5" t="n"/>
+      <c r="G392" s="7" t="n">
+        <v>511.28</v>
+      </c>
+      <c r="H392" s="6" t="n">
+        <v>511</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="5" t="inlineStr">
@@ -21263,6 +23136,12 @@
       </c>
       <c r="E393" s="5" t="n"/>
       <c r="F393" s="5" t="n"/>
+      <c r="G393" s="7" t="n">
+        <v>357.22</v>
+      </c>
+      <c r="H393" s="6" t="n">
+        <v>357</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="5" t="inlineStr">
@@ -21285,6 +23164,12 @@
       </c>
       <c r="E394" s="5" t="n"/>
       <c r="F394" s="5" t="n"/>
+      <c r="G394" s="7" t="n">
+        <v>789.3200000000001</v>
+      </c>
+      <c r="H394" s="6" t="n">
+        <v>789</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="5" t="inlineStr">
@@ -21307,6 +23192,12 @@
       </c>
       <c r="E395" s="5" t="n"/>
       <c r="F395" s="5" t="n"/>
+      <c r="G395" s="7" t="n">
+        <v>366.06</v>
+      </c>
+      <c r="H395" s="6" t="n">
+        <v>366</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="5" t="inlineStr">
@@ -21329,6 +23220,12 @@
       </c>
       <c r="E396" s="5" t="n"/>
       <c r="F396" s="5" t="n"/>
+      <c r="G396" s="7" t="n">
+        <v>1279.2</v>
+      </c>
+      <c r="H396" s="6" t="n">
+        <v>1279</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="5" t="inlineStr">
@@ -21351,6 +23248,12 @@
       </c>
       <c r="E397" s="5" t="n"/>
       <c r="F397" s="5" t="n"/>
+      <c r="G397" s="7" t="n">
+        <v>485.55</v>
+      </c>
+      <c r="H397" s="6" t="n">
+        <v>486</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="5" t="inlineStr">
@@ -21373,6 +23276,12 @@
       </c>
       <c r="E398" s="5" t="n"/>
       <c r="F398" s="5" t="n"/>
+      <c r="G398" s="7" t="n">
+        <v>93.48999999999999</v>
+      </c>
+      <c r="H398" s="6" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="5" t="inlineStr">
@@ -21395,6 +23304,12 @@
       </c>
       <c r="E399" s="5" t="n"/>
       <c r="F399" s="5" t="n"/>
+      <c r="G399" s="7" t="n">
+        <v>327.15</v>
+      </c>
+      <c r="H399" s="6" t="n">
+        <v>327</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="5" t="inlineStr">
@@ -21417,6 +23332,12 @@
       </c>
       <c r="E400" s="5" t="n"/>
       <c r="F400" s="5" t="n"/>
+      <c r="G400" s="7" t="n">
+        <v>460.73</v>
+      </c>
+      <c r="H400" s="6" t="n">
+        <v>461</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="5" t="inlineStr">
@@ -21439,6 +23360,12 @@
       </c>
       <c r="E401" s="5" t="n"/>
       <c r="F401" s="5" t="n"/>
+      <c r="G401" s="7" t="n">
+        <v>322.7</v>
+      </c>
+      <c r="H401" s="6" t="n">
+        <v>323</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="5" t="inlineStr">
@@ -21461,6 +23388,12 @@
       </c>
       <c r="E402" s="5" t="n"/>
       <c r="F402" s="5" t="n"/>
+      <c r="G402" s="7" t="n">
+        <v>169.51</v>
+      </c>
+      <c r="H402" s="6" t="n">
+        <v>170</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="5" t="inlineStr">
@@ -21483,6 +23416,12 @@
       </c>
       <c r="E403" s="5" t="n"/>
       <c r="F403" s="5" t="n"/>
+      <c r="G403" s="7" t="n">
+        <v>801.09</v>
+      </c>
+      <c r="H403" s="6" t="n">
+        <v>801</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="5" t="inlineStr">
@@ -21505,6 +23444,12 @@
       </c>
       <c r="E404" s="5" t="n"/>
       <c r="F404" s="5" t="n"/>
+      <c r="G404" s="7" t="n">
+        <v>179.71</v>
+      </c>
+      <c r="H404" s="6" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="5" t="inlineStr">
@@ -21527,11 +23472,17 @@
       </c>
       <c r="E405" s="5" t="n"/>
       <c r="F405" s="5" t="n"/>
+      <c r="G405" s="7" t="n">
+        <v>1399.16</v>
+      </c>
+      <c r="H405" s="6" t="n">
+        <v>1399</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22065,7 +24016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -22212,285 +24163,308 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Not on FW27 Plan (Sheet 4 — no price source)</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>127190</v>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Not on FW27 Plan — priced at Historical ASP (REG-INV-015, blended, not RRP)</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>100966</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>75897156</v>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>n/a — single blended price</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>n/a — no cost source</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Not on FW27 Plan — no price source of any kind</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>26224</v>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>Inventory Value by Activity (merchandising category, column AN)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Same Sheets 2-3 rows, grouped by the FW27 plan's "NEW MAPPING: Activity" field (column AN) instead of tier. Sorted by Retail Value, descending.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Activity</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Retail Value (RRP, SEK)</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Wholesale Value (WP, SEK)</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Est. Cost Value (SEK)</t>
         </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Active Essentials</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>133516</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>231030400</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>110094359</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>41785944</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Daily Essentials</t>
+          <t>Active Essentials</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>129806</v>
+        <v>133516</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>180271250</v>
+        <v>231030400</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>86225584</v>
+        <v>110094359</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>33036293</v>
+        <v>41785944</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Trekking</t>
+          <t>Daily Essentials</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>34784</v>
+        <v>129806</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>76087600</v>
+        <v>180271250</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>36319093</v>
+        <v>86225584</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>14545337</v>
+        <v>33036293</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Day Hiking</t>
+          <t>Trekking</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>30148</v>
+        <v>34784</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>75590600</v>
+        <v>76087600</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>36236938</v>
+        <v>36319093</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>14063535</v>
+        <v>14545337</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Trail Run &amp; Fast Hike</t>
+          <t>Day Hiking</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>27151</v>
+        <v>30148</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>74729100</v>
+        <v>75590600</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>35656190</v>
+        <v>36236938</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>16097165</v>
+        <v>14063535</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>(blank)</t>
+          <t>Trail Run &amp; Fast Hike</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>23130</v>
+        <v>27151</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>54257350</v>
+        <v>74729100</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>25877467</v>
+        <v>35656190</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>8630556</v>
+        <v>16097165</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Mountaineering</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>6164</v>
+        <v>23130</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>33084700</v>
+        <v>54257350</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>15754621</v>
+        <v>25877467</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>7592625</v>
+        <v>8630556</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Hiking</t>
+          <t>Mountaineering</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>8718</v>
+        <v>6164</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>23329200</v>
+        <v>33084700</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>11109139</v>
+        <v>15754621</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>3901056</v>
+        <v>7592625</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Freeride</t>
+          <t>Hiking</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>4542</v>
+        <v>8718</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>20693500</v>
+        <v>23329200</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>10557526</v>
+        <v>11109139</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>4860882</v>
+        <v>3901056</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>All Mountain</t>
+          <t>Freeride</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>2128</v>
+        <v>4542</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>3386900</v>
+        <v>20693500</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>1612816</v>
+        <v>10557526</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>689607</v>
+        <v>4860882</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>All Mountain</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>2128</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>3386900</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>1612816</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>689607</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
           <t>Ski Touring</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B28" s="6" t="n">
         <v>686</v>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="C28" s="6" t="n">
         <v>2724600</v>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D28" s="6" t="n">
         <v>1297428</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="E28" s="6" t="n">
         <v>549244</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A15:E15"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A13:E13"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/inventory_analysis/Project_Bob_Sell_Down_Priority_11092026.xlsx
+++ b/data/inventory_analysis/Project_Bob_Sell_Down_Priority_11092026.xlsx
@@ -12312,7 +12312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H405"/>
+  <dimension ref="A1:I405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -12323,6 +12323,7 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12380,6 +12381,11 @@
           <t>Est. Value at Historical ASP (SEK)</t>
         </is>
       </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>No-Price Reason (REG-INV-016)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -12712,6 +12718,11 @@
       </c>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -12960,6 +12971,11 @@
       </c>
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>Not in the curated 1,860-franchise tiering universe (likely a small accessory, out of scope)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -12982,6 +12998,11 @@
       </c>
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -13004,6 +13025,11 @@
       </c>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -13116,6 +13142,11 @@
       </c>
       <c r="E30" s="5" t="n"/>
       <c r="F30" s="5" t="n"/>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -13206,6 +13237,11 @@
       </c>
       <c r="E33" s="5" t="n"/>
       <c r="F33" s="5" t="n"/>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -13296,6 +13332,11 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -13476,6 +13517,11 @@
       </c>
       <c r="E42" s="5" t="n"/>
       <c r="F42" s="5" t="n"/>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>Not in the curated 1,860-franchise tiering universe (likely a small accessory, out of scope)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -13532,6 +13578,11 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>Not in the curated 1,860-franchise tiering universe (likely a small accessory, out of scope)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -13734,6 +13785,11 @@
       </c>
       <c r="E51" s="5" t="n"/>
       <c r="F51" s="5" t="n"/>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -13790,6 +13846,11 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -13840,6 +13901,11 @@
       </c>
       <c r="E55" s="5" t="n"/>
       <c r="F55" s="5" t="n"/>
+      <c r="I55" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -14008,6 +14074,11 @@
       </c>
       <c r="E61" s="5" t="n"/>
       <c r="F61" s="5" t="n"/>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -14030,6 +14101,11 @@
       </c>
       <c r="E62" s="5" t="n"/>
       <c r="F62" s="5" t="n"/>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -14052,6 +14128,11 @@
       </c>
       <c r="E63" s="5" t="n"/>
       <c r="F63" s="5" t="n"/>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -14226,6 +14307,11 @@
       </c>
       <c r="E69" s="5" t="n"/>
       <c r="F69" s="5" t="n"/>
+      <c r="I69" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -14472,6 +14558,11 @@
       </c>
       <c r="E78" s="5" t="n"/>
       <c r="F78" s="5" t="n"/>
+      <c r="I78" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -14618,6 +14709,11 @@
       </c>
       <c r="E83" s="5" t="n"/>
       <c r="F83" s="5" t="n"/>
+      <c r="I83" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -14640,6 +14736,11 @@
       </c>
       <c r="E84" s="5" t="n"/>
       <c r="F84" s="5" t="n"/>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -14700,6 +14801,11 @@
       <c r="F86" s="5" t="inlineStr">
         <is>
           <t>CO</t>
+        </is>
+      </c>
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
         </is>
       </c>
     </row>
@@ -14870,6 +14976,11 @@
       </c>
       <c r="E92" s="5" t="n"/>
       <c r="F92" s="5" t="n"/>
+      <c r="I92" s="8" t="inlineStr">
+        <is>
+          <t>Not in the curated 1,860-franchise tiering universe (likely a small accessory, out of scope)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
@@ -15094,6 +15205,11 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="I100" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
@@ -15234,6 +15350,11 @@
       </c>
       <c r="E105" s="5" t="n"/>
       <c r="F105" s="5" t="n"/>
+      <c r="I105" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -15294,6 +15415,11 @@
       <c r="F107" s="5" t="inlineStr">
         <is>
           <t>CO</t>
+        </is>
+      </c>
+      <c r="I107" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
         </is>
       </c>
     </row>
@@ -15352,6 +15478,11 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="I109" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -15408,6 +15539,11 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="I111" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
@@ -15458,6 +15594,11 @@
       </c>
       <c r="E113" s="5" t="n"/>
       <c r="F113" s="5" t="n"/>
+      <c r="I113" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
@@ -15514,6 +15655,11 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="I115" s="8" t="inlineStr">
+        <is>
+          <t>Not in the curated 1,860-franchise tiering universe (likely a small accessory, out of scope)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
@@ -15660,6 +15806,11 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="I120" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
@@ -15744,6 +15895,11 @@
       </c>
       <c r="E123" s="5" t="n"/>
       <c r="F123" s="5" t="n"/>
+      <c r="I123" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
@@ -15766,6 +15922,11 @@
       </c>
       <c r="E124" s="5" t="n"/>
       <c r="F124" s="5" t="n"/>
+      <c r="I124" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
@@ -16002,6 +16163,11 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="I132" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
@@ -16204,6 +16370,11 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="I139" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
@@ -16260,6 +16431,11 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="I141" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -16338,6 +16514,11 @@
       </c>
       <c r="E144" s="5" t="n"/>
       <c r="F144" s="5" t="n"/>
+      <c r="I144" s="8" t="inlineStr">
+        <is>
+          <t>Not in the curated 1,860-franchise tiering universe (likely a small accessory, out of scope)</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
@@ -16500,6 +16681,11 @@
       </c>
       <c r="E150" s="5" t="n"/>
       <c r="F150" s="5" t="n"/>
+      <c r="I150" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
@@ -16550,6 +16736,11 @@
       </c>
       <c r="E152" s="5" t="n"/>
       <c r="F152" s="5" t="n"/>
+      <c r="I152" s="8" t="inlineStr">
+        <is>
+          <t>Not in the curated 1,860-franchise tiering universe (likely a small accessory, out of scope)</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
@@ -16656,6 +16847,11 @@
       </c>
       <c r="E156" s="5" t="n"/>
       <c r="F156" s="5" t="n"/>
+      <c r="I156" s="8" t="inlineStr">
+        <is>
+          <t>Not in the curated 1,860-franchise tiering universe (likely a small accessory, out of scope)</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
@@ -16682,6 +16878,11 @@
       <c r="F157" s="5" t="inlineStr">
         <is>
           <t>CO</t>
+        </is>
+      </c>
+      <c r="I157" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
         </is>
       </c>
     </row>
@@ -16802,6 +17003,11 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="I161" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
@@ -17088,6 +17294,11 @@
       </c>
       <c r="E171" s="5" t="n"/>
       <c r="F171" s="5" t="n"/>
+      <c r="I171" s="8" t="inlineStr">
+        <is>
+          <t>Not in the curated 1,860-franchise tiering universe (likely a small accessory, out of scope)</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
@@ -17250,6 +17461,11 @@
       </c>
       <c r="E177" s="5" t="n"/>
       <c r="F177" s="5" t="n"/>
+      <c r="I177" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
@@ -17328,6 +17544,11 @@
       </c>
       <c r="E180" s="5" t="n"/>
       <c r="F180" s="5" t="n"/>
+      <c r="I180" s="8" t="inlineStr">
+        <is>
+          <t>Not in the curated 1,860-franchise tiering universe (likely a small accessory, out of scope)</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
@@ -17378,6 +17599,11 @@
       </c>
       <c r="E182" s="5" t="n"/>
       <c r="F182" s="5" t="n"/>
+      <c r="I182" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
@@ -17462,6 +17688,11 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="I185" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
@@ -17882,6 +18113,11 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="I200" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
@@ -18022,6 +18258,11 @@
       </c>
       <c r="E205" s="5" t="n"/>
       <c r="F205" s="5" t="n"/>
+      <c r="I205" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
@@ -18100,6 +18341,11 @@
       </c>
       <c r="E208" s="5" t="n"/>
       <c r="F208" s="5" t="n"/>
+      <c r="I208" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
@@ -18436,6 +18682,11 @@
       </c>
       <c r="E220" s="5" t="n"/>
       <c r="F220" s="5" t="n"/>
+      <c r="I220" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
@@ -18514,6 +18765,11 @@
       </c>
       <c r="E223" s="5" t="n"/>
       <c r="F223" s="5" t="n"/>
+      <c r="I223" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
@@ -18536,6 +18792,11 @@
       </c>
       <c r="E224" s="5" t="n"/>
       <c r="F224" s="5" t="n"/>
+      <c r="I224" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="5" t="inlineStr">
@@ -18614,6 +18875,11 @@
       </c>
       <c r="E227" s="5" t="n"/>
       <c r="F227" s="5" t="n"/>
+      <c r="I227" s="8" t="inlineStr">
+        <is>
+          <t>Not in the curated 1,860-franchise tiering universe (likely a small accessory, out of scope)</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="5" t="inlineStr">
@@ -18782,6 +19048,11 @@
       </c>
       <c r="E233" s="5" t="n"/>
       <c r="F233" s="5" t="n"/>
+      <c r="I233" s="8" t="inlineStr">
+        <is>
+          <t>Not in the curated 1,860-franchise tiering universe (likely a small accessory, out of scope)</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="5" t="inlineStr">
@@ -18832,6 +19103,11 @@
       </c>
       <c r="E235" s="5" t="n"/>
       <c r="F235" s="5" t="n"/>
+      <c r="I235" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
@@ -19190,6 +19466,11 @@
       </c>
       <c r="E248" s="5" t="n"/>
       <c r="F248" s="5" t="n"/>
+      <c r="I248" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
@@ -19380,6 +19661,11 @@
       </c>
       <c r="E255" s="5" t="n"/>
       <c r="F255" s="5" t="n"/>
+      <c r="I255" s="8" t="inlineStr">
+        <is>
+          <t>Not in the curated 1,860-franchise tiering universe (likely a small accessory, out of scope)</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
@@ -19514,6 +19800,11 @@
       </c>
       <c r="E260" s="5" t="n"/>
       <c r="F260" s="5" t="n"/>
+      <c r="I260" s="8" t="inlineStr">
+        <is>
+          <t>Not in the curated 1,860-franchise tiering universe (likely a small accessory, out of scope)</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
@@ -19744,6 +20035,11 @@
       </c>
       <c r="E268" s="5" t="n"/>
       <c r="F268" s="5" t="n"/>
+      <c r="I268" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
@@ -19968,6 +20264,11 @@
           <t>CO</t>
         </is>
       </c>
+      <c r="I276" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
@@ -20438,6 +20739,11 @@
       </c>
       <c r="E293" s="5" t="n"/>
       <c r="F293" s="5" t="n"/>
+      <c r="I293" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
@@ -20516,6 +20822,11 @@
       </c>
       <c r="E296" s="5" t="n"/>
       <c r="F296" s="5" t="n"/>
+      <c r="I296" s="8" t="inlineStr">
+        <is>
+          <t>Not in the curated 1,860-franchise tiering universe (likely a small accessory, out of scope)</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
@@ -21070,6 +21381,11 @@
       </c>
       <c r="E316" s="5" t="n"/>
       <c r="F316" s="5" t="n"/>
+      <c r="I316" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="5" t="inlineStr">
@@ -21120,6 +21436,11 @@
       </c>
       <c r="E318" s="5" t="n"/>
       <c r="F318" s="5" t="n"/>
+      <c r="I318" s="8" t="inlineStr">
+        <is>
+          <t>Not in the curated 1,860-franchise tiering universe (likely a small accessory, out of scope)</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
@@ -21142,6 +21463,11 @@
       </c>
       <c r="E319" s="5" t="n"/>
       <c r="F319" s="5" t="n"/>
+      <c r="I319" s="8" t="inlineStr">
+        <is>
+          <t>Not in the curated 1,860-franchise tiering universe (likely a small accessory, out of scope)</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="5" t="inlineStr">
@@ -21192,6 +21518,11 @@
       </c>
       <c r="E321" s="5" t="n"/>
       <c r="F321" s="5" t="n"/>
+      <c r="I321" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="5" t="inlineStr">
@@ -21528,6 +21859,11 @@
       </c>
       <c r="E333" s="5" t="n"/>
       <c r="F333" s="5" t="n"/>
+      <c r="I333" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="5" t="inlineStr">
@@ -21550,6 +21886,11 @@
       </c>
       <c r="E334" s="5" t="n"/>
       <c r="F334" s="5" t="n"/>
+      <c r="I334" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="5" t="inlineStr">
@@ -21684,6 +22025,11 @@
       </c>
       <c r="E339" s="5" t="n"/>
       <c r="F339" s="5" t="n"/>
+      <c r="I339" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="5" t="inlineStr">
@@ -21930,6 +22276,11 @@
       </c>
       <c r="E348" s="5" t="n"/>
       <c r="F348" s="5" t="n"/>
+      <c r="I348" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="5" t="inlineStr">
@@ -22008,6 +22359,11 @@
       </c>
       <c r="E351" s="5" t="n"/>
       <c r="F351" s="5" t="n"/>
+      <c r="I351" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="5" t="inlineStr">
@@ -22198,6 +22554,11 @@
       </c>
       <c r="E358" s="5" t="n"/>
       <c r="F358" s="5" t="n"/>
+      <c r="I358" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="5" t="inlineStr">
@@ -22276,6 +22637,11 @@
       </c>
       <c r="E361" s="5" t="n"/>
       <c r="F361" s="5" t="n"/>
+      <c r="I361" s="8" t="inlineStr">
+        <is>
+          <t>Not in the curated 1,860-franchise tiering universe (likely a small accessory, out of scope)</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="5" t="inlineStr">
@@ -22298,6 +22664,11 @@
       </c>
       <c r="E362" s="5" t="n"/>
       <c r="F362" s="5" t="n"/>
+      <c r="I362" s="8" t="inlineStr">
+        <is>
+          <t>Not in the curated 1,860-franchise tiering universe (likely a small accessory, out of scope)</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="5" t="inlineStr">
@@ -22404,6 +22775,11 @@
       </c>
       <c r="E366" s="5" t="n"/>
       <c r="F366" s="5" t="n"/>
+      <c r="I366" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="5" t="inlineStr">
@@ -22622,6 +22998,11 @@
       </c>
       <c r="E374" s="5" t="n"/>
       <c r="F374" s="5" t="n"/>
+      <c r="I374" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="5" t="inlineStr">
@@ -22840,6 +23221,11 @@
       </c>
       <c r="E382" s="5" t="n"/>
       <c r="F382" s="5" t="n"/>
+      <c r="I382" s="8" t="inlineStr">
+        <is>
+          <t>Not in the curated 1,860-franchise tiering universe (likely a small accessory, out of scope)</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="5" t="inlineStr">
@@ -23058,6 +23444,11 @@
       </c>
       <c r="E390" s="5" t="n"/>
       <c r="F390" s="5" t="n"/>
+      <c r="I390" s="8" t="inlineStr">
+        <is>
+          <t>Below reliability threshold (FY25 sales &lt;50,000 SEK or zero, REG-004)</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="5" t="inlineStr">
@@ -23481,8 +23872,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/inventory_analysis/Project_Bob_Sell_Down_Priority_11092026.xlsx
+++ b/data/inventory_analysis/Project_Bob_Sell_Down_Priority_11092026.xlsx
@@ -13,6 +13,7 @@
     <sheet name="4. Not on FW27 Plan" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="5. Possible FW27 Renames" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="6. Inventory Value Summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7. Tier x Aging Schedule" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,6 +47,10 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -74,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -89,6 +94,11 @@
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -24860,4 +24870,658 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio Tier x Aging Schedule (Exit Urgency) — Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="95" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Rows = each franchise's current SS26 Portfolio Tier (Hero/Workhorse/Problem Child/etc., from the tiering workbook) — a business-health read. Columns = the FW27 plan's own exit urgency (this workbook's Sheets 2-4) — a time-to-retirement read. The two are independent signals: a Hero-tier franchise exiting FW27 is a generation-transition risk (protect continuity); a Problem Child sitting at "Long runway" is an ongoing margin problem with no forced near-term resolution (needs a pricing/cost fix regardless of aging). "Not in tiering workbook" / "Not on FW27 Plan" mean exactly what Sheets 4/5 of this workbook and the tiering workbook's own register already say about those franchises — not re-explained here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Portfolio Tier</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Exiting FW27 (last season offered)</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Exiting FW27 or SS28 (ambiguous — treat as near-term)</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>One season left (exits after SS28)</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Long runway (continues through FW28+)</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Pending Review (exit season = REVIEW)</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Not on FW27 Plan</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Hero + Near-Hero</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>55381</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>4013</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>59394</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Workhorse + Harvest</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>4188</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>120516</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>435</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>54334</v>
+      </c>
+      <c r="H8" s="11" t="n">
+        <v>179473</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Problem Child</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1633</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>6889</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>7623</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>16145</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>New / Test</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>16120</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>3971</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>2420</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>110952</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>4190</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>40489</v>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>178142</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Thin / Immaterial</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>2282</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>45828</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>14969</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>13368</v>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>76447</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>1606</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>367</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>920</v>
+      </c>
+      <c r="H12" s="11" t="n">
+        <v>2893</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Clearance — Ex China/Zalando</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>1146</v>
+      </c>
+      <c r="H13" s="11" t="n">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Not in tiering workbook</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>1131</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>4726</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>3169</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>5297</v>
+      </c>
+      <c r="H14" s="11" t="n">
+        <v>14323</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>21941</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>5102</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>4702</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>345898</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>23130</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>127190</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>527963</v>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Value below mixes bases (Target RRP for Sheets 2-3's columns, Historical ASP for "Not on FW27 Plan" per REG-INV-015) -- read each cell's own column for what it means, don't sum across the RRP and ASP columns as if they were the same currency of estimate. Cells with no price source (REG-INV-016) show as 0 here, not blank -- cross-reference the Units table above for what's actually being undercounted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Value (mixed basis — see note above), SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Portfolio Tier</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Exiting FW27 (last season offered)</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Exiting FW27 or SS28 (ambiguous — treat as near-term)</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>One season left (exits after SS28)</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Long runway (continues through FW28+)</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>Pending Review (exit season = REVIEW)</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Not on FW27 Plan</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Hero + Near-Hero</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>117506600</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>1656580</v>
+      </c>
+      <c r="H21" s="11" t="n">
+        <v>119163180</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Workhorse + Harvest</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>4007300</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>227551200</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>937900</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>26393822</v>
+      </c>
+      <c r="H22" s="11" t="n">
+        <v>258890222</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Problem Child</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>4382300</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>22380900</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>6630318</v>
+      </c>
+      <c r="H23" s="11" t="n">
+        <v>33393518</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>New / Test</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>48077300</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>7147800</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>14497300</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>161517500</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>10367500</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>37889345</v>
+      </c>
+      <c r="H24" s="11" t="n">
+        <v>279496745</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Thin / Immaterial</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>11208400</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>86610350</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>33853750</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>1741634</v>
+      </c>
+      <c r="H25" s="11" t="n">
+        <v>133414134</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>1457100</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>1175700</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>561829</v>
+      </c>
+      <c r="H26" s="11" t="n">
+        <v>3194629</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Clearance — Ex China/Zalando</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>1023629</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>1023629</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Not in tiering workbook</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>904800</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>13679000</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>7922500</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="11" t="n">
+        <v>22506300</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>56466900</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>8052600</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>25705700</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>630702650</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>54257350</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>75897156</v>
+      </c>
+      <c r="H29" s="11" t="n">
+        <v>851082356</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/inventory_analysis/Project_Bob_Sell_Down_Priority_11092026.xlsx
+++ b/data/inventory_analysis/Project_Bob_Sell_Down_Priority_11092026.xlsx
@@ -22,8 +22,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +54,11 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="FF555555"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -79,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -99,6 +106,8 @@
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -24878,7 +24887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -25206,98 +25215,98 @@
         <v>527963</v>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>% of Total</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Value below mixes bases (Target RRP for Sheets 2-3's columns, Historical ASP for "Not on FW27 Plan" per REG-INV-015) -- read each cell's own column for what it means, don't sum across the RRP and ASP columns as if they were the same currency of estimate. Cells with no price source (REG-INV-016) show as 0 here, not blank -- cross-reference the Units table above for what's actually being undercounted.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>Value (mixed basis — see note above), SEK</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>Portfolio Tier</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Exiting FW27 (last season offered)</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>Exiting FW27 or SS28 (ambiguous — treat as near-term)</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>One season left (exits after SS28)</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>Long runway (continues through FW28+)</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>Pending Review (exit season = REVIEW)</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>Not on FW27 Plan</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Hero + Near-Hero</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>117506600</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>1656580</v>
-      </c>
-      <c r="H21" s="11" t="n">
-        <v>119163180</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Workhorse + Harvest</t>
+          <t>Hero + Near-Hero</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>4007300</v>
+        <v>0</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>0</v>
@@ -25306,26 +25315,26 @@
         <v>0</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>227551200</v>
+        <v>117506600</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>937900</v>
+        <v>0</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>26393822</v>
+        <v>1656580</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>258890222</v>
+        <v>119163180</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Problem Child</t>
+          <t>Workhorse + Harvest</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>4382300</v>
+        <v>4007300</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>0</v>
@@ -25334,78 +25343,78 @@
         <v>0</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>22380900</v>
+        <v>227551200</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0</v>
+        <v>937900</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>6630318</v>
+        <v>26393822</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>33393518</v>
+        <v>258890222</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>New / Test</t>
+          <t>Problem Child</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>48077300</v>
+        <v>4382300</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>7147800</v>
+        <v>0</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>14497300</v>
+        <v>0</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>161517500</v>
+        <v>22380900</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>10367500</v>
+        <v>0</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>37889345</v>
+        <v>6630318</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>279496745</v>
+        <v>33393518</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Thin / Immaterial</t>
+          <t>New / Test</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>0</v>
+        <v>48077300</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>0</v>
+        <v>7147800</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>11208400</v>
+        <v>14497300</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>86610350</v>
+        <v>161517500</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>33853750</v>
+        <v>10367500</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>1741634</v>
+        <v>37889345</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>133414134</v>
+        <v>279496745</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Exited</t>
+          <t>Thin / Immaterial</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
@@ -25415,25 +25424,25 @@
         <v>0</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>0</v>
+        <v>11208400</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>1457100</v>
+        <v>86610350</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1175700</v>
+        <v>33853750</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>561829</v>
+        <v>1741634</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>3194629</v>
+        <v>133414134</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Clearance — Ex China/Zalando</t>
+          <t>Exited</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
@@ -25446,81 +25455,137 @@
         <v>0</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0</v>
+        <v>1457100</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0</v>
+        <v>1175700</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>1023629</v>
+        <v>561829</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>1023629</v>
+        <v>3194629</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Not in tiering workbook</t>
+          <t>Clearance — Ex China/Zalando</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>904800</v>
+        <v>0</v>
       </c>
       <c r="D28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>1023629</v>
+      </c>
+      <c r="H28" s="11" t="n">
+        <v>1023629</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Not in tiering workbook</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>904800</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="6" t="n">
         <v>13679000</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F29" s="6" t="n">
         <v>7922500</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="G29" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="11" t="n">
+      <c r="H29" s="11" t="n">
         <v>22506300</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B29" s="11" t="n">
+      <c r="B30" s="11" t="n">
         <v>56466900</v>
       </c>
-      <c r="C29" s="11" t="n">
+      <c r="C30" s="11" t="n">
         <v>8052600</v>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D30" s="11" t="n">
         <v>25705700</v>
       </c>
-      <c r="E29" s="11" t="n">
+      <c r="E30" s="11" t="n">
         <v>630702650</v>
       </c>
-      <c r="F29" s="11" t="n">
+      <c r="F30" s="11" t="n">
         <v>54257350</v>
       </c>
-      <c r="G29" s="11" t="n">
+      <c r="G30" s="11" t="n">
         <v>75897156</v>
       </c>
-      <c r="H29" s="11" t="n">
+      <c r="H30" s="11" t="n">
         <v>851082356</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>% of Total</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G31" s="14" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A20:H20"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
